--- a/import/c_phi_data_geforceerd.xlsx
+++ b/import/c_phi_data_geforceerd.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="19">
   <si>
     <t>PV_NAAM</t>
   </si>
@@ -68,6 +68,9 @@
   </si>
   <si>
     <t>kappa_2_ondergrens_cor</t>
+  </si>
+  <si>
+    <t>TXT_SAFE_klei_licht_16_175</t>
   </si>
 </sst>
 </file>
@@ -425,7 +428,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R1"/>
+  <dimension ref="A1:R41"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:18">
@@ -484,6 +487,2246 @@
         <v>17</v>
       </c>
     </row>
+    <row r="2" spans="1:18">
+      <c r="A2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2">
+        <v>102.98</v>
+      </c>
+      <c r="C2">
+        <v>62.56</v>
+      </c>
+      <c r="D2">
+        <v>2377.32083625102</v>
+      </c>
+      <c r="E2">
+        <v>-3050.286540840457</v>
+      </c>
+      <c r="F2">
+        <v>2.748859081039612</v>
+      </c>
+      <c r="G2">
+        <v>20.840000152588</v>
+      </c>
+      <c r="H2">
+        <v>13.17898383273264</v>
+      </c>
+      <c r="I2">
+        <v>17.94773050078498</v>
+      </c>
+      <c r="J2">
+        <v>48425.79727508202</v>
+      </c>
+      <c r="K2">
+        <v>-2900.149026338879</v>
+      </c>
+      <c r="L2">
+        <v>1.179783012480086</v>
+      </c>
+      <c r="M2">
+        <v>54.56</v>
+      </c>
+      <c r="N2">
+        <v>5.20612533301011</v>
+      </c>
+      <c r="O2">
+        <v>12.70175932396434</v>
+      </c>
+      <c r="P2">
+        <v>18.42495500955327</v>
+      </c>
+      <c r="Q2">
+        <v>-2795.131658382791</v>
+      </c>
+      <c r="R2">
+        <v>2.444227929496325</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18">
+      <c r="A3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3">
+        <v>196.28</v>
+      </c>
+      <c r="C3">
+        <v>110.19</v>
+      </c>
+      <c r="D3">
+        <v>1984.009613091984</v>
+      </c>
+      <c r="E3">
+        <v>4908.107531726183</v>
+      </c>
+      <c r="F3">
+        <v>4.88707161375546</v>
+      </c>
+      <c r="G3">
+        <v>32.12505770952285</v>
+      </c>
+      <c r="H3">
+        <v>19.51590318852269</v>
+      </c>
+      <c r="I3">
+        <v>24.06879877445653</v>
+      </c>
+      <c r="J3">
+        <v>43586.4013606754</v>
+      </c>
+      <c r="K3">
+        <v>-4074.404679023864</v>
+      </c>
+      <c r="L3">
+        <v>0.8385023160065448</v>
+      </c>
+      <c r="M3">
+        <v>102.19</v>
+      </c>
+      <c r="N3">
+        <v>37.82660943187111</v>
+      </c>
+      <c r="O3">
+        <v>19.06027962310524</v>
+      </c>
+      <c r="P3">
+        <v>24.52442233987398</v>
+      </c>
+      <c r="Q3">
+        <v>-3979.282523063275</v>
+      </c>
+      <c r="R3">
+        <v>1.880522070225117</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18">
+      <c r="A4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4">
+        <v>94.59</v>
+      </c>
+      <c r="C4">
+        <v>58.31</v>
+      </c>
+      <c r="D4">
+        <v>3265.868437454711</v>
+      </c>
+      <c r="E4">
+        <v>-3332.286887794231</v>
+      </c>
+      <c r="F4">
+        <v>4.157448545031228</v>
+      </c>
+      <c r="G4">
+        <v>43.41011526645769</v>
+      </c>
+      <c r="H4">
+        <v>25.84775021722176</v>
+      </c>
+      <c r="I4">
+        <v>30.19493937521905</v>
+      </c>
+      <c r="J4">
+        <v>39001.71049439544</v>
+      </c>
+      <c r="K4">
+        <v>-5104.633606075894</v>
+      </c>
+      <c r="L4">
+        <v>0.5629344852255217</v>
+      </c>
+      <c r="M4">
+        <v>50.31</v>
+      </c>
+      <c r="N4">
+        <v>3.612583131401773</v>
+      </c>
+      <c r="O4">
+        <v>25.41271238551085</v>
+      </c>
+      <c r="P4">
+        <v>30.62997720692995</v>
+      </c>
+      <c r="Q4">
+        <v>-5018.718634095613</v>
+      </c>
+      <c r="R4">
+        <v>1.405001122510772</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18">
+      <c r="A5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5">
+        <v>35.7</v>
+      </c>
+      <c r="C5">
+        <v>22.88</v>
+      </c>
+      <c r="D5">
+        <v>13464.76573458049</v>
+      </c>
+      <c r="E5">
+        <v>-2654.94434204651</v>
+      </c>
+      <c r="F5">
+        <v>0.7842975096314581</v>
+      </c>
+      <c r="G5">
+        <v>54.69517282339254</v>
+      </c>
+      <c r="H5">
+        <v>32.17377107887813</v>
+      </c>
+      <c r="I5">
+        <v>36.32690614302428</v>
+      </c>
+      <c r="J5">
+        <v>34671.72467624215</v>
+      </c>
+      <c r="K5">
+        <v>-5990.867164404954</v>
+      </c>
+      <c r="L5">
+        <v>0.3489355253842005</v>
+      </c>
+      <c r="M5">
+        <v>14.88</v>
+      </c>
+      <c r="N5">
+        <v>23.28320753568169</v>
+      </c>
+      <c r="O5">
+        <v>31.7581528926336</v>
+      </c>
+      <c r="P5">
+        <v>36.7425243292688</v>
+      </c>
+      <c r="Q5">
+        <v>-5913.477624372561</v>
+      </c>
+      <c r="R5">
+        <v>1.012691684631328</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18">
+      <c r="A6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6">
+        <v>90.70999999999999</v>
+      </c>
+      <c r="C6">
+        <v>53.42</v>
+      </c>
+      <c r="D6">
+        <v>3724.389588428528</v>
+      </c>
+      <c r="E6">
+        <v>-3260.103857348102</v>
+      </c>
+      <c r="F6">
+        <v>0.5032211749185612</v>
+      </c>
+      <c r="G6">
+        <v>65.98023038032738</v>
+      </c>
+      <c r="H6">
+        <v>38.49311176363879</v>
+      </c>
+      <c r="I6">
+        <v>42.46555308772521</v>
+      </c>
+      <c r="J6">
+        <v>30596.44390621552</v>
+      </c>
+      <c r="K6">
+        <v>-6733.153217871932</v>
+      </c>
+      <c r="L6">
+        <v>0.1916739815180599</v>
+      </c>
+      <c r="M6">
+        <v>45.42</v>
+      </c>
+      <c r="N6">
+        <v>21.61359822754606</v>
+      </c>
+      <c r="O6">
+        <v>38.09557620734718</v>
+      </c>
+      <c r="P6">
+        <v>42.86308864401683</v>
+      </c>
+      <c r="Q6">
+        <v>-6663.616937549908</v>
+      </c>
+      <c r="R6">
+        <v>0.6977953017446787</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18">
+      <c r="A7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7">
+        <v>172.76</v>
+      </c>
+      <c r="C7">
+        <v>100.26</v>
+      </c>
+      <c r="D7">
+        <v>441.9338519848084</v>
+      </c>
+      <c r="E7">
+        <v>2107.688059196543</v>
+      </c>
+      <c r="F7">
+        <v>0.7083271669301493</v>
+      </c>
+      <c r="G7">
+        <v>77.26528793726223</v>
+      </c>
+      <c r="H7">
+        <v>44.80482084166709</v>
+      </c>
+      <c r="I7">
+        <v>48.61183163915852</v>
+      </c>
+      <c r="J7">
+        <v>26775.86818431555</v>
+      </c>
+      <c r="K7">
+        <v>-7331.562239382315</v>
+      </c>
+      <c r="L7">
+        <v>0.08557713733081966</v>
+      </c>
+      <c r="M7">
+        <v>92.26000000000001</v>
+      </c>
+      <c r="N7">
+        <v>9.597852674180466</v>
+      </c>
+      <c r="O7">
+        <v>44.42384047425108</v>
+      </c>
+      <c r="P7">
+        <v>48.99281200657452</v>
+      </c>
+      <c r="Q7">
+        <v>-7269.221151454213</v>
+      </c>
+      <c r="R7">
+        <v>0.4536238966507215</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18">
+      <c r="A8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8">
+        <v>79.28</v>
+      </c>
+      <c r="C8">
+        <v>51.57</v>
+      </c>
+      <c r="D8">
+        <v>5250.12947493129</v>
+      </c>
+      <c r="E8">
+        <v>-3736.647569551509</v>
+      </c>
+      <c r="F8">
+        <v>14.05962469702511</v>
+      </c>
+      <c r="G8">
+        <v>88.55034549419707</v>
+      </c>
+      <c r="H8">
+        <v>51.10786287624045</v>
+      </c>
+      <c r="I8">
+        <v>54.76677723404675</v>
+      </c>
+      <c r="J8">
+        <v>23209.99751054226</v>
+      </c>
+      <c r="K8">
+        <v>-7786.194851299138</v>
+      </c>
+      <c r="L8">
+        <v>0.02431496851382262</v>
+      </c>
+      <c r="M8">
+        <v>43.57</v>
+      </c>
+      <c r="N8">
+        <v>0.0361172068666924</v>
+      </c>
+      <c r="O8">
+        <v>50.74170301735608</v>
+      </c>
+      <c r="P8">
+        <v>55.13293709293112</v>
+      </c>
+      <c r="Q8">
+        <v>-7730.411027684723</v>
+      </c>
+      <c r="R8">
+        <v>0.2725805114200511</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18">
+      <c r="A9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9">
+        <v>107.4</v>
+      </c>
+      <c r="C9">
+        <v>67.56</v>
+      </c>
+      <c r="D9">
+        <v>1965.838485914868</v>
+      </c>
+      <c r="E9">
+        <v>-2995.460226777194</v>
+      </c>
+      <c r="F9">
+        <v>17.79378964254533</v>
+      </c>
+      <c r="G9">
+        <v>99.83540305113192</v>
+      </c>
+      <c r="H9">
+        <v>57.40114679067597</v>
+      </c>
+      <c r="I9">
+        <v>60.93148094907284</v>
+      </c>
+      <c r="J9">
+        <v>19898.83188489562</v>
+      </c>
+      <c r="K9">
+        <v>-8097.190567085543</v>
+      </c>
+      <c r="L9">
+        <v>0.0008460867935685585</v>
+      </c>
+      <c r="M9">
+        <v>59.56</v>
+      </c>
+      <c r="N9">
+        <v>0.07762168062996844</v>
+      </c>
+      <c r="O9">
+        <v>57.04785438455682</v>
+      </c>
+      <c r="P9">
+        <v>61.28477335519198</v>
+      </c>
+      <c r="Q9">
+        <v>-8047.354002867011</v>
+      </c>
+      <c r="R9">
+        <v>0.1462144469921932</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18">
+      <c r="A10" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10">
+        <v>202.3</v>
+      </c>
+      <c r="C10">
+        <v>124.9</v>
+      </c>
+      <c r="D10">
+        <v>2556.538375756322</v>
+      </c>
+      <c r="E10">
+        <v>6315.221629300304</v>
+      </c>
+      <c r="F10">
+        <v>84.20776212045369</v>
+      </c>
+      <c r="G10">
+        <v>111.1204606080668</v>
+      </c>
+      <c r="H10">
+        <v>63.68357273222762</v>
+      </c>
+      <c r="I10">
+        <v>67.10704263698277</v>
+      </c>
+      <c r="J10">
+        <v>16842.37130737565</v>
+      </c>
+      <c r="K10">
+        <v>-8264.737012715994</v>
+      </c>
+      <c r="L10">
+        <v>0.00755151644368676</v>
+      </c>
+      <c r="M10">
+        <v>116.9</v>
+      </c>
+      <c r="N10">
+        <v>27.42425083020706</v>
+      </c>
+      <c r="O10">
+        <v>63.34097459118461</v>
+      </c>
+      <c r="P10">
+        <v>67.4496407780258</v>
+      </c>
+      <c r="Q10">
+        <v>-8220.275255699447</v>
+      </c>
+      <c r="R10">
+        <v>0.06538181461794615</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18">
+      <c r="A11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11">
+        <v>58.33</v>
+      </c>
+      <c r="C11">
+        <v>35.63</v>
+      </c>
+      <c r="D11">
+        <v>8725.01283908115</v>
+      </c>
+      <c r="E11">
+        <v>-3328.11910118519</v>
+      </c>
+      <c r="F11">
+        <v>0.3926876124277968</v>
+      </c>
+      <c r="G11">
+        <v>122.4055181650016</v>
+      </c>
+      <c r="H11">
+        <v>69.95409829057496</v>
+      </c>
+      <c r="I11">
+        <v>73.29450470809701</v>
+      </c>
+      <c r="J11">
+        <v>14040.61577798234</v>
+      </c>
+      <c r="K11">
+        <v>-8289.078268302455</v>
+      </c>
+      <c r="L11">
+        <v>0.03647569471460082</v>
+      </c>
+      <c r="M11">
+        <v>27.63</v>
+      </c>
+      <c r="N11">
+        <v>20.85118518904353</v>
+      </c>
+      <c r="O11">
+        <v>69.61981259190951</v>
+      </c>
+      <c r="P11">
+        <v>73.62879040676246</v>
+      </c>
+      <c r="Q11">
+        <v>-8249.467718128508</v>
+      </c>
+      <c r="R11">
+        <v>0.02053477173527912</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18">
+      <c r="A12" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12">
+        <v>312.6</v>
+      </c>
+      <c r="C12">
+        <v>171.5</v>
+      </c>
+      <c r="D12">
+        <v>25876.65472822748</v>
+      </c>
+      <c r="E12">
+        <v>27587.87121236992</v>
+      </c>
+      <c r="F12">
+        <v>26.0673820631274</v>
+      </c>
+      <c r="G12">
+        <v>133.6905757219365</v>
+      </c>
+      <c r="H12">
+        <v>76.21181992540581</v>
+      </c>
+      <c r="I12">
+        <v>79.49477070272776</v>
+      </c>
+      <c r="J12">
+        <v>11493.5652967157</v>
+      </c>
+      <c r="K12">
+        <v>-8170.520356581093</v>
+      </c>
+      <c r="L12">
+        <v>0.07967569657313057</v>
+      </c>
+      <c r="M12">
+        <v>163.5</v>
+      </c>
+      <c r="N12">
+        <v>81.81717124453857</v>
+      </c>
+      <c r="O12">
+        <v>75.88328400578695</v>
+      </c>
+      <c r="P12">
+        <v>79.82330662234662</v>
+      </c>
+      <c r="Q12">
+        <v>-8135.298662338109</v>
+      </c>
+      <c r="R12">
+        <v>0.002140642896065892</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18">
+      <c r="A13" t="s">
+        <v>18</v>
+      </c>
+      <c r="B13">
+        <v>127.6</v>
+      </c>
+      <c r="C13">
+        <v>66.86</v>
+      </c>
+      <c r="D13">
+        <v>582.6322875460318</v>
+      </c>
+      <c r="E13">
+        <v>-1613.851782746052</v>
+      </c>
+      <c r="F13">
+        <v>58.23965039185672</v>
+      </c>
+      <c r="G13">
+        <v>144.9756332788713</v>
+      </c>
+      <c r="H13">
+        <v>82.4560589402132</v>
+      </c>
+      <c r="I13">
+        <v>85.70851931738197</v>
+      </c>
+      <c r="J13">
+        <v>9201.219863575725</v>
+      </c>
+      <c r="K13">
+        <v>-7909.43165399569</v>
+      </c>
+      <c r="L13">
+        <v>0.1296496440619567</v>
+      </c>
+      <c r="M13">
+        <v>58.86</v>
+      </c>
+      <c r="N13">
+        <v>133.8915722205397</v>
+      </c>
+      <c r="O13">
+        <v>82.1305742974283</v>
+      </c>
+      <c r="P13">
+        <v>86.03400396016687</v>
+      </c>
+      <c r="Q13">
+        <v>-7878.210194110019</v>
+      </c>
+      <c r="R13">
+        <v>0.001196073854871941</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18">
+      <c r="A14" t="s">
+        <v>18</v>
+      </c>
+      <c r="B14">
+        <v>100.9</v>
+      </c>
+      <c r="C14">
+        <v>58.73</v>
+      </c>
+      <c r="D14">
+        <v>2584.479589350386</v>
+      </c>
+      <c r="E14">
+        <v>-2985.702654212916</v>
+      </c>
+      <c r="F14">
+        <v>1.048448243788287</v>
+      </c>
+      <c r="G14">
+        <v>156.2606908358061</v>
+      </c>
+      <c r="H14">
+        <v>88.68643578683758</v>
+      </c>
+      <c r="I14">
+        <v>91.93613010021919</v>
+      </c>
+      <c r="J14">
+        <v>7163.579478562413</v>
+      </c>
+      <c r="K14">
+        <v>-7506.236492803998</v>
+      </c>
+      <c r="L14">
+        <v>0.1797818354534798</v>
+      </c>
+      <c r="M14">
+        <v>50.73</v>
+      </c>
+      <c r="N14">
+        <v>24.63731999284618</v>
+      </c>
+      <c r="O14">
+        <v>88.36122795335372</v>
+      </c>
+      <c r="P14">
+        <v>92.26133793370305</v>
+      </c>
+      <c r="Q14">
+        <v>-7478.711574412762</v>
+      </c>
+      <c r="R14">
+        <v>0.009761251864225528</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18">
+      <c r="A15" t="s">
+        <v>18</v>
+      </c>
+      <c r="B15">
+        <v>24.93</v>
+      </c>
+      <c r="C15">
+        <v>16.92</v>
+      </c>
+      <c r="D15">
+        <v>16080.21235519596</v>
+      </c>
+      <c r="E15">
+        <v>-2145.587590009919</v>
+      </c>
+      <c r="F15">
+        <v>0.8116340526826602</v>
+      </c>
+      <c r="G15">
+        <v>167.545748392741</v>
+      </c>
+      <c r="H15">
+        <v>94.90291533798306</v>
+      </c>
+      <c r="I15">
+        <v>98.1776381785353</v>
+      </c>
+      <c r="J15">
+        <v>5380.644141675764</v>
+      </c>
+      <c r="K15">
+        <v>-6961.401602415333</v>
+      </c>
+      <c r="L15">
+        <v>0.2247210548086066</v>
+      </c>
+      <c r="M15">
+        <v>8.920000000000002</v>
+      </c>
+      <c r="N15">
+        <v>23.43111049144251</v>
+      </c>
+      <c r="O15">
+        <v>94.57520281565418</v>
+      </c>
+      <c r="P15">
+        <v>98.50535070086418</v>
+      </c>
+      <c r="Q15">
+        <v>-6937.36294701737</v>
+      </c>
+      <c r="R15">
+        <v>0.02141393265175408</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18">
+      <c r="A16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B16">
+        <v>70.91</v>
+      </c>
+      <c r="C16">
+        <v>49.13</v>
+      </c>
+      <c r="D16">
+        <v>6533.129565047488</v>
+      </c>
+      <c r="E16">
+        <v>-3971.068693214381</v>
+      </c>
+      <c r="F16">
+        <v>35.16005078187658</v>
+      </c>
+      <c r="G16">
+        <v>178.8308059496758</v>
+      </c>
+      <c r="H16">
+        <v>101.1058112136215</v>
+      </c>
+      <c r="I16">
+        <v>104.4327299323584</v>
+      </c>
+      <c r="J16">
+        <v>3852.413852915781</v>
+      </c>
+      <c r="K16">
+        <v>-6275.416943874675</v>
+      </c>
+      <c r="L16">
+        <v>0.2606148350165677</v>
+      </c>
+      <c r="M16">
+        <v>41.13</v>
+      </c>
+      <c r="N16">
+        <v>3.959818347247407</v>
+      </c>
+      <c r="O16">
+        <v>100.7728752743111</v>
+      </c>
+      <c r="P16">
+        <v>104.7656658716688</v>
+      </c>
+      <c r="Q16">
+        <v>-6254.75233706628</v>
+      </c>
+      <c r="R16">
+        <v>0.03153059043971856</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18">
+      <c r="A17" t="s">
+        <v>18</v>
+      </c>
+      <c r="B17">
+        <v>319.549987792969</v>
+      </c>
+      <c r="C17">
+        <v>209.050003051758</v>
+      </c>
+      <c r="D17">
+        <v>28160.93802834547</v>
+      </c>
+      <c r="E17">
+        <v>35081.14313922744</v>
+      </c>
+      <c r="F17">
+        <v>818.4295447895945</v>
+      </c>
+      <c r="G17">
+        <v>190.1158635066107</v>
+      </c>
+      <c r="H17">
+        <v>107.2957479732355</v>
+      </c>
+      <c r="I17">
+        <v>110.7007808022061</v>
+      </c>
+      <c r="J17">
+        <v>2578.888612282462</v>
+      </c>
+      <c r="K17">
+        <v>-5448.774111715502</v>
+      </c>
+      <c r="L17">
+        <v>0.2851585008045973</v>
+      </c>
+      <c r="M17">
+        <v>201.050003051758</v>
+      </c>
+      <c r="N17">
+        <v>608.5371501485484</v>
+      </c>
+      <c r="O17">
+        <v>106.9549948923407</v>
+      </c>
+      <c r="P17">
+        <v>111.0415338831008</v>
+      </c>
+      <c r="Q17">
+        <v>-5431.469730127802</v>
+      </c>
+      <c r="R17">
+        <v>0.03734527675238551</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18">
+      <c r="A18" t="s">
+        <v>18</v>
+      </c>
+      <c r="B18">
+        <v>87.389999389648</v>
+      </c>
+      <c r="C18">
+        <v>51.990001678467</v>
+      </c>
+      <c r="D18">
+        <v>4140.636507502104</v>
+      </c>
+      <c r="E18">
+        <v>-3345.441075708017</v>
+      </c>
+      <c r="F18">
+        <v>0.09415332170862969</v>
+      </c>
+      <c r="G18">
+        <v>201.4009210635455</v>
+      </c>
+      <c r="H18">
+        <v>113.4735912658377</v>
+      </c>
+      <c r="I18">
+        <v>116.9809251390655</v>
+      </c>
+      <c r="J18">
+        <v>1560.068419775808</v>
+      </c>
+      <c r="K18">
+        <v>-4481.946030194753</v>
+      </c>
+      <c r="L18">
+        <v>0.2974684961560704</v>
+      </c>
+      <c r="M18">
+        <v>43.990001678467</v>
+      </c>
+      <c r="N18">
+        <v>18.03281333628908</v>
+      </c>
+      <c r="O18">
+        <v>113.1226005755687</v>
+      </c>
+      <c r="P18">
+        <v>117.3319158293344</v>
+      </c>
+      <c r="Q18">
+        <v>-4468.082704699036</v>
+      </c>
+      <c r="R18">
+        <v>0.03779759473194401</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18">
+      <c r="A19" t="s">
+        <v>18</v>
+      </c>
+      <c r="B19">
+        <v>42.080001831055</v>
+      </c>
+      <c r="C19">
+        <v>27.079999923706</v>
+      </c>
+      <c r="D19">
+        <v>12024.8276960911</v>
+      </c>
+      <c r="E19">
+        <v>-2969.53254828217</v>
+      </c>
+      <c r="F19">
+        <v>0.04291710799402142</v>
+      </c>
+      <c r="G19">
+        <v>212.6859786204804</v>
+      </c>
+      <c r="H19">
+        <v>119.6403627614145</v>
+      </c>
+      <c r="I19">
+        <v>123.2721412729502</v>
+      </c>
+      <c r="J19">
+        <v>795.9532753958177</v>
+      </c>
+      <c r="K19">
+        <v>-3375.370949737799</v>
+      </c>
+      <c r="L19">
+        <v>0.2978313969722741</v>
+      </c>
+      <c r="M19">
+        <v>19.079999923706</v>
+      </c>
+      <c r="N19">
+        <v>17.19616860493785</v>
+      </c>
+      <c r="O19">
+        <v>119.2769184778811</v>
+      </c>
+      <c r="P19">
+        <v>123.6355855564837</v>
+      </c>
+      <c r="Q19">
+        <v>-3365.117225591765</v>
+      </c>
+      <c r="R19">
+        <v>0.03323147750718273</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18">
+      <c r="A20" t="s">
+        <v>18</v>
+      </c>
+      <c r="B20">
+        <v>65.330001831055</v>
+      </c>
+      <c r="C20">
+        <v>39.830001831055</v>
+      </c>
+      <c r="D20">
+        <v>7466.303642023503</v>
+      </c>
+      <c r="E20">
+        <v>-3441.621850658518</v>
+      </c>
+      <c r="F20">
+        <v>0.08434671569162262</v>
+      </c>
+      <c r="G20">
+        <v>223.9710361774152</v>
+      </c>
+      <c r="H20">
+        <v>125.7971567621093</v>
+      </c>
+      <c r="I20">
+        <v>129.573334901717</v>
+      </c>
+      <c r="J20">
+        <v>286.5431791424922</v>
+      </c>
+      <c r="K20">
+        <v>-2129.442231838719</v>
+      </c>
+      <c r="L20">
+        <v>0.287397210263021</v>
+      </c>
+      <c r="M20">
+        <v>31.830001831055</v>
+      </c>
+      <c r="N20">
+        <v>17.8936355442914</v>
+      </c>
+      <c r="O20">
+        <v>125.4192619224088</v>
+      </c>
+      <c r="P20">
+        <v>129.9512297414175</v>
+      </c>
+      <c r="Q20">
+        <v>-2123.045384313986</v>
+      </c>
+      <c r="R20">
+        <v>0.02502710222213793</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18">
+      <c r="A21" t="s">
+        <v>18</v>
+      </c>
+      <c r="B21">
+        <v>250.683853149414</v>
+      </c>
+      <c r="C21">
+        <v>139.483856201172</v>
+      </c>
+      <c r="D21">
+        <v>9790.325948291043</v>
+      </c>
+      <c r="E21">
+        <v>13801.38023116313</v>
+      </c>
+      <c r="F21">
+        <v>8.679017821972542</v>
+      </c>
+      <c r="G21">
+        <v>235.2560937343501</v>
+      </c>
+      <c r="H21">
+        <v>131.9450704402343</v>
+      </c>
+      <c r="I21">
+        <v>135.8834088530537</v>
+      </c>
+      <c r="J21">
+        <v>31.8381310158313</v>
+      </c>
+      <c r="K21">
+        <v>-744.5038571359127</v>
+      </c>
+      <c r="L21">
+        <v>0.2678778494988603</v>
+      </c>
+      <c r="M21">
+        <v>131.483856201172</v>
+      </c>
+      <c r="N21">
+        <v>47.41257754745181</v>
+      </c>
+      <c r="O21">
+        <v>131.5509476769069</v>
+      </c>
+      <c r="P21">
+        <v>136.277531616381</v>
+      </c>
+      <c r="Q21">
+        <v>-742.2800081015889</v>
+      </c>
+      <c r="R21">
+        <v>0.01523901621823073</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18">
+      <c r="A22" t="s">
+        <v>18</v>
+      </c>
+      <c r="B22">
+        <v>460.957244873047</v>
+      </c>
+      <c r="C22">
+        <v>250.057250976563</v>
+      </c>
+      <c r="D22">
+        <v>95616.6791958274</v>
+      </c>
+      <c r="E22">
+        <v>77322.5700379222</v>
+      </c>
+      <c r="F22">
+        <v>71.18069043253089</v>
+      </c>
+      <c r="G22">
+        <v>246.5411512912849</v>
+      </c>
+      <c r="H22">
+        <v>138.0851530758964</v>
+      </c>
+      <c r="I22">
+        <v>142.2013138468531</v>
+      </c>
+      <c r="J22">
+        <v>31.83813101583483</v>
+      </c>
+      <c r="K22">
+        <v>779.1494501098464</v>
+      </c>
+      <c r="L22">
+        <v>0.2412901136815812</v>
+      </c>
+      <c r="M22">
+        <v>242.057250976563</v>
+      </c>
+      <c r="N22">
+        <v>153.1784167995084</v>
+      </c>
+      <c r="O22">
+        <v>137.673235031457</v>
+      </c>
+      <c r="P22">
+        <v>142.6132318912925</v>
+      </c>
+      <c r="Q22">
+        <v>776.8251906897268</v>
+      </c>
+      <c r="R22">
+        <v>0.006287674207990829</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18">
+      <c r="A23" t="s">
+        <v>18</v>
+      </c>
+      <c r="B23">
+        <v>76.209999084473</v>
+      </c>
+      <c r="C23">
+        <v>44.909999847412</v>
+      </c>
+      <c r="D23">
+        <v>5704.445265157044</v>
+      </c>
+      <c r="E23">
+        <v>-3391.95250307546</v>
+      </c>
+      <c r="F23">
+        <v>1.478267925751405</v>
+      </c>
+      <c r="G23">
+        <v>257.8262088482197</v>
+      </c>
+      <c r="H23">
+        <v>144.2183742485364</v>
+      </c>
+      <c r="I23">
+        <v>148.5260803036747</v>
+      </c>
+      <c r="J23">
+        <v>286.5431791425019</v>
+      </c>
+      <c r="K23">
+        <v>2441.268981243473</v>
+      </c>
+      <c r="L23">
+        <v>0.2097595706792486</v>
+      </c>
+      <c r="M23">
+        <v>36.909999847412</v>
+      </c>
+      <c r="N23">
+        <v>26.57920398623899</v>
+      </c>
+      <c r="O23">
+        <v>143.7872876236473</v>
+      </c>
+      <c r="P23">
+        <v>148.9571669285638</v>
+      </c>
+      <c r="Q23">
+        <v>2433.971725182626</v>
+      </c>
+      <c r="R23">
+        <v>0.0007240695024572424</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18">
+      <c r="A24" t="s">
+        <v>18</v>
+      </c>
+      <c r="B24">
+        <v>27.590000152588</v>
+      </c>
+      <c r="C24">
+        <v>18.590000152588</v>
+      </c>
+      <c r="D24">
+        <v>15412.67054267235</v>
+      </c>
+      <c r="E24">
+        <v>-2307.90719401964</v>
+      </c>
+      <c r="F24">
+        <v>0.488800804908938</v>
+      </c>
+      <c r="G24">
+        <v>269.1112664051545</v>
+      </c>
+      <c r="H24">
+        <v>150.3456077956754</v>
+      </c>
+      <c r="I24">
+        <v>154.8568343859972</v>
+      </c>
+      <c r="J24">
+        <v>795.9532753958322</v>
+      </c>
+      <c r="K24">
+        <v>4241.647093516389</v>
+      </c>
+      <c r="L24">
+        <v>0.1753848989937095</v>
+      </c>
+      <c r="M24">
+        <v>10.590000152588</v>
+      </c>
+      <c r="N24">
+        <v>21.51850987845511</v>
+      </c>
+      <c r="O24">
+        <v>149.8941541867153</v>
+      </c>
+      <c r="P24">
+        <v>155.3082879949573</v>
+      </c>
+      <c r="Q24">
+        <v>4228.910393612887</v>
+      </c>
+      <c r="R24">
+        <v>0.001066924227839477</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18">
+      <c r="A25" t="s">
+        <v>18</v>
+      </c>
+      <c r="B25">
+        <v>242.449996948242</v>
+      </c>
+      <c r="C25">
+        <v>131.449996948242</v>
+      </c>
+      <c r="D25">
+        <v>8228.706813948824</v>
+      </c>
+      <c r="E25">
+        <v>11924.12101073784</v>
+      </c>
+      <c r="F25">
+        <v>41.40985672966868</v>
+      </c>
+      <c r="G25">
+        <v>280.3963239620894</v>
+      </c>
+      <c r="H25">
+        <v>156.4676272792761</v>
+      </c>
+      <c r="I25">
+        <v>161.1928025318582</v>
+      </c>
+      <c r="J25">
+        <v>1560.068419775826</v>
+      </c>
+      <c r="K25">
+        <v>6180.111628752818</v>
+      </c>
+      <c r="L25">
+        <v>0.1401531797321536</v>
+      </c>
+      <c r="M25">
+        <v>123.449996948242</v>
+      </c>
+      <c r="N25">
+        <v>107.6346276646026</v>
+      </c>
+      <c r="O25">
+        <v>155.9947631085151</v>
+      </c>
+      <c r="P25">
+        <v>161.6656667026191</v>
+      </c>
+      <c r="Q25">
+        <v>6161.434580910044</v>
+      </c>
+      <c r="R25">
+        <v>0.009701027262872666</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18">
+      <c r="A26" t="s">
+        <v>18</v>
+      </c>
+      <c r="B26">
+        <v>29.979999542236</v>
+      </c>
+      <c r="C26">
+        <v>18.979999542236</v>
+      </c>
+      <c r="D26">
+        <v>14824.9564170764</v>
+      </c>
+      <c r="E26">
+        <v>-2310.962563967888</v>
+      </c>
+      <c r="F26">
+        <v>2.651515161109947</v>
+      </c>
+      <c r="G26">
+        <v>291.6813815190242</v>
+      </c>
+      <c r="H26">
+        <v>162.5851089389309</v>
+      </c>
+      <c r="I26">
+        <v>167.5333085016649</v>
+      </c>
+      <c r="J26">
+        <v>2578.888612282482</v>
+      </c>
+      <c r="K26">
+        <v>8256.520405243615</v>
+      </c>
+      <c r="L26">
+        <v>0.1058937043076859</v>
+      </c>
+      <c r="M26">
+        <v>10.979999542236</v>
+      </c>
+      <c r="N26">
+        <v>31.00272704871483</v>
+      </c>
+      <c r="O26">
+        <v>162.0899259757777</v>
+      </c>
+      <c r="P26">
+        <v>168.0284914648181</v>
+      </c>
+      <c r="Q26">
+        <v>8231.373648161825</v>
+      </c>
+      <c r="R26">
+        <v>0.02882179670208083</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18">
+      <c r="A27" t="s">
+        <v>18</v>
+      </c>
+      <c r="B27">
+        <v>67.84</v>
+      </c>
+      <c r="C27">
+        <v>43.64</v>
+      </c>
+      <c r="D27">
+        <v>7038.8370169778</v>
+      </c>
+      <c r="E27">
+        <v>-3661.298996455843</v>
+      </c>
+      <c r="F27">
+        <v>4.554526800029939</v>
+      </c>
+      <c r="G27">
+        <v>302.966439075959</v>
+      </c>
+      <c r="H27">
+        <v>168.6986389335552</v>
+      </c>
+      <c r="I27">
+        <v>173.8777661365021</v>
+      </c>
+      <c r="J27">
+        <v>3852.413852915803</v>
+      </c>
+      <c r="K27">
+        <v>10470.75617577957</v>
+      </c>
+      <c r="L27">
+        <v>0.0742585469507482</v>
+      </c>
+      <c r="M27">
+        <v>35.64</v>
+      </c>
+      <c r="N27">
+        <v>3.259931890447133</v>
+      </c>
+      <c r="O27">
+        <v>168.1803462652042</v>
+      </c>
+      <c r="P27">
+        <v>174.3960588048532</v>
+      </c>
+      <c r="Q27">
+        <v>10438.58688151434</v>
+      </c>
+      <c r="R27">
+        <v>0.06041196401897916</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18">
+      <c r="A28" t="s">
+        <v>18</v>
+      </c>
+      <c r="B28">
+        <v>31.84</v>
+      </c>
+      <c r="C28">
+        <v>19.78</v>
+      </c>
+      <c r="D28">
+        <v>14375.47697446682</v>
+      </c>
+      <c r="E28">
+        <v>-2371.578032765733</v>
+      </c>
+      <c r="F28">
+        <v>3.441055302341098</v>
+      </c>
+      <c r="G28">
+        <v>314.2514966328938</v>
+      </c>
+      <c r="H28">
+        <v>174.8087226013817</v>
+      </c>
+      <c r="I28">
+        <v>180.2256700981373</v>
+      </c>
+      <c r="J28">
+        <v>5380.644141675785</v>
+      </c>
+      <c r="K28">
+        <v>12822.72222407052</v>
+      </c>
+      <c r="L28">
+        <v>0.04672037880942322</v>
+      </c>
+      <c r="M28">
+        <v>11.78</v>
+      </c>
+      <c r="N28">
+        <v>33.57820099107776</v>
+      </c>
+      <c r="O28">
+        <v>174.2666304568185</v>
+      </c>
+      <c r="P28">
+        <v>180.7677622427004</v>
+      </c>
+      <c r="Q28">
+        <v>12782.95820722889</v>
+      </c>
+      <c r="R28">
+        <v>0.106238950665715</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18">
+      <c r="A29" t="s">
+        <v>18</v>
+      </c>
+      <c r="B29">
+        <v>39.47</v>
+      </c>
+      <c r="C29">
+        <v>27.63</v>
+      </c>
+      <c r="D29">
+        <v>12604.0537945879</v>
+      </c>
+      <c r="E29">
+        <v>-3101.95868368641</v>
+      </c>
+      <c r="F29">
+        <v>3.180778981725064</v>
+      </c>
+      <c r="G29">
+        <v>325.5365541898286</v>
+      </c>
+      <c r="H29">
+        <v>180.9157942687035</v>
+      </c>
+      <c r="I29">
+        <v>186.576586060277</v>
+      </c>
+      <c r="J29">
+        <v>7163.579478562432</v>
+      </c>
+      <c r="K29">
+        <v>15312.33863460676</v>
+      </c>
+      <c r="L29">
+        <v>0.02458051156323227</v>
+      </c>
+      <c r="M29">
+        <v>19.63</v>
+      </c>
+      <c r="N29">
+        <v>4.649146821735417</v>
+      </c>
+      <c r="O29">
+        <v>180.3492998058981</v>
+      </c>
+      <c r="P29">
+        <v>187.1430805230824</v>
+      </c>
+      <c r="Q29">
+        <v>15264.39171496843</v>
+      </c>
+      <c r="R29">
+        <v>0.1678645215898153</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18">
+      <c r="A30" t="s">
+        <v>18</v>
+      </c>
+      <c r="B30">
+        <v>36.58</v>
+      </c>
+      <c r="C30">
+        <v>25.38</v>
+      </c>
+      <c r="D30">
+        <v>13261.31364673076</v>
+      </c>
+      <c r="E30">
+        <v>-2922.704385014878</v>
+      </c>
+      <c r="F30">
+        <v>1.273878322957281</v>
+      </c>
+      <c r="G30">
+        <v>336.8216117467634</v>
+      </c>
+      <c r="H30">
+        <v>187.0202267392967</v>
+      </c>
+      <c r="I30">
+        <v>192.9301412191454</v>
+      </c>
+      <c r="J30">
+        <v>9201.219863575741</v>
+      </c>
+      <c r="K30">
+        <v>17939.53919604372</v>
+      </c>
+      <c r="L30">
+        <v>0.008982356371106412</v>
+      </c>
+      <c r="M30">
+        <v>17.38</v>
+      </c>
+      <c r="N30">
+        <v>7.90171931155601</v>
+      </c>
+      <c r="O30">
+        <v>186.428801731673</v>
+      </c>
+      <c r="P30">
+        <v>193.521566226769</v>
+      </c>
+      <c r="Q30">
+        <v>17882.80794140475</v>
+      </c>
+      <c r="R30">
+        <v>0.2466609379464854</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18">
+      <c r="A31" t="s">
+        <v>18</v>
+      </c>
+      <c r="B31">
+        <v>83.33</v>
+      </c>
+      <c r="C31">
+        <v>44.76</v>
+      </c>
+      <c r="D31">
+        <v>4679.623979713776</v>
+      </c>
+      <c r="E31">
+        <v>-3061.932106905672</v>
+      </c>
+      <c r="F31">
+        <v>28.04607943156623</v>
+      </c>
+      <c r="G31">
+        <v>348.1066693036983</v>
+      </c>
+      <c r="H31">
+        <v>193.1223400087439</v>
+      </c>
+      <c r="I31">
+        <v>199.2860155791597</v>
+      </c>
+      <c r="J31">
+        <v>11493.56529671571</v>
+      </c>
+      <c r="K31">
+        <v>20704.26886402184</v>
+      </c>
+      <c r="L31">
+        <v>0.0009271814780645421</v>
+      </c>
+      <c r="M31">
+        <v>36.76</v>
+      </c>
+      <c r="N31">
+        <v>85.29477078004213</v>
+      </c>
+      <c r="O31">
+        <v>192.505520275793</v>
+      </c>
+      <c r="P31">
+        <v>199.9028353121107</v>
+      </c>
+      <c r="Q31">
+        <v>20638.14082523009</v>
+      </c>
+      <c r="R31">
+        <v>0.3438298685387012</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18">
+      <c r="A32" t="s">
+        <v>18</v>
+      </c>
+      <c r="B32">
+        <v>380.579986572266</v>
+      </c>
+      <c r="C32">
+        <v>218.779998779297</v>
+      </c>
+      <c r="D32">
+        <v>52368.75679617091</v>
+      </c>
+      <c r="E32">
+        <v>50066.09828988411</v>
+      </c>
+      <c r="F32">
+        <v>21.63719548595194</v>
+      </c>
+      <c r="G32">
+        <v>359.3917268606331</v>
+      </c>
+      <c r="H32">
+        <v>199.2224090107087</v>
+      </c>
+      <c r="I32">
+        <v>205.6439342066566</v>
+      </c>
+      <c r="J32">
+        <v>14040.61577798235</v>
+      </c>
+      <c r="K32">
+        <v>23606.48169932913</v>
+      </c>
+      <c r="L32">
+        <v>0.00129026450076935</v>
+      </c>
+      <c r="M32">
+        <v>210.779998779297</v>
+      </c>
+      <c r="N32">
+        <v>0.5068272513700383</v>
+      </c>
+      <c r="O32">
+        <v>198.5797853989933</v>
+      </c>
+      <c r="P32">
+        <v>206.2865578183719</v>
+      </c>
+      <c r="Q32">
+        <v>23530.33523264977</v>
+      </c>
+      <c r="R32">
+        <v>0.4604217749295739</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18">
+      <c r="A33" t="s">
+        <v>18</v>
+      </c>
+      <c r="B33">
+        <v>270.5</v>
+      </c>
+      <c r="C33">
+        <v>142.300003051758</v>
+      </c>
+      <c r="D33">
+        <v>14104.46556740213</v>
+      </c>
+      <c r="E33">
+        <v>16899.86466867402</v>
+      </c>
+      <c r="F33">
+        <v>122.4951992671089</v>
+      </c>
+      <c r="G33">
+        <v>370.6767844175679</v>
+      </c>
+      <c r="H33">
+        <v>205.3206703585628</v>
+      </c>
+      <c r="I33">
+        <v>212.003660488264</v>
+      </c>
+      <c r="J33">
+        <v>16842.37130737565</v>
+      </c>
+      <c r="K33">
+        <v>26646.13920018548</v>
+      </c>
+      <c r="L33">
+        <v>0.0108363546376743</v>
+      </c>
+      <c r="M33">
+        <v>134.300003051758</v>
+      </c>
+      <c r="N33">
+        <v>225.2225594880809</v>
+      </c>
+      <c r="O33">
+        <v>204.6518810720368</v>
+      </c>
+      <c r="P33">
+        <v>212.67244977479</v>
+      </c>
+      <c r="Q33">
+        <v>26559.34495587854</v>
+      </c>
+      <c r="R33">
+        <v>0.5973544683634713</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18">
+      <c r="A34" t="s">
+        <v>18</v>
+      </c>
+      <c r="B34">
+        <v>309.440002441406</v>
+      </c>
+      <c r="C34">
+        <v>173.740005493164</v>
+      </c>
+      <c r="D34">
+        <v>24869.99185008183</v>
+      </c>
+      <c r="E34">
+        <v>27399.18548192432</v>
+      </c>
+      <c r="F34">
+        <v>1.257535002237749</v>
+      </c>
+      <c r="G34">
+        <v>381.9618419745027</v>
+      </c>
+      <c r="H34">
+        <v>211.4173281314331</v>
+      </c>
+      <c r="I34">
+        <v>218.3649903448552</v>
+      </c>
+      <c r="J34">
+        <v>19898.83188489561</v>
+      </c>
+      <c r="K34">
+        <v>29823.2089562075</v>
+      </c>
+      <c r="L34">
+        <v>0.03023388880148443</v>
+      </c>
+      <c r="M34">
+        <v>165.740005493164</v>
+      </c>
+      <c r="N34">
+        <v>25.61433402967278</v>
+      </c>
+      <c r="O34">
+        <v>210.7220522198187</v>
+      </c>
+      <c r="P34">
+        <v>219.0602662564697</v>
+      </c>
+      <c r="Q34">
+        <v>29725.13109770101</v>
+      </c>
+      <c r="R34">
+        <v>0.7554301712105329</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18">
+      <c r="A35" t="s">
+        <v>18</v>
+      </c>
+      <c r="B35">
+        <v>110.029998779297</v>
+      </c>
+      <c r="C35">
+        <v>64.23000335693401</v>
+      </c>
+      <c r="D35">
+        <v>1739.53877973504</v>
+      </c>
+      <c r="E35">
+        <v>-2678.890747159341</v>
+      </c>
+      <c r="F35">
+        <v>0.3174240527079064</v>
+      </c>
+      <c r="G35">
+        <v>393.2468995314375</v>
+      </c>
+      <c r="H35">
+        <v>217.5125587950426</v>
+      </c>
+      <c r="I35">
+        <v>224.7277473107073</v>
+      </c>
+      <c r="J35">
+        <v>23209.99751054224</v>
+      </c>
+      <c r="K35">
+        <v>33137.66356233606</v>
+      </c>
+      <c r="L35">
+        <v>0.06006773257725708</v>
+      </c>
+      <c r="M35">
+        <v>56.23000335693401</v>
+      </c>
+      <c r="N35">
+        <v>20.27760222622262</v>
+      </c>
+      <c r="O35">
+        <v>216.7905106270981</v>
+      </c>
+      <c r="P35">
+        <v>225.4497954786518</v>
+      </c>
+      <c r="Q35">
+        <v>33027.66076802526</v>
+      </c>
+      <c r="R35">
+        <v>0.9353508079859983</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18">
+      <c r="A36" t="s">
+        <v>18</v>
+      </c>
+      <c r="B36">
+        <v>411.130004882813</v>
+      </c>
+      <c r="C36">
+        <v>228.229995727539</v>
+      </c>
+      <c r="D36">
+        <v>67284.32778881623</v>
+      </c>
+      <c r="E36">
+        <v>59201.08701869292</v>
+      </c>
+      <c r="F36">
+        <v>7.623475713315658</v>
+      </c>
+      <c r="G36">
+        <v>404.5319570883723</v>
+      </c>
+      <c r="H36">
+        <v>223.6065153626354</v>
+      </c>
+      <c r="I36">
+        <v>231.091778372576</v>
+      </c>
+      <c r="J36">
+        <v>26775.86818431553</v>
+      </c>
+      <c r="K36">
+        <v>36589.4797416081</v>
+      </c>
+      <c r="L36">
+        <v>0.1008504095386824</v>
+      </c>
+      <c r="M36">
+        <v>220.229995727539</v>
+      </c>
+      <c r="N36">
+        <v>44.89973051035379</v>
+      </c>
+      <c r="O36">
+        <v>222.8574399322185</v>
+      </c>
+      <c r="P36">
+        <v>231.8408538029929</v>
+      </c>
+      <c r="Q36">
+        <v>36466.90603108037</v>
+      </c>
+      <c r="R36">
+        <v>1.137731482177156</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18">
+      <c r="A37" t="s">
+        <v>18</v>
+      </c>
+      <c r="B37">
+        <v>319.399993896484</v>
+      </c>
+      <c r="C37">
+        <v>177.600006103516</v>
+      </c>
+      <c r="D37">
+        <v>28110.61891182146</v>
+      </c>
+      <c r="E37">
+        <v>29776.81071087166</v>
+      </c>
+      <c r="F37">
+        <v>7.612066806844364</v>
+      </c>
+      <c r="G37">
+        <v>415.8170146453072</v>
+      </c>
+      <c r="H37">
+        <v>229.6993309014234</v>
+      </c>
+      <c r="I37">
+        <v>237.4569504632496</v>
+      </c>
+      <c r="J37">
+        <v>30596.44390621548</v>
+      </c>
+      <c r="K37">
+        <v>40178.63763518572</v>
+      </c>
+      <c r="L37">
+        <v>0.1530318888533582</v>
+      </c>
+      <c r="M37">
+        <v>169.600006103516</v>
+      </c>
+      <c r="N37">
+        <v>44.87203655611126</v>
+      </c>
+      <c r="O37">
+        <v>228.9229998353583</v>
+      </c>
+      <c r="P37">
+        <v>238.2332815293148</v>
+      </c>
+      <c r="Q37">
+        <v>40042.8430533471</v>
+      </c>
+      <c r="R37">
+        <v>1.363112222805872</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18">
+      <c r="A38" t="s">
+        <v>18</v>
+      </c>
+      <c r="B38">
+        <v>314.140014648438</v>
+      </c>
+      <c r="C38">
+        <v>180.139999389648</v>
+      </c>
+      <c r="D38">
+        <v>26374.48673236844</v>
+      </c>
+      <c r="E38">
+        <v>29255.13895711832</v>
+      </c>
+      <c r="F38">
+        <v>7.20566813147533</v>
+      </c>
+      <c r="G38">
+        <v>427.102072202242</v>
+      </c>
+      <c r="H38">
+        <v>235.7911214825619</v>
+      </c>
+      <c r="I38">
+        <v>243.8231475115727</v>
+      </c>
+      <c r="J38">
+        <v>34671.7246762421</v>
+      </c>
+      <c r="K38">
+        <v>43905.12022619123</v>
+      </c>
+      <c r="L38">
+        <v>0.2170080539036305</v>
+      </c>
+      <c r="M38">
+        <v>172.139999389648</v>
+      </c>
+      <c r="N38">
+        <v>1.575839156800939</v>
+      </c>
+      <c r="O38">
+        <v>234.9873296389338</v>
+      </c>
+      <c r="P38">
+        <v>244.6269393552008</v>
+      </c>
+      <c r="Q38">
+        <v>43755.45141207546</v>
+      </c>
+      <c r="R38">
+        <v>1.61196814801608</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18">
+      <c r="A39" t="s">
+        <v>18</v>
+      </c>
+      <c r="B39">
+        <v>20.840000152588</v>
+      </c>
+      <c r="C39">
+        <v>13.340000152588</v>
+      </c>
+      <c r="D39">
+        <v>17134.2280326416</v>
+      </c>
+      <c r="E39">
+        <v>-1746.176365617121</v>
+      </c>
+      <c r="F39">
+        <v>4.943316412462525</v>
+      </c>
+      <c r="G39">
+        <v>438.3871297591768</v>
+      </c>
+      <c r="H39">
+        <v>241.881988661942</v>
+      </c>
+      <c r="I39">
+        <v>250.1902679616542</v>
+      </c>
+      <c r="J39">
+        <v>39001.71049439537</v>
+      </c>
+      <c r="K39">
+        <v>47768.91287062776</v>
+      </c>
+      <c r="L39">
+        <v>0.2931279952705457</v>
+      </c>
+      <c r="M39">
+        <v>5.340000152588001</v>
+      </c>
+      <c r="N39">
+        <v>37.98280192078255</v>
+      </c>
+      <c r="O39">
+        <v>241.0505512249153</v>
+      </c>
+      <c r="P39">
+        <v>251.0217053986809</v>
+      </c>
+      <c r="Q39">
+        <v>47604.71353232062</v>
+      </c>
+      <c r="R39">
+        <v>1.884718217724613</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18">
+      <c r="A40" t="s">
+        <v>18</v>
+      </c>
+      <c r="B40">
+        <v>70.23000335693401</v>
+      </c>
+      <c r="C40">
+        <v>42.729999542236</v>
+      </c>
+      <c r="D40">
+        <v>6643.517194789833</v>
+      </c>
+      <c r="E40">
+        <v>-3482.827138462243</v>
+      </c>
+      <c r="F40">
+        <v>0.009038830785578463</v>
+      </c>
+      <c r="G40">
+        <v>449.6721873161116</v>
+      </c>
+      <c r="H40">
+        <v>247.9720215674928</v>
+      </c>
+      <c r="I40">
+        <v>256.5582226855649</v>
+      </c>
+      <c r="J40">
+        <v>43586.40136067531</v>
+      </c>
+      <c r="K40">
+        <v>51770.00291412485</v>
+      </c>
+      <c r="L40">
+        <v>0.3817002735670845</v>
+      </c>
+      <c r="M40">
+        <v>34.729999542236</v>
+      </c>
+      <c r="N40">
+        <v>16.27908368175363</v>
+      </c>
+      <c r="O40">
+        <v>247.1127715598946</v>
+      </c>
+      <c r="P40">
+        <v>257.4174726931631</v>
+      </c>
+      <c r="Q40">
+        <v>51590.61422698132</v>
+      </c>
+      <c r="R40">
+        <v>2.181732749939935</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18">
+      <c r="A41" t="s">
+        <v>18</v>
+      </c>
+      <c r="B41">
+        <v>224.669998168945</v>
+      </c>
+      <c r="C41">
+        <v>128.470001220703</v>
+      </c>
+      <c r="D41">
+        <v>5319.108857308576</v>
+      </c>
+      <c r="E41">
+        <v>9369.602518534417</v>
+      </c>
+      <c r="F41">
+        <v>0.1591615335336428</v>
+      </c>
+      <c r="G41">
+        <v>460.9572448730464</v>
+      </c>
+      <c r="H41">
+        <v>254.0612986575061</v>
+      </c>
+      <c r="I41">
+        <v>262.9269332250132</v>
+      </c>
+      <c r="J41">
+        <v>48425.79727508192</v>
+      </c>
+      <c r="K41">
+        <v>55908.37937762152</v>
+      </c>
+      <c r="L41">
+        <v>0.4829982898005652</v>
+      </c>
+      <c r="M41">
+        <v>120.470001220703</v>
+      </c>
+      <c r="N41">
+        <v>12.53663680945795</v>
+      </c>
+      <c r="O41">
+        <v>253.1740848053336</v>
+      </c>
+      <c r="P41">
+        <v>263.8141470771858</v>
+      </c>
+      <c r="Q41">
+        <v>55713.14031957351</v>
+      </c>
+      <c r="R41">
+        <v>2.503339865984894</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/import/c_phi_data_geforceerd.xlsx
+++ b/import/c_phi_data_geforceerd.xlsx
@@ -510,37 +510,37 @@
         <v>20.840000152588</v>
       </c>
       <c r="H2">
-        <v>13.17898383273264</v>
+        <v>9.9020746549891</v>
       </c>
       <c r="I2">
-        <v>17.94773050078498</v>
+        <v>21.22463967852851</v>
       </c>
       <c r="J2">
         <v>48425.79727508202</v>
       </c>
       <c r="K2">
-        <v>-2900.149026338879</v>
+        <v>-2179.036907085044</v>
       </c>
       <c r="L2">
-        <v>1.179783012480086</v>
+        <v>0.2298293414006464</v>
       </c>
       <c r="M2">
-        <v>54.56</v>
+        <v>58.5</v>
       </c>
       <c r="N2">
-        <v>5.20612533301011</v>
+        <v>2.749517329212706</v>
       </c>
       <c r="O2">
-        <v>12.70175932396434</v>
+        <v>9.901764788491688</v>
       </c>
       <c r="P2">
-        <v>18.42495500955327</v>
+        <v>21.22432981922115</v>
       </c>
       <c r="Q2">
-        <v>-2795.131658382791</v>
+        <v>-2178.968718290508</v>
       </c>
       <c r="R2">
-        <v>2.444227929496325</v>
+        <v>0.2301265406353878</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -566,37 +566,37 @@
         <v>32.12505770952285</v>
       </c>
       <c r="H3">
-        <v>19.51590318852269</v>
+        <v>16.17567064198671</v>
       </c>
       <c r="I3">
-        <v>24.06879877445653</v>
+        <v>27.40903132099251</v>
       </c>
       <c r="J3">
         <v>43586.4013606754</v>
       </c>
       <c r="K3">
-        <v>-4074.404679023864</v>
+        <v>-3377.052423011561</v>
       </c>
       <c r="L3">
-        <v>0.8385023160065448</v>
+        <v>0.1638346036939383</v>
       </c>
       <c r="M3">
-        <v>102.19</v>
+        <v>106.13</v>
       </c>
       <c r="N3">
-        <v>37.82660943187111</v>
+        <v>4.886753265765213</v>
       </c>
       <c r="O3">
-        <v>19.06027962310524</v>
+        <v>16.17537607564727</v>
       </c>
       <c r="P3">
-        <v>24.52442233987398</v>
+        <v>27.40873676178646</v>
       </c>
       <c r="Q3">
-        <v>-3979.282523063275</v>
+        <v>-3376.990925346805</v>
       </c>
       <c r="R3">
-        <v>1.880522070225117</v>
+        <v>0.1640731506781457</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -622,37 +622,37 @@
         <v>43.41011526645769</v>
       </c>
       <c r="H4">
-        <v>25.84775021722176</v>
+        <v>22.44555813639322</v>
       </c>
       <c r="I4">
-        <v>30.19493937521905</v>
+        <v>33.59713145604758</v>
       </c>
       <c r="J4">
         <v>39001.71049439544</v>
       </c>
       <c r="K4">
-        <v>-5104.633606075894</v>
+        <v>-4432.739770667679</v>
       </c>
       <c r="L4">
-        <v>0.5629344852255217</v>
+        <v>0.1114445028195387</v>
       </c>
       <c r="M4">
-        <v>50.31</v>
+        <v>54.25</v>
       </c>
       <c r="N4">
-        <v>3.612583131401773</v>
+        <v>4.1583044463321</v>
       </c>
       <c r="O4">
-        <v>25.41271238551085</v>
+        <v>22.44527887020941</v>
       </c>
       <c r="P4">
-        <v>30.62997720692995</v>
+        <v>33.59685219694523</v>
       </c>
       <c r="Q4">
-        <v>-5018.718634095613</v>
+        <v>-4432.684618805913</v>
       </c>
       <c r="R4">
-        <v>1.405001122510772</v>
+        <v>0.111631037370897</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -678,37 +678,37 @@
         <v>54.69517282339254</v>
       </c>
       <c r="H5">
-        <v>32.17377107887813</v>
+        <v>28.71165499502634</v>
       </c>
       <c r="I5">
-        <v>36.32690614302428</v>
+        <v>39.78902222687607</v>
       </c>
       <c r="J5">
         <v>34671.72467624215</v>
       </c>
       <c r="K5">
-        <v>-5990.867164404954</v>
+        <v>-5346.209206366509</v>
       </c>
       <c r="L5">
-        <v>0.3489355253842005</v>
+        <v>0.07112454490776596</v>
       </c>
       <c r="M5">
-        <v>14.88</v>
+        <v>18.82</v>
       </c>
       <c r="N5">
-        <v>23.28320753568169</v>
+        <v>0.7837844454196563</v>
       </c>
       <c r="O5">
-        <v>31.7581528926336</v>
+        <v>28.71139102899574</v>
       </c>
       <c r="P5">
-        <v>36.7425243292688</v>
+        <v>39.78875826787981</v>
       </c>
       <c r="Q5">
-        <v>-5913.477624372561</v>
+        <v>-5346.160054981011</v>
       </c>
       <c r="R5">
-        <v>1.012691684631328</v>
+        <v>0.07126540976593447</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -734,37 +734,37 @@
         <v>65.98023038032738</v>
       </c>
       <c r="H6">
-        <v>38.49311176363879</v>
+        <v>34.9738845782874</v>
       </c>
       <c r="I6">
-        <v>42.46555308772521</v>
+        <v>45.9847802730766</v>
       </c>
       <c r="J6">
         <v>30596.44390621552</v>
       </c>
       <c r="K6">
-        <v>-6733.153217871932</v>
+        <v>-6117.575657061318</v>
       </c>
       <c r="L6">
-        <v>0.1916739815180599</v>
+        <v>0.04137885698653937</v>
       </c>
       <c r="M6">
-        <v>45.42</v>
+        <v>49.36</v>
       </c>
       <c r="N6">
-        <v>21.61359822754606</v>
+        <v>0.5029159971931801</v>
       </c>
       <c r="O6">
-        <v>38.09557620734718</v>
+        <v>34.97363591240757</v>
       </c>
       <c r="P6">
-        <v>42.86308864401683</v>
+        <v>45.98453161418889</v>
       </c>
       <c r="Q6">
-        <v>-6663.616937549908</v>
+        <v>-6117.532160825439</v>
       </c>
       <c r="R6">
-        <v>0.6977953017446787</v>
+        <v>0.04148008502168629</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -790,37 +790,37 @@
         <v>77.26528793726223</v>
       </c>
       <c r="H7">
-        <v>44.80482084166709</v>
+        <v>41.23217647208939</v>
       </c>
       <c r="I7">
-        <v>48.61183163915852</v>
+        <v>52.18447600873621</v>
       </c>
       <c r="J7">
         <v>26775.86818431555</v>
       </c>
       <c r="K7">
-        <v>-7331.562239382315</v>
+        <v>-6746.958527935734</v>
       </c>
       <c r="L7">
-        <v>0.08557713733081966</v>
+        <v>0.02075953889376583</v>
       </c>
       <c r="M7">
-        <v>92.26000000000001</v>
+        <v>96.2</v>
       </c>
       <c r="N7">
-        <v>9.597852674180466</v>
+        <v>0.7085020529279198</v>
       </c>
       <c r="O7">
-        <v>44.42384047425108</v>
+        <v>41.23194310635781</v>
       </c>
       <c r="P7">
-        <v>48.99281200657452</v>
+        <v>52.18424264995955</v>
       </c>
       <c r="Q7">
-        <v>-7269.221151454213</v>
+        <v>-6746.9203415229</v>
       </c>
       <c r="R7">
-        <v>0.4536238966507215</v>
+        <v>0.02082684082022829</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -846,37 +846,37 @@
         <v>88.55034549419707</v>
       </c>
       <c r="H8">
-        <v>51.10786287624045</v>
+        <v>47.48646718137286</v>
       </c>
       <c r="I8">
-        <v>54.76677723404675</v>
+        <v>58.38817292891434</v>
       </c>
       <c r="J8">
         <v>23209.99751054226</v>
       </c>
       <c r="K8">
-        <v>-7786.194851299138</v>
+        <v>-7234.481456783412</v>
       </c>
       <c r="L8">
-        <v>0.02431496851382262</v>
+        <v>0.007875970718547069</v>
       </c>
       <c r="M8">
-        <v>43.57</v>
+        <v>47.51</v>
       </c>
       <c r="N8">
-        <v>0.0361172068666924</v>
+        <v>14.06135430388009</v>
       </c>
       <c r="O8">
-        <v>50.74170301735608</v>
+        <v>47.48624911578699</v>
       </c>
       <c r="P8">
-        <v>55.13293709293112</v>
+        <v>58.38795487025126</v>
       </c>
       <c r="Q8">
-        <v>-7730.411027684723</v>
+        <v>-7234.448234867127</v>
       </c>
       <c r="R8">
-        <v>0.2725805114200511</v>
+        <v>0.007914723458558712</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -902,37 +902,37 @@
         <v>99.83540305113192</v>
       </c>
       <c r="H9">
-        <v>57.40114679067597</v>
+        <v>53.73670078057049</v>
       </c>
       <c r="I9">
-        <v>60.93148094907284</v>
+        <v>64.59592695917831</v>
       </c>
       <c r="J9">
         <v>19898.83188489562</v>
       </c>
       <c r="K9">
-        <v>-8097.190567085543</v>
+        <v>-7580.272015356536</v>
       </c>
       <c r="L9">
-        <v>0.0008460867935685585</v>
+        <v>0.001403905946059814</v>
       </c>
       <c r="M9">
-        <v>59.56</v>
+        <v>63.5</v>
       </c>
       <c r="N9">
-        <v>0.07762168062996844</v>
+        <v>17.79541376375152</v>
       </c>
       <c r="O9">
-        <v>57.04785438455682</v>
+        <v>53.73649801512776</v>
       </c>
       <c r="P9">
-        <v>61.28477335519198</v>
+        <v>64.59572420063139</v>
       </c>
       <c r="Q9">
-        <v>-8047.354002867011</v>
+        <v>-7580.243412610389</v>
       </c>
       <c r="R9">
-        <v>0.1462144469921932</v>
+        <v>0.001419141788319563</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -958,37 +958,37 @@
         <v>111.1204606080668</v>
       </c>
       <c r="H10">
-        <v>63.68357273222762</v>
+        <v>59.9828295064279</v>
       </c>
       <c r="I10">
-        <v>67.10704263698277</v>
+        <v>70.80778586278251</v>
       </c>
       <c r="J10">
         <v>16842.37130737565</v>
       </c>
       <c r="K10">
-        <v>-8264.737012715994</v>
+        <v>-7784.461359190249</v>
       </c>
       <c r="L10">
-        <v>0.00755151644368676</v>
+        <v>9.417395849304534E-05</v>
       </c>
       <c r="M10">
-        <v>116.9</v>
+        <v>120.84</v>
       </c>
       <c r="N10">
-        <v>27.42425083020706</v>
+        <v>84.20893381163276</v>
       </c>
       <c r="O10">
-        <v>63.34097459118461</v>
+        <v>59.9826420411257</v>
       </c>
       <c r="P10">
-        <v>67.4496407780258</v>
+        <v>70.80759840435437</v>
       </c>
       <c r="Q10">
-        <v>-8220.275255699447</v>
+        <v>-7784.437030287909</v>
       </c>
       <c r="R10">
-        <v>0.06538181461794615</v>
+        <v>9.05706526230713E-05</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -1014,37 +1014,37 @@
         <v>122.4055181650016</v>
       </c>
       <c r="H11">
-        <v>69.95409829057496</v>
+        <v>66.22481427918164</v>
       </c>
       <c r="I11">
-        <v>73.29450470809701</v>
+        <v>77.02378871949033</v>
       </c>
       <c r="J11">
         <v>14040.61577798234</v>
       </c>
       <c r="K11">
-        <v>-8289.078268302455</v>
+        <v>-7847.183828797787</v>
       </c>
       <c r="L11">
-        <v>0.03647569471460082</v>
+        <v>0.002780814997462076</v>
       </c>
       <c r="M11">
-        <v>27.63</v>
+        <v>31.57</v>
       </c>
       <c r="N11">
-        <v>20.85118518904353</v>
+        <v>0.3923630327124475</v>
       </c>
       <c r="O11">
-        <v>69.61981259190951</v>
+        <v>66.22464211401736</v>
       </c>
       <c r="P11">
-        <v>73.62879040676246</v>
+        <v>77.0236165611836</v>
       </c>
       <c r="Q11">
-        <v>-8249.467718128508</v>
+        <v>-7847.16342841301</v>
       </c>
       <c r="R11">
-        <v>0.02053477173527912</v>
+        <v>0.002762686917858693</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -1070,37 +1070,37 @@
         <v>133.6905757219365</v>
       </c>
       <c r="H12">
-        <v>76.21181992540581</v>
+        <v>72.46262513925232</v>
       </c>
       <c r="I12">
-        <v>79.49477070272776</v>
+        <v>83.24396548888124</v>
       </c>
       <c r="J12">
         <v>11493.5652967157</v>
       </c>
       <c r="K12">
-        <v>-8170.520356581093</v>
+        <v>-7768.576506519023</v>
       </c>
       <c r="L12">
-        <v>0.07967569657313057</v>
+        <v>0.008388476652801321</v>
       </c>
       <c r="M12">
-        <v>163.5</v>
+        <v>167.44</v>
       </c>
       <c r="N12">
-        <v>81.81717124453857</v>
+        <v>26.06825718839467</v>
       </c>
       <c r="O12">
-        <v>75.88328400578695</v>
+        <v>72.4624682742233</v>
       </c>
       <c r="P12">
-        <v>79.82330662234662</v>
+        <v>83.24380863069858</v>
       </c>
       <c r="Q12">
-        <v>-8135.298662338109</v>
+        <v>-7768.559689325652</v>
       </c>
       <c r="R12">
-        <v>0.002140642896065892</v>
+        <v>0.008359767154075194</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -1126,37 +1126,37 @@
         <v>144.9756332788713</v>
       </c>
       <c r="H13">
-        <v>82.4560589402132</v>
+        <v>78.69624158831694</v>
       </c>
       <c r="I13">
-        <v>85.70851931738197</v>
+        <v>89.46833666927823</v>
       </c>
       <c r="J13">
         <v>9201.219863575725</v>
       </c>
       <c r="K13">
-        <v>-7909.43165399569</v>
+        <v>-7548.778734628141</v>
       </c>
       <c r="L13">
-        <v>0.1296496440619567</v>
+        <v>0.0159389135817621</v>
       </c>
       <c r="M13">
-        <v>58.86</v>
+        <v>62.8</v>
       </c>
       <c r="N13">
-        <v>133.8915722205397</v>
+        <v>58.23713020895935</v>
       </c>
       <c r="O13">
-        <v>82.1305742974283</v>
+        <v>78.6961000234205</v>
       </c>
       <c r="P13">
-        <v>86.03400396016687</v>
+        <v>89.46819511122227</v>
       </c>
       <c r="Q13">
-        <v>-7878.210194110019</v>
+        <v>-7548.765155300104</v>
       </c>
       <c r="R13">
-        <v>0.001196073854871941</v>
+        <v>0.01590318865301467</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -1182,37 +1182,37 @@
         <v>156.2606908358061</v>
       </c>
       <c r="H14">
-        <v>88.68643578683758</v>
+        <v>84.92565282582993</v>
       </c>
       <c r="I14">
-        <v>91.93613010021919</v>
+        <v>95.69691306122684</v>
       </c>
       <c r="J14">
         <v>7163.579478562413</v>
       </c>
       <c r="K14">
-        <v>-7506.236492803998</v>
+        <v>-7187.931601498165</v>
       </c>
       <c r="L14">
-        <v>0.1797818354534798</v>
+        <v>0.02455645125316587</v>
       </c>
       <c r="M14">
-        <v>50.73</v>
+        <v>54.66999999999999</v>
       </c>
       <c r="N14">
-        <v>24.63731999284618</v>
+        <v>1.048036008883847</v>
       </c>
       <c r="O14">
-        <v>88.36122795335372</v>
+        <v>84.92552656106342</v>
       </c>
       <c r="P14">
-        <v>92.26133793370305</v>
+        <v>95.69678680330027</v>
       </c>
       <c r="Q14">
-        <v>-7478.711574412762</v>
+        <v>-7187.920914709484</v>
       </c>
       <c r="R14">
-        <v>0.009761251864225528</v>
+        <v>0.02451689456013674</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -1238,37 +1238,37 @@
         <v>167.545748392741</v>
       </c>
       <c r="H15">
-        <v>94.90291533798306</v>
+        <v>91.15085787468156</v>
       </c>
       <c r="I15">
-        <v>98.1776381785353</v>
+        <v>101.9296956418368</v>
       </c>
       <c r="J15">
         <v>5380.644141675764</v>
       </c>
       <c r="K15">
-        <v>-6961.401602415333</v>
+        <v>-6686.177403618485</v>
       </c>
       <c r="L15">
-        <v>0.2247210548086066</v>
+        <v>0.03347229941010008</v>
       </c>
       <c r="M15">
-        <v>8.920000000000002</v>
+        <v>12.86</v>
       </c>
       <c r="N15">
-        <v>23.43111049144251</v>
+        <v>0.8110858211229168</v>
       </c>
       <c r="O15">
-        <v>94.57520281565418</v>
+        <v>91.15074691004229</v>
       </c>
       <c r="P15">
-        <v>98.50535070086418</v>
+        <v>101.9295846840423</v>
       </c>
       <c r="Q15">
-        <v>-6937.36294701737</v>
+        <v>-6686.169264043269</v>
       </c>
       <c r="R15">
-        <v>0.02141393265175408</v>
+        <v>0.03343170879317794</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -1294,37 +1294,37 @@
         <v>178.8308059496758</v>
       </c>
       <c r="H16">
-        <v>101.1058112136215</v>
+        <v>97.37186559260125</v>
       </c>
       <c r="I16">
-        <v>104.4327299323584</v>
+        <v>108.1666755533787</v>
       </c>
       <c r="J16">
         <v>3852.413852915781</v>
       </c>
       <c r="K16">
-        <v>-6275.416943874675</v>
+        <v>-6043.659092012444</v>
       </c>
       <c r="L16">
-        <v>0.2606148350165677</v>
+        <v>0.0420276306215713</v>
       </c>
       <c r="M16">
-        <v>41.13</v>
+        <v>45.07</v>
       </c>
       <c r="N16">
-        <v>3.959818347247407</v>
+        <v>35.1629205095526</v>
       </c>
       <c r="O16">
-        <v>100.7728752743111</v>
+        <v>97.37176992808656</v>
       </c>
       <c r="P16">
-        <v>104.7656658716688</v>
+        <v>108.1665798957189</v>
       </c>
       <c r="Q16">
-        <v>-6254.75233706628</v>
+        <v>-6043.653154324894</v>
       </c>
       <c r="R16">
-        <v>0.03153059043971856</v>
+        <v>0.04198841609467178</v>
       </c>
     </row>
     <row r="17" spans="1:18">
@@ -1350,37 +1350,37 @@
         <v>190.1158635066107</v>
       </c>
       <c r="H17">
-        <v>107.2957479732355</v>
+        <v>103.5886945689971</v>
       </c>
       <c r="I17">
-        <v>110.7007808022061</v>
+        <v>114.4078342064445</v>
       </c>
       <c r="J17">
         <v>2578.888612282462</v>
       </c>
       <c r="K17">
-        <v>-5448.774111715502</v>
+        <v>-5260.519712064926</v>
       </c>
       <c r="L17">
-        <v>0.2851585008045973</v>
+        <v>0.04967537239241795</v>
       </c>
       <c r="M17">
-        <v>201.050003051758</v>
+        <v>204.990003051758</v>
       </c>
       <c r="N17">
-        <v>608.5371501485484</v>
+        <v>818.4241021391014</v>
       </c>
       <c r="O17">
-        <v>106.9549948923407</v>
+        <v>103.5886142046043</v>
       </c>
       <c r="P17">
-        <v>111.0415338831008</v>
+        <v>114.4077538489221</v>
       </c>
       <c r="Q17">
-        <v>-5431.469730127802</v>
+        <v>-5260.515630939335</v>
       </c>
       <c r="R17">
-        <v>0.03734527675238551</v>
+        <v>0.04963955566312393</v>
       </c>
     </row>
     <row r="18" spans="1:18">
@@ -1406,37 +1406,37 @@
         <v>201.4009210635455</v>
       </c>
       <c r="H18">
-        <v>113.4735912658377</v>
+        <v>109.8013729100198</v>
       </c>
       <c r="I18">
-        <v>116.9809251390655</v>
+        <v>120.6531434948833</v>
       </c>
       <c r="J18">
         <v>1560.068419775808</v>
       </c>
       <c r="K18">
-        <v>-4481.946030194753</v>
+        <v>-4336.901845920123</v>
       </c>
       <c r="L18">
-        <v>0.2974684961560704</v>
+        <v>0.05598069623610943</v>
       </c>
       <c r="M18">
-        <v>43.990001678467</v>
+        <v>47.930001678467</v>
       </c>
       <c r="N18">
-        <v>18.03281333628908</v>
+        <v>0.09401858233828998</v>
       </c>
       <c r="O18">
-        <v>113.1226005755687</v>
+        <v>109.8013078457464</v>
       </c>
       <c r="P18">
-        <v>117.3319158293344</v>
+        <v>120.6530784375009</v>
       </c>
       <c r="Q18">
-        <v>-4468.082704699036</v>
+        <v>-4336.899276030875</v>
       </c>
       <c r="R18">
-        <v>0.03779759473194401</v>
+        <v>0.05594991174280269</v>
       </c>
     </row>
     <row r="19" spans="1:18">
@@ -1462,37 +1462,37 @@
         <v>212.6859786204804</v>
       </c>
       <c r="H19">
-        <v>119.6403627614145</v>
+        <v>116.0099379176039</v>
       </c>
       <c r="I19">
-        <v>123.2721412729502</v>
+        <v>126.9025661167609</v>
       </c>
       <c r="J19">
         <v>795.9532753958177</v>
       </c>
       <c r="K19">
-        <v>-3375.370949737799</v>
+        <v>-3272.947066441477</v>
       </c>
       <c r="L19">
-        <v>0.2978313969722741</v>
+        <v>0.06062022219138373</v>
       </c>
       <c r="M19">
-        <v>19.079999923706</v>
+        <v>23.019999923706</v>
       </c>
       <c r="N19">
-        <v>17.19616860493785</v>
+        <v>0.04280073323022309</v>
       </c>
       <c r="O19">
-        <v>119.2769184778811</v>
+        <v>116.0098881534471</v>
       </c>
       <c r="P19">
-        <v>123.6355855564837</v>
+        <v>126.9025163595211</v>
       </c>
       <c r="Q19">
-        <v>-3365.117225591765</v>
+        <v>-3272.945662463042</v>
       </c>
       <c r="R19">
-        <v>0.03323147750718273</v>
+        <v>0.06059571962832663</v>
       </c>
     </row>
     <row r="20" spans="1:18">
@@ -1518,37 +1518,37 @@
         <v>223.9710361774152</v>
       </c>
       <c r="H20">
-        <v>125.7971567621093</v>
+        <v>122.2144356709254</v>
       </c>
       <c r="I20">
-        <v>129.573334901717</v>
+        <v>133.156055992901</v>
       </c>
       <c r="J20">
         <v>286.5431791424922</v>
       </c>
       <c r="K20">
-        <v>-2129.442231838719</v>
+        <v>-2068.795411252037</v>
       </c>
       <c r="L20">
-        <v>0.287397210263021</v>
+        <v>0.06337999080047554</v>
       </c>
       <c r="M20">
-        <v>31.830001831055</v>
+        <v>35.770001831055</v>
       </c>
       <c r="N20">
-        <v>17.8936355442914</v>
+        <v>0.08420183032746099</v>
       </c>
       <c r="O20">
-        <v>125.4192619224088</v>
+        <v>122.2144012068827</v>
       </c>
       <c r="P20">
-        <v>129.9512297414175</v>
+        <v>133.1560215358064</v>
       </c>
       <c r="Q20">
-        <v>-2123.045384313986</v>
+        <v>-2068.794827858979</v>
       </c>
       <c r="R20">
-        <v>0.02502710222213793</v>
+        <v>0.06336263907876868</v>
       </c>
     </row>
     <row r="21" spans="1:18">
@@ -1574,37 +1574,37 @@
         <v>235.2560937343501</v>
       </c>
       <c r="H21">
-        <v>131.9450704402343</v>
+        <v>128.4149205210134</v>
       </c>
       <c r="I21">
-        <v>135.8834088530537</v>
+        <v>139.4135587722746</v>
       </c>
       <c r="J21">
         <v>31.8381310158313</v>
       </c>
       <c r="K21">
-        <v>-744.5038571359127</v>
+        <v>-724.5848846244047</v>
       </c>
       <c r="L21">
-        <v>0.2678778494988603</v>
+        <v>0.06415228502825564</v>
       </c>
       <c r="M21">
-        <v>131.483856201172</v>
+        <v>135.423856201172</v>
       </c>
       <c r="N21">
-        <v>47.41257754745181</v>
+        <v>8.679028170216601</v>
       </c>
       <c r="O21">
-        <v>131.5509476769069</v>
+        <v>128.4149013570822</v>
       </c>
       <c r="P21">
-        <v>136.277531616381</v>
+        <v>139.4135396153278</v>
       </c>
       <c r="Q21">
-        <v>-742.2800081015889</v>
+        <v>-724.5847764913717</v>
       </c>
       <c r="R21">
-        <v>0.01523901621823073</v>
+        <v>0.06414257759904375</v>
       </c>
     </row>
     <row r="22" spans="1:18">
@@ -1630,37 +1630,37 @@
         <v>246.5411512912849</v>
       </c>
       <c r="H22">
-        <v>138.0851530758964</v>
+        <v>134.61145451106</v>
       </c>
       <c r="I22">
-        <v>142.2013138468531</v>
+        <v>145.6750124116895</v>
       </c>
       <c r="J22">
         <v>31.83813101583483</v>
       </c>
       <c r="K22">
-        <v>779.1494501098464</v>
+        <v>759.5490059900357</v>
       </c>
       <c r="L22">
-        <v>0.2412901136815812</v>
+        <v>0.06293141069874647</v>
       </c>
       <c r="M22">
-        <v>242.057250976563</v>
+        <v>245.997250976563</v>
       </c>
       <c r="N22">
-        <v>153.1784167995084</v>
+        <v>71.18553061184967</v>
       </c>
       <c r="O22">
-        <v>137.673235031457</v>
+        <v>134.6114506472379</v>
       </c>
       <c r="P22">
-        <v>142.6132318912925</v>
+        <v>145.675008554893</v>
       </c>
       <c r="Q22">
-        <v>776.8251906897268</v>
+        <v>759.5489841883083</v>
       </c>
       <c r="R22">
-        <v>0.006287674207990829</v>
+        <v>0.06292947214652157</v>
       </c>
     </row>
     <row r="23" spans="1:18">
@@ -1686,37 +1686,37 @@
         <v>257.8262088482197</v>
       </c>
       <c r="H23">
-        <v>144.2183742485364</v>
+        <v>140.8041067362444</v>
       </c>
       <c r="I23">
-        <v>148.5260803036747</v>
+        <v>151.9403478159667</v>
       </c>
       <c r="J23">
         <v>286.5431791425019</v>
       </c>
       <c r="K23">
-        <v>2441.268981243473</v>
+        <v>2383.473673156991</v>
       </c>
       <c r="L23">
-        <v>0.2097595706792486</v>
+        <v>0.0598085648013368</v>
       </c>
       <c r="M23">
-        <v>36.909999847412</v>
+        <v>40.849999847412</v>
       </c>
       <c r="N23">
-        <v>26.57920398623899</v>
+        <v>1.477697039238471</v>
       </c>
       <c r="O23">
-        <v>143.7872876236473</v>
+        <v>140.8041181725289</v>
       </c>
       <c r="P23">
-        <v>148.9571669285638</v>
+        <v>151.9403592593229</v>
       </c>
       <c r="Q23">
-        <v>2433.971725182626</v>
+        <v>2383.473866745684</v>
       </c>
       <c r="R23">
-        <v>0.0007240695024572424</v>
+        <v>0.05981415859947429</v>
       </c>
     </row>
     <row r="24" spans="1:18">
@@ -1742,37 +1742,37 @@
         <v>269.1112664051545</v>
       </c>
       <c r="H24">
-        <v>150.3456077956754</v>
+        <v>146.9929526575888</v>
       </c>
       <c r="I24">
-        <v>154.8568343859972</v>
+        <v>158.2094895240839</v>
       </c>
       <c r="J24">
         <v>795.9532753958322</v>
       </c>
       <c r="K24">
-        <v>4241.647093516389</v>
+        <v>4147.059828011735</v>
       </c>
       <c r="L24">
-        <v>0.1753848989937095</v>
+        <v>0.05496593588997659</v>
       </c>
       <c r="M24">
-        <v>10.590000152588</v>
+        <v>14.530000152588</v>
       </c>
       <c r="N24">
-        <v>21.51850987845511</v>
+        <v>0.4883804149310934</v>
       </c>
       <c r="O24">
-        <v>149.8941541867153</v>
+        <v>146.9929793939774</v>
       </c>
       <c r="P24">
-        <v>155.3082879949573</v>
+        <v>158.2095162675952</v>
       </c>
       <c r="Q24">
-        <v>4228.910393612887</v>
+        <v>4147.060582315947</v>
       </c>
       <c r="R24">
-        <v>0.001066924227839477</v>
+        <v>0.05497847319861389</v>
       </c>
     </row>
     <row r="25" spans="1:18">
@@ -1798,37 +1798,37 @@
         <v>280.3963239620894</v>
       </c>
       <c r="H25">
-        <v>156.4676272792761</v>
+        <v>153.1780733845188</v>
       </c>
       <c r="I25">
-        <v>161.1928025318582</v>
+        <v>164.4823564266154</v>
       </c>
       <c r="J25">
         <v>1560.068419775826</v>
       </c>
       <c r="K25">
-        <v>6180.111628752818</v>
+        <v>6050.181811116407</v>
       </c>
       <c r="L25">
-        <v>0.1401531797321536</v>
+        <v>0.04867018957082105</v>
       </c>
       <c r="M25">
-        <v>123.449996948242</v>
+        <v>127.389996948242</v>
       </c>
       <c r="N25">
-        <v>107.6346276646026</v>
+        <v>41.40973566020971</v>
       </c>
       <c r="O25">
-        <v>155.9947631085151</v>
+        <v>153.1781154210093</v>
       </c>
       <c r="P25">
-        <v>161.6656667026191</v>
+        <v>164.4823984702843</v>
       </c>
       <c r="Q25">
-        <v>6161.434580910044</v>
+        <v>6050.183471461156</v>
       </c>
       <c r="R25">
-        <v>0.009701027262872666</v>
+        <v>0.04868873894829245</v>
       </c>
     </row>
     <row r="26" spans="1:18">
@@ -1854,37 +1854,37 @@
         <v>291.6813815190242</v>
       </c>
       <c r="H26">
-        <v>162.5851089389309</v>
+        <v>159.359554940443</v>
       </c>
       <c r="I26">
-        <v>167.5333085016649</v>
+        <v>170.7588625001528</v>
       </c>
       <c r="J26">
         <v>2578.888612282482</v>
       </c>
       <c r="K26">
-        <v>8256.520405243615</v>
+        <v>8092.717873876894</v>
       </c>
       <c r="L26">
-        <v>0.1058937043076859</v>
+        <v>0.04126549490965226</v>
       </c>
       <c r="M26">
-        <v>10.979999542236</v>
+        <v>14.919999542236</v>
       </c>
       <c r="N26">
-        <v>31.00272704871483</v>
+        <v>2.650546477312232</v>
       </c>
       <c r="O26">
-        <v>162.0899259757777</v>
+        <v>159.3596122770329</v>
       </c>
       <c r="P26">
-        <v>168.0284914648181</v>
+        <v>170.7589198439815</v>
       </c>
       <c r="Q26">
-        <v>8231.373648161825</v>
+        <v>8092.720785587121</v>
       </c>
       <c r="R26">
-        <v>0.02882179670208083</v>
+        <v>0.04128879280394272</v>
       </c>
     </row>
     <row r="27" spans="1:18">
@@ -1910,37 +1910,37 @@
         <v>302.966439075959</v>
       </c>
       <c r="H27">
-        <v>168.6986389335552</v>
+        <v>165.5374875248642</v>
       </c>
       <c r="I27">
-        <v>173.8777661365021</v>
+        <v>177.0389175451931</v>
       </c>
       <c r="J27">
         <v>3852.413852915803</v>
       </c>
       <c r="K27">
-        <v>10470.75617577957</v>
+        <v>10274.55041001663</v>
       </c>
       <c r="L27">
-        <v>0.0742585469507482</v>
+        <v>0.03316624497142829</v>
       </c>
       <c r="M27">
-        <v>35.64</v>
+        <v>39.58</v>
       </c>
       <c r="N27">
-        <v>3.259931890447133</v>
+        <v>4.555577455953099</v>
       </c>
       <c r="O27">
-        <v>168.1803462652042</v>
+        <v>165.5375601615514</v>
       </c>
       <c r="P27">
-        <v>174.3960588048532</v>
+        <v>177.0389901891839</v>
       </c>
       <c r="Q27">
-        <v>10438.58688151434</v>
+        <v>10274.5549184172</v>
       </c>
       <c r="R27">
-        <v>0.06041196401897916</v>
+        <v>0.03319270685633794</v>
       </c>
     </row>
     <row r="28" spans="1:18">
@@ -1966,37 +1966,37 @@
         <v>314.2514966328938</v>
       </c>
       <c r="H28">
-        <v>174.8087226013817</v>
+        <v>171.7119647843776</v>
       </c>
       <c r="I28">
-        <v>180.2256700981373</v>
+        <v>183.3224279151414</v>
       </c>
       <c r="J28">
         <v>5380.644141675785</v>
       </c>
       <c r="K28">
-        <v>12822.72222407052</v>
+        <v>12595.56613773945</v>
       </c>
       <c r="L28">
-        <v>0.04672037880942322</v>
+        <v>0.0248496173458238</v>
       </c>
       <c r="M28">
-        <v>11.78</v>
+        <v>15.72</v>
       </c>
       <c r="N28">
-        <v>33.57820099107776</v>
+        <v>3.439961122799935</v>
       </c>
       <c r="O28">
-        <v>174.2666304568185</v>
+        <v>171.7120527211598</v>
       </c>
       <c r="P28">
-        <v>180.7677622427004</v>
+        <v>183.3225158592964</v>
       </c>
       <c r="Q28">
-        <v>12782.95820722889</v>
+        <v>12595.57258815517</v>
       </c>
       <c r="R28">
-        <v>0.106238950665715</v>
+        <v>0.02487734936774722</v>
       </c>
     </row>
     <row r="29" spans="1:18">
@@ -2022,37 +2022,37 @@
         <v>325.5365541898286</v>
       </c>
       <c r="H29">
-        <v>180.9157942687035</v>
+        <v>177.8830831034738</v>
       </c>
       <c r="I29">
-        <v>186.576586060277</v>
+        <v>189.6092972255067</v>
       </c>
       <c r="J29">
         <v>7163.579478562432</v>
       </c>
       <c r="K29">
-        <v>15312.33863460676</v>
+        <v>15055.65623420794</v>
       </c>
       <c r="L29">
-        <v>0.02458051156323227</v>
+        <v>0.01684810929715163</v>
       </c>
       <c r="M29">
-        <v>19.63</v>
+        <v>23.57</v>
       </c>
       <c r="N29">
-        <v>4.649146821735417</v>
+        <v>3.181794232444192</v>
       </c>
       <c r="O29">
-        <v>180.3492998058981</v>
+        <v>177.8831863403489</v>
       </c>
       <c r="P29">
-        <v>187.1430805230824</v>
+        <v>189.6094004698281</v>
       </c>
       <c r="Q29">
-        <v>15264.39171496843</v>
+        <v>15055.66497196352</v>
       </c>
       <c r="R29">
-        <v>0.1678645215898153</v>
+        <v>0.0168749203028823</v>
       </c>
     </row>
     <row r="30" spans="1:18">
@@ -2078,37 +2078,37 @@
         <v>336.8216117467634</v>
       </c>
       <c r="H30">
-        <v>187.0202267392967</v>
+        <v>184.0509409244641</v>
       </c>
       <c r="I30">
-        <v>192.9301412191454</v>
+        <v>195.899427033978</v>
       </c>
       <c r="J30">
         <v>9201.219863575741</v>
       </c>
       <c r="K30">
-        <v>17939.53919604372</v>
+        <v>17654.71642479502</v>
       </c>
       <c r="L30">
-        <v>0.008982356371106412</v>
+        <v>0.009742168064365382</v>
       </c>
       <c r="M30">
-        <v>17.38</v>
+        <v>21.32</v>
       </c>
       <c r="N30">
-        <v>7.90171931155601</v>
+        <v>1.274529695798266</v>
       </c>
       <c r="O30">
-        <v>186.428801731673</v>
+        <v>184.05105946143</v>
       </c>
       <c r="P30">
-        <v>193.521566226769</v>
+        <v>195.8995455784679</v>
       </c>
       <c r="Q30">
-        <v>17882.80794140475</v>
+        <v>17654.72779521513</v>
       </c>
       <c r="R30">
-        <v>0.2466609379464854</v>
+        <v>0.00976558188658334</v>
       </c>
     </row>
     <row r="31" spans="1:18">
@@ -2134,37 +2134,37 @@
         <v>348.1066693036983</v>
       </c>
       <c r="H31">
-        <v>193.1223400087439</v>
+        <v>190.2156381041452</v>
       </c>
       <c r="I31">
-        <v>199.2860155791597</v>
+        <v>202.1927174837585</v>
       </c>
       <c r="J31">
         <v>11493.56529671571</v>
       </c>
       <c r="K31">
-        <v>20704.26886402184</v>
+        <v>20392.64703022647</v>
       </c>
       <c r="L31">
-        <v>0.0009271814780645421</v>
+        <v>0.004153020797467776</v>
       </c>
       <c r="M31">
-        <v>36.76</v>
+        <v>40.7</v>
       </c>
       <c r="N31">
-        <v>85.29477078004213</v>
+        <v>28.04369486682699</v>
       </c>
       <c r="O31">
-        <v>192.505520275793</v>
+        <v>190.2157719411999</v>
       </c>
       <c r="P31">
-        <v>199.9028353121107</v>
+        <v>202.1928513284189</v>
       </c>
       <c r="Q31">
-        <v>20638.14082523009</v>
+        <v>20392.66137863569</v>
       </c>
       <c r="R31">
-        <v>0.3438298685387012</v>
+        <v>0.004170288682814313</v>
       </c>
     </row>
     <row r="32" spans="1:18">
@@ -2190,37 +2190,37 @@
         <v>359.3917268606331</v>
       </c>
       <c r="H32">
-        <v>199.2224090107087</v>
+        <v>196.3772753131205</v>
       </c>
       <c r="I32">
-        <v>205.6439342066566</v>
+        <v>208.4890679042447</v>
       </c>
       <c r="J32">
         <v>14040.61577798235</v>
       </c>
       <c r="K32">
-        <v>23606.48169932913</v>
+        <v>23269.35297521733</v>
       </c>
       <c r="L32">
-        <v>0.00129026450076935</v>
+        <v>0.0007357915636016385</v>
       </c>
       <c r="M32">
-        <v>210.779998779297</v>
+        <v>214.719998779297</v>
       </c>
       <c r="N32">
-        <v>0.5068272513700383</v>
+        <v>21.63554078553236</v>
       </c>
       <c r="O32">
-        <v>198.5797853989933</v>
+        <v>196.3774244502621</v>
       </c>
       <c r="P32">
-        <v>206.2865578183719</v>
+        <v>208.4892170490775</v>
       </c>
       <c r="Q32">
-        <v>23530.33523264977</v>
+        <v>23269.37064694021</v>
       </c>
       <c r="R32">
-        <v>0.4604217749295739</v>
+        <v>0.0007439046380328445</v>
       </c>
     </row>
     <row r="33" spans="1:18">
@@ -2246,37 +2246,37 @@
         <v>370.6767844175679</v>
       </c>
       <c r="H33">
-        <v>205.3206703585628</v>
+        <v>202.5359534820523</v>
       </c>
       <c r="I33">
-        <v>212.003660488264</v>
+        <v>214.7883773647745</v>
       </c>
       <c r="J33">
         <v>16842.37130737565</v>
       </c>
       <c r="K33">
-        <v>26646.13920018548</v>
+        <v>26284.74376252681</v>
       </c>
       <c r="L33">
-        <v>0.0108363546376743</v>
+        <v>0.0001729756062536362</v>
       </c>
       <c r="M33">
-        <v>134.300003051758</v>
+        <v>138.240003051758</v>
       </c>
       <c r="N33">
-        <v>225.2225594880809</v>
+        <v>122.4958328476762</v>
       </c>
       <c r="O33">
-        <v>204.6518810720368</v>
+        <v>202.5361179192789</v>
       </c>
       <c r="P33">
-        <v>212.67244977479</v>
+        <v>214.7885418097816</v>
       </c>
       <c r="Q33">
-        <v>26559.34495587854</v>
+        <v>26284.76510288782</v>
       </c>
       <c r="R33">
-        <v>0.5973544683634713</v>
+        <v>0.0001686772827677555</v>
       </c>
     </row>
     <row r="34" spans="1:18">
@@ -2302,37 +2302,37 @@
         <v>381.9618419745027</v>
       </c>
       <c r="H34">
-        <v>211.4173281314331</v>
+        <v>208.6917732975846</v>
       </c>
       <c r="I34">
-        <v>218.3649903448552</v>
+        <v>221.0905451787038</v>
       </c>
       <c r="J34">
         <v>19898.83188489561</v>
       </c>
       <c r="K34">
-        <v>29823.2089562075</v>
+        <v>29438.73341652547</v>
       </c>
       <c r="L34">
-        <v>0.03023388880148443</v>
+        <v>0.003168324276997596</v>
       </c>
       <c r="M34">
-        <v>165.740005493164</v>
+        <v>169.680005493164</v>
       </c>
       <c r="N34">
-        <v>25.61433402967278</v>
+        <v>1.25771761094449</v>
       </c>
       <c r="O34">
-        <v>210.7220522198187</v>
+        <v>208.6919530348944</v>
       </c>
       <c r="P34">
-        <v>219.0602662564697</v>
+        <v>221.090724923887</v>
       </c>
       <c r="Q34">
-        <v>29725.13109770101</v>
+        <v>29438.75877084904</v>
       </c>
       <c r="R34">
-        <v>0.7554301712105329</v>
+        <v>0.003148122521948395</v>
       </c>
     </row>
     <row r="35" spans="1:18">
@@ -2358,37 +2358,37 @@
         <v>393.2468995314375</v>
       </c>
       <c r="H35">
-        <v>217.5125587950426</v>
+        <v>214.8448347492987</v>
       </c>
       <c r="I35">
-        <v>224.7277473107073</v>
+        <v>227.3954713564512</v>
       </c>
       <c r="J35">
         <v>23209.99751054224</v>
       </c>
       <c r="K35">
-        <v>33137.66356233606</v>
+        <v>32731.24040040583</v>
       </c>
       <c r="L35">
-        <v>0.06006773257725708</v>
+        <v>0.01044117832187113</v>
       </c>
       <c r="M35">
-        <v>56.23000335693401</v>
+        <v>60.170003356934</v>
       </c>
       <c r="N35">
-        <v>20.27760222622262</v>
+        <v>0.3172111889711278</v>
       </c>
       <c r="O35">
-        <v>216.7905106270981</v>
+        <v>214.8450297866899</v>
       </c>
       <c r="P35">
-        <v>225.4497954786518</v>
+        <v>227.3956664018123</v>
       </c>
       <c r="Q35">
-        <v>33027.66076802526</v>
+        <v>32731.27011401634</v>
       </c>
       <c r="R35">
-        <v>0.9353508079859983</v>
+        <v>0.01040135770720935</v>
       </c>
     </row>
     <row r="36" spans="1:18">
@@ -2414,37 +2414,37 @@
         <v>404.5319570883723</v>
       </c>
       <c r="H36">
-        <v>223.6065153626354</v>
+        <v>220.9952367278531</v>
       </c>
       <c r="I36">
-        <v>231.091778372576</v>
+        <v>233.7030570073583</v>
       </c>
       <c r="J36">
         <v>26775.86818431553</v>
       </c>
       <c r="K36">
-        <v>36589.4797416081</v>
+        <v>36162.18751109277</v>
       </c>
       <c r="L36">
-        <v>0.1008504095386824</v>
+        <v>0.02272127288545152</v>
       </c>
       <c r="M36">
-        <v>220.229995727539</v>
+        <v>224.169995727539</v>
       </c>
       <c r="N36">
-        <v>44.89973051035379</v>
+        <v>7.624686692667408</v>
       </c>
       <c r="O36">
-        <v>222.8574399322185</v>
+        <v>220.9954470653241</v>
       </c>
       <c r="P36">
-        <v>231.8408538029929</v>
+        <v>233.703267352899</v>
       </c>
       <c r="Q36">
-        <v>36466.90603108037</v>
+        <v>36162.22192931454</v>
       </c>
       <c r="R36">
-        <v>1.137731482177156</v>
+        <v>0.02265790636526348</v>
       </c>
     </row>
     <row r="37" spans="1:18">
@@ -2470,37 +2470,37 @@
         <v>415.8170146453072</v>
       </c>
       <c r="H37">
-        <v>229.6993309014234</v>
+        <v>227.1430766734426</v>
       </c>
       <c r="I37">
-        <v>237.4569504632496</v>
+        <v>240.0132046912304</v>
       </c>
       <c r="J37">
         <v>30596.44390621548</v>
       </c>
       <c r="K37">
-        <v>40178.63763518572</v>
+        <v>39731.50175574544</v>
       </c>
       <c r="L37">
-        <v>0.1530318888533582</v>
+        <v>0.04074402494955186</v>
       </c>
       <c r="M37">
-        <v>169.600006103516</v>
+        <v>173.540006103516</v>
       </c>
       <c r="N37">
-        <v>44.87203655611126</v>
+        <v>7.612590587965868</v>
       </c>
       <c r="O37">
-        <v>228.9229998353583</v>
+        <v>227.1433023109917</v>
       </c>
       <c r="P37">
-        <v>238.2332815293148</v>
+        <v>240.0134303369522</v>
       </c>
       <c r="Q37">
-        <v>40042.8430533471</v>
+        <v>39731.54122390273</v>
       </c>
       <c r="R37">
-        <v>1.363112222805872</v>
+        <v>0.04065298530984798</v>
       </c>
     </row>
     <row r="38" spans="1:18">
@@ -2526,37 +2526,37 @@
         <v>427.102072202242</v>
       </c>
       <c r="H38">
-        <v>235.7911214825619</v>
+        <v>233.2884502728751</v>
       </c>
       <c r="I38">
-        <v>243.8231475115727</v>
+        <v>246.3258187212595</v>
       </c>
       <c r="J38">
         <v>34671.7246762421</v>
       </c>
       <c r="K38">
-        <v>43905.12022619123</v>
+        <v>43439.11421350915</v>
       </c>
       <c r="L38">
-        <v>0.2170080539036305</v>
+        <v>0.06524630308105343</v>
       </c>
       <c r="M38">
-        <v>172.139999389648</v>
+        <v>176.079999389648</v>
       </c>
       <c r="N38">
-        <v>1.575839156800939</v>
+        <v>7.205196826829299</v>
       </c>
       <c r="O38">
-        <v>234.9873296389338</v>
+        <v>233.2886912105008</v>
       </c>
       <c r="P38">
-        <v>244.6269393552008</v>
+        <v>246.3260596671641</v>
       </c>
       <c r="Q38">
-        <v>43755.45141207546</v>
+        <v>43439.1590769262</v>
       </c>
       <c r="R38">
-        <v>1.61196814801608</v>
+        <v>0.06512327402154366</v>
       </c>
     </row>
     <row r="39" spans="1:18">
@@ -2582,37 +2582,37 @@
         <v>438.3871297591768</v>
       </c>
       <c r="H39">
-        <v>241.881988661942</v>
+        <v>239.4314512029183</v>
       </c>
       <c r="I39">
-        <v>250.1902679616542</v>
+        <v>252.6408054206779</v>
       </c>
       <c r="J39">
         <v>39001.71049439537</v>
       </c>
       <c r="K39">
-        <v>47768.91287062776</v>
+        <v>47284.95988589388</v>
       </c>
       <c r="L39">
-        <v>0.2931279952705457</v>
+        <v>0.0969626703527305</v>
       </c>
       <c r="M39">
-        <v>5.340000152588001</v>
+        <v>9.280000152588002</v>
       </c>
       <c r="N39">
-        <v>37.98280192078255</v>
+        <v>4.941938636762619</v>
       </c>
       <c r="O39">
-        <v>241.0505512249153</v>
+        <v>239.431707440619</v>
       </c>
       <c r="P39">
-        <v>251.0217053986809</v>
+        <v>252.6410616667668</v>
       </c>
       <c r="Q39">
-        <v>47604.71353232062</v>
+        <v>47285.0104898949</v>
       </c>
       <c r="R39">
-        <v>1.884718217724613</v>
+        <v>0.09680315716893774</v>
       </c>
     </row>
     <row r="40" spans="1:18">
@@ -2638,37 +2638,37 @@
         <v>449.6721873161116</v>
       </c>
       <c r="H40">
-        <v>247.9720215674928</v>
+        <v>245.572170917081</v>
       </c>
       <c r="I40">
-        <v>256.5582226855649</v>
+        <v>258.9580733359768</v>
       </c>
       <c r="J40">
         <v>43586.40136067531</v>
       </c>
       <c r="K40">
-        <v>51770.00291412485</v>
+        <v>51268.97753884286</v>
       </c>
       <c r="L40">
-        <v>0.3817002735670845</v>
+        <v>0.1366220840693752</v>
       </c>
       <c r="M40">
-        <v>34.729999542236</v>
+        <v>38.669999542236</v>
       </c>
       <c r="N40">
-        <v>16.27908368175363</v>
+        <v>0.00899270332286399</v>
       </c>
       <c r="O40">
-        <v>247.1127715598946</v>
+        <v>245.5724424548552</v>
       </c>
       <c r="P40">
-        <v>257.4174726931631</v>
+        <v>258.9583448822514</v>
       </c>
       <c r="Q40">
-        <v>51590.61422698132</v>
+        <v>51269.03422875197</v>
       </c>
       <c r="R40">
-        <v>2.181732749939935</v>
+        <v>0.136421423911374</v>
       </c>
     </row>
     <row r="41" spans="1:18">
@@ -2694,37 +2694,37 @@
         <v>460.9572448730464</v>
       </c>
       <c r="H41">
-        <v>254.0612986575061</v>
+        <v>251.7106984726677</v>
       </c>
       <c r="I41">
-        <v>262.9269332250132</v>
+        <v>265.2775334098516</v>
       </c>
       <c r="J41">
         <v>48425.79727508192</v>
       </c>
       <c r="K41">
-        <v>55908.37937762152</v>
+        <v>55391.10953922627</v>
       </c>
       <c r="L41">
-        <v>0.4829982898005652</v>
+        <v>0.1849450303632487</v>
       </c>
       <c r="M41">
-        <v>120.470001220703</v>
+        <v>124.410001220703</v>
       </c>
       <c r="N41">
-        <v>12.53663680945795</v>
+        <v>0.1591882746560856</v>
       </c>
       <c r="O41">
-        <v>253.1740848053336</v>
+        <v>251.7109853105141</v>
       </c>
       <c r="P41">
-        <v>263.8141470771858</v>
+        <v>265.2778202563132</v>
       </c>
       <c r="Q41">
-        <v>55713.14031957351</v>
+        <v>55391.1726603676</v>
       </c>
       <c r="R41">
-        <v>2.503339865984894</v>
+        <v>0.1846984020549281</v>
       </c>
     </row>
   </sheetData>

--- a/import/c_phi_data_geforceerd.xlsx
+++ b/import/c_phi_data_geforceerd.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="19">
   <si>
     <t>PV_NAAM</t>
   </si>
@@ -70,7 +70,7 @@
     <t>kappa_2_ondergrens_cor</t>
   </si>
   <si>
-    <t>TXT_SAFE_klei_licht_16_175</t>
+    <t>tussen 16 en 17,5</t>
   </si>
 </sst>
 </file>
@@ -428,7 +428,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R41"/>
+  <dimension ref="A1:R75"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:18">
@@ -492,55 +492,55 @@
         <v>18</v>
       </c>
       <c r="B2">
-        <v>102.98</v>
+        <v>30.45757719153017</v>
       </c>
       <c r="C2">
-        <v>62.56</v>
+        <v>17.23696784559116</v>
       </c>
       <c r="D2">
-        <v>2377.32083625102</v>
+        <v>4215.30105663436</v>
       </c>
       <c r="E2">
-        <v>-3050.286540840457</v>
+        <v>-1119.116168191414</v>
       </c>
       <c r="F2">
-        <v>2.748859081039612</v>
+        <v>0.2256011256281381</v>
       </c>
       <c r="G2">
-        <v>20.840000152588</v>
+        <v>22.08</v>
       </c>
       <c r="H2">
-        <v>9.9020746549891</v>
+        <v>7.270697493878088</v>
       </c>
       <c r="I2">
-        <v>21.22463967852851</v>
+        <v>18.53665855711645</v>
       </c>
       <c r="J2">
-        <v>48425.79727508202</v>
+        <v>23457.98559999996</v>
       </c>
       <c r="K2">
-        <v>-2179.036907085044</v>
+        <v>-1113.580028162367</v>
       </c>
       <c r="L2">
-        <v>0.2298293414006464</v>
+        <v>0.1090974378084473</v>
       </c>
       <c r="M2">
-        <v>58.5</v>
+        <v>12.23696784559116</v>
       </c>
       <c r="N2">
-        <v>2.749517329212706</v>
+        <v>18.79839203259223</v>
       </c>
       <c r="O2">
-        <v>9.901764788491688</v>
+        <v>10.77394176386681</v>
       </c>
       <c r="P2">
-        <v>21.22432981922115</v>
+        <v>23.25454560412721</v>
       </c>
       <c r="Q2">
-        <v>-2178.968718290508</v>
+        <v>-1650.136920553839</v>
       </c>
       <c r="R2">
-        <v>0.2301265406353878</v>
+        <v>10.06758160557948</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -548,55 +548,55 @@
         <v>18</v>
       </c>
       <c r="B3">
-        <v>196.28</v>
+        <v>82.39</v>
       </c>
       <c r="C3">
-        <v>110.19</v>
+        <v>48.29</v>
       </c>
       <c r="D3">
-        <v>1984.009613091984</v>
+        <v>168.8161538048414</v>
       </c>
       <c r="E3">
-        <v>4908.107531726183</v>
+        <v>-627.4284481331846</v>
       </c>
       <c r="F3">
-        <v>4.88707161375546</v>
+        <v>0.5955621919067512</v>
       </c>
       <c r="G3">
-        <v>32.12505770952285</v>
+        <v>26.27616438356164</v>
       </c>
       <c r="H3">
-        <v>16.17567064198671</v>
+        <v>9.692499532043442</v>
       </c>
       <c r="I3">
-        <v>27.40903132099251</v>
+        <v>20.93158779373224</v>
       </c>
       <c r="J3">
-        <v>43586.4013606754</v>
+        <v>22190.22432156123</v>
       </c>
       <c r="K3">
-        <v>-3377.052423011561</v>
+        <v>-1443.831907003724</v>
       </c>
       <c r="L3">
-        <v>0.1638346036939383</v>
+        <v>0.091578074508861</v>
       </c>
       <c r="M3">
-        <v>106.13</v>
+        <v>43.29</v>
       </c>
       <c r="N3">
-        <v>4.886753265765213</v>
+        <v>2.372595681635037</v>
       </c>
       <c r="O3">
-        <v>16.17537607564727</v>
+        <v>13.07205785756846</v>
       </c>
       <c r="P3">
-        <v>27.40873676178646</v>
+        <v>25.52289159758305</v>
       </c>
       <c r="Q3">
-        <v>-3376.990925346805</v>
+        <v>-1947.263877863398</v>
       </c>
       <c r="R3">
-        <v>0.1640731506781457</v>
+        <v>9.467557490451018</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -604,55 +604,55 @@
         <v>18</v>
       </c>
       <c r="B4">
-        <v>94.59</v>
+        <v>104.8941188889608</v>
       </c>
       <c r="C4">
-        <v>58.31</v>
+        <v>50.37884143065421</v>
       </c>
       <c r="D4">
-        <v>3265.868437454711</v>
+        <v>90.4627698474434</v>
       </c>
       <c r="E4">
-        <v>-3332.286887794231</v>
+        <v>479.1628245444109</v>
       </c>
       <c r="F4">
-        <v>4.157448545031228</v>
+        <v>101.1140450975978</v>
       </c>
       <c r="G4">
-        <v>43.41011526645769</v>
+        <v>30.47232876712329</v>
       </c>
       <c r="H4">
-        <v>22.44555813639322</v>
+        <v>12.11353916001163</v>
       </c>
       <c r="I4">
-        <v>33.59713145604758</v>
+        <v>23.32727944054518</v>
       </c>
       <c r="J4">
-        <v>39001.71049439544</v>
+        <v>20957.67863419024</v>
       </c>
       <c r="K4">
-        <v>-4432.739770667679</v>
+        <v>-1753.64885458314</v>
       </c>
       <c r="L4">
-        <v>0.1114445028195387</v>
+        <v>0.07601092411209022</v>
       </c>
       <c r="M4">
-        <v>54.25</v>
+        <v>45.37884143065421</v>
       </c>
       <c r="N4">
-        <v>4.1583044463321</v>
+        <v>136.808076822833</v>
       </c>
       <c r="O4">
-        <v>22.44527887020941</v>
+        <v>15.36932934160201</v>
       </c>
       <c r="P4">
-        <v>33.59685219694523</v>
+        <v>27.79208220070699</v>
       </c>
       <c r="Q4">
-        <v>-4432.684618805913</v>
+        <v>-2224.982017194843</v>
       </c>
       <c r="R4">
-        <v>0.111631037370897</v>
+        <v>8.880932798024118</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -660,55 +660,55 @@
         <v>18</v>
       </c>
       <c r="B5">
-        <v>35.7</v>
+        <v>74.32740099031673</v>
       </c>
       <c r="C5">
-        <v>22.88</v>
+        <v>45.12740099031674</v>
       </c>
       <c r="D5">
-        <v>13464.76573458049</v>
+        <v>443.3351784249741</v>
       </c>
       <c r="E5">
-        <v>-2654.94434204651</v>
+        <v>-950.1811683878738</v>
       </c>
       <c r="F5">
-        <v>0.7842975096314581</v>
+        <v>5.00243516639133</v>
       </c>
       <c r="G5">
-        <v>54.69517282339254</v>
+        <v>34.66849315068493</v>
       </c>
       <c r="H5">
-        <v>28.71165499502634</v>
+        <v>14.53381119663159</v>
       </c>
       <c r="I5">
-        <v>39.78902222687607</v>
+        <v>25.72373867870636</v>
       </c>
       <c r="J5">
-        <v>34671.72467624215</v>
+        <v>19760.348537887</v>
       </c>
       <c r="K5">
-        <v>-5346.209206366509</v>
+        <v>-2043.039740173948</v>
       </c>
       <c r="L5">
-        <v>0.07112454490776596</v>
+        <v>0.06227543758513404</v>
       </c>
       <c r="M5">
-        <v>18.82</v>
+        <v>40.12740099031674</v>
       </c>
       <c r="N5">
-        <v>0.7837844454196563</v>
+        <v>0.0997762725656989</v>
       </c>
       <c r="O5">
-        <v>28.71139102899574</v>
+        <v>17.6657504762091</v>
       </c>
       <c r="P5">
-        <v>39.78875826787981</v>
+        <v>30.06212315325739</v>
       </c>
       <c r="Q5">
-        <v>-5346.160054981011</v>
+        <v>-2483.301164064716</v>
       </c>
       <c r="R5">
-        <v>0.07126540976593447</v>
+        <v>8.308165243711086</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -716,55 +716,55 @@
         <v>18</v>
       </c>
       <c r="B6">
-        <v>90.70999999999999</v>
+        <v>154.929992675781</v>
       </c>
       <c r="C6">
-        <v>53.42</v>
+        <v>78.09999847412099</v>
       </c>
       <c r="D6">
-        <v>3724.389588428528</v>
+        <v>3545.85302244937</v>
       </c>
       <c r="E6">
-        <v>-3260.103857348102</v>
+        <v>4650.625733074598</v>
       </c>
       <c r="F6">
-        <v>0.5032211749185612</v>
+        <v>122.151290680583</v>
       </c>
       <c r="G6">
-        <v>65.98023038032738</v>
+        <v>38.86465753424658</v>
       </c>
       <c r="H6">
-        <v>34.9738845782874</v>
+        <v>16.95331073169653</v>
       </c>
       <c r="I6">
-        <v>45.9847802730766</v>
+        <v>28.12097041842257</v>
       </c>
       <c r="J6">
-        <v>30596.44390621552</v>
+        <v>18598.2340326515</v>
       </c>
       <c r="K6">
-        <v>-6117.575657061318</v>
+        <v>-2312.013556963445</v>
       </c>
       <c r="L6">
-        <v>0.04137885698653937</v>
+        <v>0.05025337983293977</v>
       </c>
       <c r="M6">
-        <v>49.36</v>
+        <v>73.09999847412099</v>
       </c>
       <c r="N6">
-        <v>0.5029159971931801</v>
+        <v>125.4630499873</v>
       </c>
       <c r="O6">
-        <v>34.97363591240757</v>
+        <v>19.96131582178764</v>
       </c>
       <c r="P6">
-        <v>45.98453161418889</v>
+        <v>32.33301989483634</v>
       </c>
       <c r="Q6">
-        <v>-6117.532160825439</v>
+        <v>-2722.231281263349</v>
       </c>
       <c r="R6">
-        <v>0.04148008502168629</v>
+        <v>7.749723019423053</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -772,55 +772,55 @@
         <v>18</v>
       </c>
       <c r="B7">
-        <v>172.76</v>
+        <v>76.1703463274298</v>
       </c>
       <c r="C7">
-        <v>100.26</v>
+        <v>45.37034632742979</v>
       </c>
       <c r="D7">
-        <v>441.9338519848084</v>
+        <v>369.1232587284174</v>
       </c>
       <c r="E7">
-        <v>2107.688059196543</v>
+        <v>-871.6814420616653</v>
       </c>
       <c r="F7">
-        <v>0.7083271669301493</v>
+        <v>2.021541839441918</v>
       </c>
       <c r="G7">
-        <v>77.26528793726223</v>
+        <v>43.06082191780822</v>
       </c>
       <c r="H7">
-        <v>41.23217647208939</v>
+        <v>19.3720331356209</v>
       </c>
       <c r="I7">
-        <v>52.18447600873621</v>
+        <v>30.51897928927935</v>
       </c>
       <c r="J7">
-        <v>26775.86818431555</v>
+        <v>17471.33511848373</v>
       </c>
       <c r="K7">
-        <v>-6746.958527935734</v>
+        <v>-2560.579417647352</v>
       </c>
       <c r="L7">
-        <v>0.02075953889376583</v>
+        <v>0.03982897229712686</v>
       </c>
       <c r="M7">
-        <v>96.2</v>
+        <v>40.37034632742979</v>
       </c>
       <c r="N7">
-        <v>0.7085020529279198</v>
+        <v>1.157169402852753</v>
       </c>
       <c r="O7">
-        <v>41.23194310635781</v>
+        <v>22.25602024961196</v>
       </c>
       <c r="P7">
-        <v>52.18424264995955</v>
+        <v>34.60477755416951</v>
       </c>
       <c r="Q7">
-        <v>-6746.9203415229</v>
+        <v>-2941.782463974323</v>
       </c>
       <c r="R7">
-        <v>0.02082684082022829</v>
+        <v>7.206084650661484</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -828,55 +828,55 @@
         <v>18</v>
       </c>
       <c r="B8">
-        <v>79.28</v>
+        <v>94.1125706661046</v>
       </c>
       <c r="C8">
-        <v>51.57</v>
+        <v>50.93030371992502</v>
       </c>
       <c r="D8">
-        <v>5250.12947493129</v>
+        <v>1.613805388860725</v>
       </c>
       <c r="E8">
-        <v>-3736.647569551509</v>
+        <v>-64.69963740161259</v>
       </c>
       <c r="F8">
-        <v>14.05962469702511</v>
+        <v>10.99635307521173</v>
       </c>
       <c r="G8">
-        <v>88.55034549419707</v>
+        <v>47.25698630136986</v>
       </c>
       <c r="H8">
-        <v>47.48646718137286</v>
+        <v>21.78997406869397</v>
       </c>
       <c r="I8">
-        <v>58.38817292891434</v>
+        <v>32.91776963098742</v>
       </c>
       <c r="J8">
-        <v>23209.99751054226</v>
+        <v>16379.65179538372</v>
       </c>
       <c r="K8">
-        <v>-7234.481456783412</v>
+        <v>-2788.746549726452</v>
       </c>
       <c r="L8">
-        <v>0.007875970718547069</v>
+        <v>0.03088903264741465</v>
       </c>
       <c r="M8">
-        <v>47.51</v>
+        <v>45.93030371992502</v>
       </c>
       <c r="N8">
-        <v>14.06135430388009</v>
+        <v>27.86302678576693</v>
       </c>
       <c r="O8">
-        <v>47.48624911578699</v>
+        <v>24.54985895208423</v>
       </c>
       <c r="P8">
-        <v>58.38795487025126</v>
+        <v>36.87740093885473</v>
       </c>
       <c r="Q8">
-        <v>-7234.448234867127</v>
+        <v>-3141.96493456403</v>
       </c>
       <c r="R8">
-        <v>0.007914723458558712</v>
+        <v>6.677738831140457</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -884,55 +884,55 @@
         <v>18</v>
       </c>
       <c r="B9">
-        <v>107.4</v>
+        <v>74</v>
       </c>
       <c r="C9">
-        <v>67.56</v>
+        <v>41</v>
       </c>
       <c r="D9">
-        <v>1965.838485914868</v>
+        <v>457.229570012645</v>
       </c>
       <c r="E9">
-        <v>-2995.460226777194</v>
+        <v>-876.7000098045262</v>
       </c>
       <c r="F9">
-        <v>17.79378964254533</v>
+        <v>2.899795351008727</v>
       </c>
       <c r="G9">
-        <v>99.83540305113192</v>
+        <v>51.45315068493151</v>
       </c>
       <c r="H9">
-        <v>53.73670078057049</v>
+        <v>24.2071294898689</v>
       </c>
       <c r="I9">
-        <v>64.59592695917831</v>
+        <v>35.31734548459362</v>
       </c>
       <c r="J9">
-        <v>19898.83188489562</v>
+        <v>15323.18406335144</v>
       </c>
       <c r="K9">
-        <v>-7580.272015356536</v>
+        <v>-2996.52429051275</v>
       </c>
       <c r="L9">
-        <v>0.001403905946059814</v>
+        <v>0.02332311103454144</v>
       </c>
       <c r="M9">
-        <v>63.5</v>
+        <v>36</v>
       </c>
       <c r="N9">
-        <v>17.79541376375152</v>
+        <v>18.19131931956453</v>
       </c>
       <c r="O9">
-        <v>53.73649801512776</v>
+        <v>26.84282745247101</v>
       </c>
       <c r="P9">
-        <v>64.59572420063139</v>
+        <v>39.15089452562543</v>
       </c>
       <c r="Q9">
-        <v>-7580.243412610389</v>
+        <v>-3322.789037049409</v>
       </c>
       <c r="R9">
-        <v>0.001419141788319563</v>
+        <v>6.165184234876356</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -940,55 +940,55 @@
         <v>18</v>
       </c>
       <c r="B10">
-        <v>202.3</v>
+        <v>34</v>
       </c>
       <c r="C10">
-        <v>124.9</v>
+        <v>23</v>
       </c>
       <c r="D10">
-        <v>2556.538375756322</v>
+        <v>3767.863735484891</v>
       </c>
       <c r="E10">
-        <v>6315.221629300304</v>
+        <v>-1411.807322573271</v>
       </c>
       <c r="F10">
-        <v>84.20776212045369</v>
+        <v>10.59439390574282</v>
       </c>
       <c r="G10">
-        <v>111.1204606080668</v>
+        <v>55.64931506849315</v>
       </c>
       <c r="H10">
-        <v>59.9828295064279</v>
+        <v>26.62349566504712</v>
       </c>
       <c r="I10">
-        <v>70.80778586278251</v>
+        <v>37.71771058419655</v>
       </c>
       <c r="J10">
-        <v>16842.37130737565</v>
+        <v>14301.93192238691</v>
       </c>
       <c r="K10">
-        <v>-7784.461359190249</v>
+        <v>-3183.922081853985</v>
       </c>
       <c r="L10">
-        <v>9.417395849304534E-05</v>
+        <v>0.01702362237829368</v>
       </c>
       <c r="M10">
-        <v>120.84</v>
+        <v>18</v>
       </c>
       <c r="N10">
-        <v>84.20893381163276</v>
+        <v>0.2501941162850943</v>
       </c>
       <c r="O10">
-        <v>59.9826420411257</v>
+        <v>29.1349216140808</v>
       </c>
       <c r="P10">
-        <v>70.80759840435437</v>
+        <v>41.42526245117313</v>
       </c>
       <c r="Q10">
-        <v>-7784.437030287909</v>
+        <v>-3484.265231253682</v>
       </c>
       <c r="R10">
-        <v>9.05706526230713E-05</v>
+        <v>5.668929305787432</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -996,55 +996,55 @@
         <v>18</v>
       </c>
       <c r="B11">
-        <v>58.33</v>
+        <v>60.64</v>
       </c>
       <c r="C11">
-        <v>35.63</v>
+        <v>34.42</v>
       </c>
       <c r="D11">
-        <v>8725.01283908115</v>
+        <v>1207.070981280375</v>
       </c>
       <c r="E11">
-        <v>-3328.11910118519</v>
+        <v>-1195.851549694434</v>
       </c>
       <c r="F11">
-        <v>0.3926876124277968</v>
+        <v>0.3781997762184174</v>
       </c>
       <c r="G11">
-        <v>122.4055181650016</v>
+        <v>59.8454794520548</v>
       </c>
       <c r="H11">
-        <v>66.22481427918164</v>
+        <v>29.03906917481951</v>
       </c>
       <c r="I11">
-        <v>77.02378871949033</v>
+        <v>40.11886834920531</v>
       </c>
       <c r="J11">
-        <v>14040.61577798234</v>
+        <v>13315.89537249011</v>
       </c>
       <c r="K11">
-        <v>-7847.183828797787</v>
+        <v>-3350.949464586908</v>
       </c>
       <c r="L11">
-        <v>0.002780814997462076</v>
+        <v>0.01188597417264742</v>
       </c>
       <c r="M11">
-        <v>31.57</v>
+        <v>29.42</v>
       </c>
       <c r="N11">
-        <v>0.3923630327124475</v>
+        <v>12.78520328732236</v>
       </c>
       <c r="O11">
-        <v>66.22464211401736</v>
+        <v>31.42613764883993</v>
       </c>
       <c r="P11">
-        <v>77.0236165611836</v>
+        <v>43.70050850357149</v>
       </c>
       <c r="Q11">
-        <v>-7847.16342841301</v>
+        <v>-3626.40408666161</v>
       </c>
       <c r="R11">
-        <v>0.002762686917858693</v>
+        <v>5.189492024955336</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -1052,55 +1052,55 @@
         <v>18</v>
       </c>
       <c r="B12">
-        <v>312.6</v>
+        <v>137.1416930596449</v>
       </c>
       <c r="C12">
-        <v>171.5</v>
+        <v>70.27755004352284</v>
       </c>
       <c r="D12">
-        <v>25876.65472822748</v>
+        <v>1743.794537111294</v>
       </c>
       <c r="E12">
-        <v>27587.87121236992</v>
+        <v>2934.703766705256</v>
       </c>
       <c r="F12">
-        <v>26.0673820631274</v>
+        <v>75.08497166554244</v>
       </c>
       <c r="G12">
-        <v>133.6905757219365</v>
+        <v>64.04164383561644</v>
       </c>
       <c r="H12">
-        <v>72.46262513925232</v>
+        <v>31.45384692162812</v>
       </c>
       <c r="I12">
-        <v>83.24396548888124</v>
+        <v>42.52082187717784</v>
       </c>
       <c r="J12">
-        <v>11493.5652967157</v>
+        <v>12365.07441366107</v>
       </c>
       <c r="K12">
-        <v>-7768.576506519023</v>
+        <v>-3497.616072731199</v>
       </c>
       <c r="L12">
-        <v>0.008388476652801321</v>
+        <v>0.007808689302282334</v>
       </c>
       <c r="M12">
-        <v>167.44</v>
+        <v>65.27755004352284</v>
       </c>
       <c r="N12">
-        <v>26.06825718839467</v>
+        <v>87.31871083996543</v>
       </c>
       <c r="O12">
-        <v>72.4624682742233</v>
+        <v>33.71647212522639</v>
       </c>
       <c r="P12">
-        <v>83.24380863069858</v>
+        <v>45.97663611434253</v>
       </c>
       <c r="Q12">
-        <v>-7768.559689325652</v>
+        <v>-3749.21627598743</v>
       </c>
       <c r="R12">
-        <v>0.008359767154075194</v>
+        <v>4.727399655810668</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -1108,55 +1108,55 @@
         <v>18</v>
       </c>
       <c r="B13">
-        <v>127.6</v>
+        <v>39.57172591084831</v>
       </c>
       <c r="C13">
-        <v>66.86</v>
+        <v>23.11388189268761</v>
       </c>
       <c r="D13">
-        <v>582.6322875460318</v>
+        <v>3114.890174649043</v>
       </c>
       <c r="E13">
-        <v>-1613.851782746052</v>
+        <v>-1290.013511844751</v>
       </c>
       <c r="F13">
-        <v>58.23965039185672</v>
+        <v>0.02921476880348097</v>
       </c>
       <c r="G13">
-        <v>144.9756332788713</v>
+        <v>68.23780821917808</v>
       </c>
       <c r="H13">
-        <v>78.69624158831694</v>
+        <v>33.86782613631402</v>
       </c>
       <c r="I13">
-        <v>89.46833666927823</v>
+        <v>44.92357393727308</v>
       </c>
       <c r="J13">
-        <v>9201.219863575725</v>
+        <v>11449.46904589977</v>
       </c>
       <c r="K13">
-        <v>-7548.778734628141</v>
+        <v>-3623.931627437402</v>
       </c>
       <c r="L13">
-        <v>0.0159389135817621</v>
+        <v>0.004693523380763964</v>
       </c>
       <c r="M13">
-        <v>62.8</v>
+        <v>18.11388189268761</v>
       </c>
       <c r="N13">
-        <v>58.23713020895935</v>
+        <v>11.68284966717229</v>
       </c>
       <c r="O13">
-        <v>78.6961000234205</v>
+        <v>36.00592197552358</v>
       </c>
       <c r="P13">
-        <v>89.46819511122227</v>
+        <v>48.25364835120283</v>
       </c>
       <c r="Q13">
-        <v>-7548.765155300104</v>
+        <v>-3852.71256847028</v>
       </c>
       <c r="R13">
-        <v>0.01590318865301467</v>
+        <v>4.283188467617434</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -1164,55 +1164,55 @@
         <v>18</v>
       </c>
       <c r="B14">
-        <v>100.9</v>
+        <v>145.0997033165353</v>
       </c>
       <c r="C14">
-        <v>58.73</v>
+        <v>87.29970331653533</v>
       </c>
       <c r="D14">
-        <v>2584.479589350386</v>
+        <v>2471.757840506848</v>
       </c>
       <c r="E14">
-        <v>-2985.702654212916</v>
+        <v>4340.259816316517</v>
       </c>
       <c r="F14">
-        <v>1.048448243788287</v>
+        <v>14.36060011296359</v>
       </c>
       <c r="G14">
-        <v>156.2606908358061</v>
+        <v>72.43397260273971</v>
       </c>
       <c r="H14">
-        <v>84.92565282582993</v>
+        <v>36.28100438401951</v>
       </c>
       <c r="I14">
-        <v>95.69691306122684</v>
+        <v>47.32712696434872</v>
       </c>
       <c r="J14">
-        <v>7163.579478562413</v>
+        <v>10569.0792692062</v>
       </c>
       <c r="K14">
-        <v>-7187.931601498165</v>
+        <v>-3729.905930703625</v>
       </c>
       <c r="L14">
-        <v>0.02455645125316587</v>
+        <v>0.002445576140430317</v>
       </c>
       <c r="M14">
-        <v>54.66999999999999</v>
+        <v>82.29970331653533</v>
       </c>
       <c r="N14">
-        <v>1.048036008883847</v>
+        <v>11.20619746593326</v>
       </c>
       <c r="O14">
-        <v>84.92552656106342</v>
+        <v>38.29448450235891</v>
       </c>
       <c r="P14">
-        <v>95.69678680330027</v>
+        <v>50.53154791152497</v>
       </c>
       <c r="Q14">
-        <v>-7187.920914709484</v>
+        <v>-3936.903822913464</v>
       </c>
       <c r="R14">
-        <v>0.02451689456013674</v>
+        <v>3.857403437743577</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -1220,55 +1220,55 @@
         <v>18</v>
       </c>
       <c r="B15">
-        <v>24.93</v>
+        <v>29.418424606323</v>
       </c>
       <c r="C15">
-        <v>16.92</v>
+        <v>18.318424224854</v>
       </c>
       <c r="D15">
-        <v>16080.21235519596</v>
+        <v>4351.315585069769</v>
       </c>
       <c r="E15">
-        <v>-2145.587590009919</v>
+        <v>-1208.365739881809</v>
       </c>
       <c r="F15">
-        <v>0.8116340526826602</v>
+        <v>1.446962307638206</v>
       </c>
       <c r="G15">
-        <v>167.545748392741</v>
+        <v>76.63013698630135</v>
       </c>
       <c r="H15">
-        <v>91.15085787468156</v>
+        <v>38.69337956941578</v>
       </c>
       <c r="I15">
-        <v>101.9296956418368</v>
+        <v>49.73148305373358</v>
       </c>
       <c r="J15">
-        <v>5380.644141675764</v>
+        <v>9723.905083580386</v>
       </c>
       <c r="K15">
-        <v>-6686.177403618485</v>
+        <v>-3815.548858877131</v>
       </c>
       <c r="L15">
-        <v>0.03347229941010008</v>
+        <v>0.0009733964274356878</v>
       </c>
       <c r="M15">
-        <v>12.86</v>
+        <v>13.318424224854</v>
       </c>
       <c r="N15">
-        <v>0.8110858211229168</v>
+        <v>7.229794283109459</v>
       </c>
       <c r="O15">
-        <v>91.15074691004229</v>
+        <v>40.58215738449513</v>
       </c>
       <c r="P15">
-        <v>101.9295846840423</v>
+        <v>52.81033711654624</v>
       </c>
       <c r="Q15">
-        <v>-6686.169264043269</v>
+        <v>-4001.800980485418</v>
       </c>
       <c r="R15">
-        <v>0.03343170879317794</v>
+        <v>3.450597933316929</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -1276,55 +1276,55 @@
         <v>18</v>
       </c>
       <c r="B16">
-        <v>70.91</v>
+        <v>27.23</v>
       </c>
       <c r="C16">
-        <v>49.13</v>
+        <v>16.95</v>
       </c>
       <c r="D16">
-        <v>6533.129565047488</v>
+        <v>4644.821467991068</v>
       </c>
       <c r="E16">
-        <v>-3971.068693214381</v>
+        <v>-1155.192113809432</v>
       </c>
       <c r="F16">
-        <v>35.16005078187658</v>
+        <v>1.189206810140965</v>
       </c>
       <c r="G16">
-        <v>178.8308059496758</v>
+        <v>80.82630136986299</v>
       </c>
       <c r="H16">
-        <v>97.37186559260125</v>
+        <v>41.10494994123017</v>
       </c>
       <c r="I16">
-        <v>108.1666755533787</v>
+        <v>52.13664395670033</v>
       </c>
       <c r="J16">
-        <v>3852.413852915781</v>
+        <v>8913.94648902231</v>
       </c>
       <c r="K16">
-        <v>-6043.659092012444</v>
+        <v>-3880.870355958168</v>
       </c>
       <c r="L16">
-        <v>0.0420276306215713</v>
+        <v>0.0001890803822308853</v>
       </c>
       <c r="M16">
-        <v>45.07</v>
+        <v>11.95</v>
       </c>
       <c r="N16">
-        <v>35.1629205095526</v>
+        <v>8.216701648488856</v>
       </c>
       <c r="O16">
-        <v>97.37176992808656</v>
+        <v>42.86893868184559</v>
       </c>
       <c r="P16">
-        <v>108.1665798957189</v>
+        <v>55.09001790635325</v>
       </c>
       <c r="Q16">
-        <v>-6043.653154324894</v>
+        <v>-4047.415057301587</v>
       </c>
       <c r="R16">
-        <v>0.04198841609467178</v>
+        <v>3.063333372974528</v>
       </c>
     </row>
     <row r="17" spans="1:18">
@@ -1332,55 +1332,55 @@
         <v>18</v>
       </c>
       <c r="B17">
-        <v>319.549987792969</v>
+        <v>26.62</v>
       </c>
       <c r="C17">
-        <v>209.050003051758</v>
+        <v>18.18</v>
       </c>
       <c r="D17">
-        <v>28160.93802834547</v>
+        <v>4728.34013901452</v>
       </c>
       <c r="E17">
-        <v>35081.14313922744</v>
+        <v>-1250.110014103568</v>
       </c>
       <c r="F17">
-        <v>818.4295447895945</v>
+        <v>7.132177867699284</v>
       </c>
       <c r="G17">
-        <v>190.1158635066107</v>
+        <v>85.02246575342463</v>
       </c>
       <c r="H17">
-        <v>103.5886945689971</v>
+        <v>43.51571409605019</v>
       </c>
       <c r="I17">
-        <v>114.4078342064445</v>
+        <v>54.54261107666144</v>
       </c>
       <c r="J17">
-        <v>2578.888612282462</v>
+        <v>8139.203485531976</v>
       </c>
       <c r="K17">
-        <v>-5260.519712064926</v>
+        <v>-3925.880426724585</v>
       </c>
       <c r="L17">
-        <v>0.04967537239241795</v>
+        <v>8.36241600058667E-06</v>
       </c>
       <c r="M17">
-        <v>204.990003051758</v>
+        <v>13.18</v>
       </c>
       <c r="N17">
-        <v>818.4241021391014</v>
+        <v>1.701886491315864</v>
       </c>
       <c r="O17">
-        <v>103.5886142046043</v>
+        <v>45.15482683968852</v>
       </c>
       <c r="P17">
-        <v>114.4077538489221</v>
+        <v>57.37059183566781</v>
       </c>
       <c r="Q17">
-        <v>-5260.515630939335</v>
+        <v>-4073.757136807774</v>
       </c>
       <c r="R17">
-        <v>0.04963955566312393</v>
+        <v>2.696178869521781</v>
       </c>
     </row>
     <row r="18" spans="1:18">
@@ -1388,55 +1388,55 @@
         <v>18</v>
       </c>
       <c r="B18">
-        <v>87.389999389648</v>
+        <v>89.136192321777</v>
       </c>
       <c r="C18">
-        <v>51.990001678467</v>
+        <v>48.036190032959</v>
       </c>
       <c r="D18">
-        <v>4140.636507502104</v>
+        <v>39.02169499470553</v>
       </c>
       <c r="E18">
-        <v>-3345.441075708017</v>
+        <v>-300.0693373744181</v>
       </c>
       <c r="F18">
-        <v>0.09415332170862969</v>
+        <v>11.24947334909074</v>
       </c>
       <c r="G18">
-        <v>201.4009210635455</v>
+        <v>89.21863013698626</v>
       </c>
       <c r="H18">
-        <v>109.8013729100198</v>
+        <v>45.92567098138539</v>
       </c>
       <c r="I18">
-        <v>120.6531434948833</v>
+        <v>56.94938546610737</v>
       </c>
       <c r="J18">
-        <v>1560.068419775808</v>
+        <v>7399.676073109385</v>
       </c>
       <c r="K18">
-        <v>-4336.901845920123</v>
+        <v>-3950.589129696824</v>
       </c>
       <c r="L18">
-        <v>0.05598069623610943</v>
+        <v>0.000350698626772948</v>
       </c>
       <c r="M18">
-        <v>47.930001678467</v>
+        <v>43.036190032959</v>
       </c>
       <c r="N18">
-        <v>0.09401858233828998</v>
+        <v>29.86506651524754</v>
       </c>
       <c r="O18">
-        <v>109.8013078457464</v>
+        <v>47.43982069205892</v>
       </c>
       <c r="P18">
-        <v>120.6530784375009</v>
+        <v>59.65206007045489</v>
       </c>
       <c r="Q18">
-        <v>-4336.899276030875</v>
+        <v>-4080.838361986646</v>
       </c>
       <c r="R18">
-        <v>0.05594991174280269</v>
+        <v>2.349710854420493</v>
       </c>
     </row>
     <row r="19" spans="1:18">
@@ -1444,55 +1444,55 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>42.080001831055</v>
+        <v>34.76</v>
       </c>
       <c r="C19">
-        <v>27.079999923706</v>
+        <v>25.64</v>
       </c>
       <c r="D19">
-        <v>12024.8276960911</v>
+        <v>3675.139286340919</v>
       </c>
       <c r="E19">
-        <v>-2969.53254828217</v>
+        <v>-1554.371850033855</v>
       </c>
       <c r="F19">
-        <v>0.04291710799402142</v>
+        <v>29.79746252364318</v>
       </c>
       <c r="G19">
-        <v>212.6859786204804</v>
+        <v>93.4147945205479</v>
       </c>
       <c r="H19">
-        <v>116.0099379176039</v>
+        <v>48.33481989797137</v>
       </c>
       <c r="I19">
-        <v>126.9025661167609</v>
+        <v>59.35696782430253</v>
       </c>
       <c r="J19">
-        <v>795.9532753958177</v>
+        <v>6695.364251754536</v>
       </c>
       <c r="K19">
-        <v>-3272.947066441477</v>
+        <v>-3955.006569963811</v>
       </c>
       <c r="L19">
-        <v>0.06062022219138373</v>
+        <v>0.001139342335026935</v>
       </c>
       <c r="M19">
-        <v>23.019999923706</v>
+        <v>20.64</v>
       </c>
       <c r="N19">
-        <v>0.04280073323022309</v>
+        <v>2.980015609711292</v>
       </c>
       <c r="O19">
-        <v>116.0098881534471</v>
+        <v>49.72391946430096</v>
       </c>
       <c r="P19">
-        <v>126.9025163595211</v>
+        <v>61.93442338537034</v>
       </c>
       <c r="Q19">
-        <v>-3272.945662463042</v>
+        <v>-4068.669927410147</v>
       </c>
       <c r="R19">
-        <v>0.06059571962832663</v>
+        <v>2.024512685123576</v>
       </c>
     </row>
     <row r="20" spans="1:18">
@@ -1500,55 +1500,55 @@
         <v>18</v>
       </c>
       <c r="B20">
-        <v>65.330001831055</v>
+        <v>37.01</v>
       </c>
       <c r="C20">
-        <v>39.830001831055</v>
+        <v>19.77</v>
       </c>
       <c r="D20">
-        <v>7466.303642023503</v>
+        <v>3407.398614533105</v>
       </c>
       <c r="E20">
-        <v>-3441.621850658518</v>
+        <v>-1154.032768142329</v>
       </c>
       <c r="F20">
-        <v>0.08434671569162262</v>
+        <v>2.89908516120506</v>
       </c>
       <c r="G20">
-        <v>223.9710361774152</v>
+        <v>97.61095890410954</v>
       </c>
       <c r="H20">
-        <v>122.2144356709254</v>
+        <v>50.74316050130416</v>
       </c>
       <c r="I20">
-        <v>133.156055992901</v>
+        <v>61.76535849575087</v>
       </c>
       <c r="J20">
-        <v>286.5431791424922</v>
+        <v>6026.268021467429</v>
       </c>
       <c r="K20">
-        <v>-2068.795411252037</v>
+        <v>-3939.1428918911</v>
       </c>
       <c r="L20">
-        <v>0.06337999080047554</v>
+        <v>0.002301411457154669</v>
       </c>
       <c r="M20">
-        <v>35.770001831055</v>
+        <v>14.77</v>
       </c>
       <c r="N20">
-        <v>0.08420183032746099</v>
+        <v>28.81548173750238</v>
       </c>
       <c r="O20">
-        <v>122.2144012068827</v>
+        <v>52.00712277476791</v>
       </c>
       <c r="P20">
-        <v>133.1560215358064</v>
+        <v>64.21768216206087</v>
       </c>
       <c r="Q20">
-        <v>-2068.794827858979</v>
+        <v>-4037.263071161472</v>
       </c>
       <c r="R20">
-        <v>0.06336263907876868</v>
+        <v>1.721174236366224</v>
       </c>
     </row>
     <row r="21" spans="1:18">
@@ -1556,55 +1556,55 @@
         <v>18</v>
       </c>
       <c r="B21">
-        <v>250.683853149414</v>
+        <v>40.18154390183008</v>
       </c>
       <c r="C21">
-        <v>139.483856201172</v>
+        <v>25.88154390183008</v>
       </c>
       <c r="D21">
-        <v>9790.325948291043</v>
+        <v>3047.192703502809</v>
       </c>
       <c r="E21">
-        <v>13801.38023116313</v>
+        <v>-1428.697021867403</v>
       </c>
       <c r="F21">
-        <v>8.679017821972542</v>
+        <v>6.700764982421616</v>
       </c>
       <c r="G21">
-        <v>235.2560937343501</v>
+        <v>101.8071232876712</v>
       </c>
       <c r="H21">
-        <v>128.4149205210134</v>
+        <v>53.15069280239734</v>
       </c>
       <c r="I21">
-        <v>139.4135587722746</v>
+        <v>64.17455746943882</v>
       </c>
       <c r="J21">
-        <v>31.8381310158313</v>
+        <v>5392.387382248065</v>
       </c>
       <c r="K21">
-        <v>-724.5848846244047</v>
+        <v>-3903.0082717333</v>
       </c>
       <c r="L21">
-        <v>0.06415228502825564</v>
+        <v>0.003767947475888611</v>
       </c>
       <c r="M21">
-        <v>135.423856201172</v>
+        <v>20.88154390183008</v>
       </c>
       <c r="N21">
-        <v>8.679028170216601</v>
+        <v>0.9646629873129645</v>
       </c>
       <c r="O21">
-        <v>128.4149013570822</v>
+        <v>54.28943063566076</v>
       </c>
       <c r="P21">
-        <v>139.4135396153278</v>
+        <v>66.5018363883255</v>
       </c>
       <c r="Q21">
-        <v>-724.5847764913717</v>
+        <v>-3986.629066650997</v>
       </c>
       <c r="R21">
-        <v>0.06414257759904375</v>
+        <v>1.440291476611038</v>
       </c>
     </row>
     <row r="22" spans="1:18">
@@ -1612,55 +1612,55 @@
         <v>18</v>
       </c>
       <c r="B22">
-        <v>460.957244873047</v>
+        <v>38.59</v>
       </c>
       <c r="C22">
-        <v>250.057250976563</v>
+        <v>23.94</v>
       </c>
       <c r="D22">
-        <v>95616.6791958274</v>
+        <v>3225.43656499695</v>
       </c>
       <c r="E22">
-        <v>77322.5700379222</v>
+        <v>-1359.62267401757</v>
       </c>
       <c r="F22">
-        <v>71.18069043253089</v>
+        <v>2.435152813049836</v>
       </c>
       <c r="G22">
-        <v>246.5411512912849</v>
+        <v>106.0032876712328</v>
       </c>
       <c r="H22">
-        <v>134.61145451106</v>
+        <v>55.55741716775779</v>
       </c>
       <c r="I22">
-        <v>145.6750124116895</v>
+        <v>66.58456437885951</v>
       </c>
       <c r="J22">
-        <v>31.83813101583483</v>
+        <v>4793.722334096444</v>
       </c>
       <c r="K22">
-        <v>759.5490059900357</v>
+        <v>-3846.61291017335</v>
       </c>
       <c r="L22">
-        <v>0.06293141069874647</v>
+        <v>0.005473965809334915</v>
       </c>
       <c r="M22">
-        <v>245.997250976563</v>
+        <v>18.94</v>
       </c>
       <c r="N22">
-        <v>71.18553061184967</v>
+        <v>4.234212747563004</v>
       </c>
       <c r="O22">
-        <v>134.6114506472379</v>
+        <v>56.57084345300147</v>
       </c>
       <c r="P22">
-        <v>145.675008554893</v>
+        <v>68.78688565814228</v>
       </c>
       <c r="Q22">
-        <v>759.5489841883083</v>
+        <v>-3916.779214351177</v>
       </c>
       <c r="R22">
-        <v>0.06292947214652157</v>
+        <v>1.182466030921527</v>
       </c>
     </row>
     <row r="23" spans="1:18">
@@ -1668,55 +1668,55 @@
         <v>18</v>
       </c>
       <c r="B23">
-        <v>76.209999084473</v>
+        <v>26</v>
       </c>
       <c r="C23">
-        <v>44.909999847412</v>
+        <v>18</v>
       </c>
       <c r="D23">
-        <v>5704.445265157044</v>
+        <v>4813.99056857934</v>
       </c>
       <c r="E23">
-        <v>-3391.95250307546</v>
+        <v>-1248.892687231255</v>
       </c>
       <c r="F23">
-        <v>1.478267925751405</v>
+        <v>8.102330986237282</v>
       </c>
       <c r="G23">
-        <v>257.8262088482197</v>
+        <v>110.1994520547944</v>
       </c>
       <c r="H23">
-        <v>140.8041067362444</v>
+        <v>57.96333431858037</v>
       </c>
       <c r="I23">
-        <v>151.9403478159667</v>
+        <v>68.99537850281807</v>
       </c>
       <c r="J23">
-        <v>286.5431791425019</v>
+        <v>4230.272877012565</v>
       </c>
       <c r="K23">
-        <v>2383.473673156991</v>
+        <v>-3769.967024811597</v>
       </c>
       <c r="L23">
-        <v>0.0598085648013368</v>
+        <v>0.007358497424196068</v>
       </c>
       <c r="M23">
-        <v>40.849999847412</v>
+        <v>13</v>
       </c>
       <c r="N23">
-        <v>1.477697039238471</v>
+        <v>1.316084443686027</v>
       </c>
       <c r="O23">
-        <v>140.8041181725289</v>
+        <v>58.85136202574068</v>
       </c>
       <c r="P23">
-        <v>151.9403592593229</v>
+        <v>71.07282917256055</v>
       </c>
       <c r="Q23">
-        <v>2383.473866745684</v>
+        <v>-3827.724833475828</v>
       </c>
       <c r="R23">
-        <v>0.05981415859947429</v>
+        <v>0.9483047316098149</v>
       </c>
     </row>
     <row r="24" spans="1:18">
@@ -1724,55 +1724,55 @@
         <v>18</v>
       </c>
       <c r="B24">
-        <v>27.590000152588</v>
+        <v>29.15548904960638</v>
       </c>
       <c r="C24">
-        <v>18.590000152588</v>
+        <v>17.35548904960638</v>
       </c>
       <c r="D24">
-        <v>15412.67054267235</v>
+        <v>4386.073546533559</v>
       </c>
       <c r="E24">
-        <v>-2307.90719401964</v>
+        <v>-1149.409575318712</v>
       </c>
       <c r="F24">
-        <v>0.488800804908938</v>
+        <v>0.1527814796518018</v>
       </c>
       <c r="G24">
-        <v>269.1112664051545</v>
+        <v>114.3956164383561</v>
       </c>
       <c r="H24">
-        <v>146.9929526575888</v>
+        <v>60.36844532916549</v>
       </c>
       <c r="I24">
-        <v>158.2094895240839</v>
+        <v>71.40699876701409</v>
       </c>
       <c r="J24">
-        <v>795.9532753958322</v>
+        <v>3702.039010996428</v>
       </c>
       <c r="K24">
-        <v>4147.059828011735</v>
+        <v>-3673.080842627868</v>
       </c>
       <c r="L24">
-        <v>0.05496593588997659</v>
+        <v>0.009364621583758604</v>
       </c>
       <c r="M24">
-        <v>14.530000152588</v>
+        <v>12.35548904960638</v>
       </c>
       <c r="N24">
-        <v>0.4883804149310934</v>
+        <v>12.31092990937941</v>
       </c>
       <c r="O24">
-        <v>146.9929793939774</v>
+        <v>61.13098754400483</v>
       </c>
       <c r="P24">
-        <v>158.2095162675952</v>
+        <v>73.35966574145388</v>
       </c>
       <c r="Q24">
-        <v>4147.060582315947</v>
+        <v>-3719.477253629498</v>
       </c>
       <c r="R24">
-        <v>0.05497847319861389</v>
+        <v>0.7384191580658834</v>
       </c>
     </row>
     <row r="25" spans="1:18">
@@ -1780,55 +1780,55 @@
         <v>18</v>
       </c>
       <c r="B25">
-        <v>242.449996948242</v>
+        <v>31.28404045105</v>
       </c>
       <c r="C25">
-        <v>131.449996948242</v>
+        <v>17.68404006958</v>
       </c>
       <c r="D25">
-        <v>8228.706813948824</v>
+        <v>4108.667265584285</v>
       </c>
       <c r="E25">
-        <v>11924.12101073784</v>
+        <v>-1133.527279356737</v>
       </c>
       <c r="F25">
-        <v>41.40985672966868</v>
+        <v>0.2522517675896706</v>
       </c>
       <c r="G25">
-        <v>280.3963239620894</v>
+        <v>118.5917808219177</v>
       </c>
       <c r="H25">
-        <v>153.1780733845188</v>
+        <v>62.77275162456781</v>
       </c>
       <c r="I25">
-        <v>164.4823564266154</v>
+        <v>73.81942374639287</v>
       </c>
       <c r="J25">
-        <v>1560.068419775826</v>
+        <v>3209.020736048034</v>
       </c>
       <c r="K25">
-        <v>6050.181811116407</v>
+        <v>-3555.964592439829</v>
       </c>
       <c r="L25">
-        <v>0.04867018957082105</v>
+        <v>0.01143948966675481</v>
       </c>
       <c r="M25">
-        <v>127.389996948242</v>
+        <v>12.68404006958</v>
       </c>
       <c r="N25">
-        <v>41.40973566020971</v>
+        <v>18.82116780870427</v>
       </c>
       <c r="O25">
-        <v>153.1781154210093</v>
+        <v>63.40972158649126</v>
       </c>
       <c r="P25">
-        <v>164.4823984702843</v>
+        <v>75.64739378612492</v>
       </c>
       <c r="Q25">
-        <v>6050.183471461156</v>
+        <v>-3592.047806452723</v>
       </c>
       <c r="R25">
-        <v>0.04868873894829245</v>
+        <v>0.553425167227644</v>
       </c>
     </row>
     <row r="26" spans="1:18">
@@ -1836,55 +1836,55 @@
         <v>18</v>
       </c>
       <c r="B26">
-        <v>29.979999542236</v>
+        <v>32.52860296262585</v>
       </c>
       <c r="C26">
-        <v>18.979999542236</v>
+        <v>23.72860296262585</v>
       </c>
       <c r="D26">
-        <v>14824.9564170764</v>
+        <v>3950.666058794089</v>
       </c>
       <c r="E26">
-        <v>-2310.962563967888</v>
+        <v>-1491.445301190191</v>
       </c>
       <c r="F26">
-        <v>2.651515161109947</v>
+        <v>23.30964497622582</v>
       </c>
       <c r="G26">
-        <v>291.6813815190242</v>
+        <v>122.7879452054794</v>
       </c>
       <c r="H26">
-        <v>159.359554940443</v>
+        <v>65.17625497748801</v>
       </c>
       <c r="I26">
-        <v>170.7588625001528</v>
+        <v>76.23265166825382</v>
       </c>
       <c r="J26">
-        <v>2578.888612282482</v>
+        <v>2751.218052167382</v>
       </c>
       <c r="K26">
-        <v>8092.717873876894</v>
+        <v>-3418.628497380841</v>
       </c>
       <c r="L26">
-        <v>0.04126549490965226</v>
+        <v>0.01353434003898953</v>
       </c>
       <c r="M26">
-        <v>14.919999542236</v>
+        <v>18.72860296262585</v>
       </c>
       <c r="N26">
-        <v>2.650546477312232</v>
+        <v>1.058903516569232</v>
       </c>
       <c r="O26">
-        <v>159.3596122770329</v>
+        <v>65.68756611702484</v>
       </c>
       <c r="P26">
-        <v>170.7589198439815</v>
+        <v>77.93601134274881</v>
       </c>
       <c r="Q26">
-        <v>8092.720785587121</v>
+        <v>-3445.447817288876</v>
       </c>
       <c r="R26">
-        <v>0.04128879280394272</v>
+        <v>0.3939424161931498</v>
       </c>
     </row>
     <row r="27" spans="1:18">
@@ -1892,55 +1892,55 @@
         <v>18</v>
       </c>
       <c r="B27">
-        <v>67.84</v>
+        <v>34.544059753418</v>
       </c>
       <c r="C27">
-        <v>43.64</v>
+        <v>21.444061279297</v>
       </c>
       <c r="D27">
-        <v>7038.8370169778</v>
+        <v>3701.36777617036</v>
       </c>
       <c r="E27">
-        <v>-3661.298996455843</v>
+        <v>-1304.632398865559</v>
       </c>
       <c r="F27">
-        <v>4.554526800029939</v>
+        <v>1.922948567690058</v>
       </c>
       <c r="G27">
-        <v>302.966439075959</v>
+        <v>126.984109589041</v>
       </c>
       <c r="H27">
-        <v>165.5374875248642</v>
+        <v>67.57895750442323</v>
       </c>
       <c r="I27">
-        <v>177.0389175451931</v>
+        <v>78.64668041609973</v>
       </c>
       <c r="J27">
-        <v>3852.413852915803</v>
+        <v>2328.630959354472</v>
       </c>
       <c r="K27">
-        <v>10274.55041001663</v>
+        <v>-3261.082767420294</v>
       </c>
       <c r="L27">
-        <v>0.03316624497142829</v>
+        <v>0.01560450400504775</v>
       </c>
       <c r="M27">
-        <v>39.58</v>
+        <v>16.444061279297</v>
       </c>
       <c r="N27">
-        <v>4.555577455953099</v>
+        <v>5.532696265741723</v>
       </c>
       <c r="O27">
-        <v>165.5375601615514</v>
+        <v>67.96452348029349</v>
       </c>
       <c r="P27">
-        <v>177.0389901891839</v>
+        <v>80.22551606663767</v>
       </c>
       <c r="Q27">
-        <v>10274.5549184172</v>
+        <v>-3279.688596898084</v>
       </c>
       <c r="R27">
-        <v>0.03319270685633794</v>
+        <v>0.2605938785091709</v>
       </c>
     </row>
     <row r="28" spans="1:18">
@@ -1948,55 +1948,55 @@
         <v>18</v>
       </c>
       <c r="B28">
-        <v>31.84</v>
+        <v>22.08</v>
       </c>
       <c r="C28">
-        <v>19.78</v>
+        <v>15.38</v>
       </c>
       <c r="D28">
-        <v>14375.47697446682</v>
+        <v>5373.319116795621</v>
       </c>
       <c r="E28">
-        <v>-2371.578032765733</v>
+        <v>-1127.39901831204</v>
       </c>
       <c r="F28">
-        <v>3.441055302341098</v>
+        <v>6.132170521405106</v>
       </c>
       <c r="G28">
-        <v>314.2514966328938</v>
+        <v>131.1802739726026</v>
       </c>
       <c r="H28">
-        <v>171.7119647843776</v>
+        <v>69.98086166109587</v>
       </c>
       <c r="I28">
-        <v>183.3224279151414</v>
+        <v>81.06150753420823</v>
       </c>
       <c r="J28">
-        <v>5380.644141675785</v>
+        <v>1941.259457609305</v>
       </c>
       <c r="K28">
-        <v>12595.56613773945</v>
+        <v>-3083.337591949071</v>
       </c>
       <c r="L28">
-        <v>0.0248496173458238</v>
+        <v>0.01760940291239625</v>
       </c>
       <c r="M28">
-        <v>15.72</v>
+        <v>10.38</v>
       </c>
       <c r="N28">
-        <v>3.439961122799935</v>
+        <v>2.670752418684113</v>
       </c>
       <c r="O28">
-        <v>171.7120527211598</v>
+        <v>70.24059639678397</v>
       </c>
       <c r="P28">
-        <v>183.3225158592964</v>
+        <v>82.51590523730466</v>
       </c>
       <c r="Q28">
-        <v>12595.57258815517</v>
+        <v>-3094.781433243287</v>
       </c>
       <c r="R28">
-        <v>0.02487734936774722</v>
+        <v>0.1540053556909359</v>
       </c>
     </row>
     <row r="29" spans="1:18">
@@ -2004,55 +2004,55 @@
         <v>18</v>
       </c>
       <c r="B29">
-        <v>39.47</v>
+        <v>35</v>
       </c>
       <c r="C29">
-        <v>27.63</v>
+        <v>22</v>
       </c>
       <c r="D29">
-        <v>12604.0537945879</v>
+        <v>3646.097881348085</v>
       </c>
       <c r="E29">
-        <v>-3101.95868368641</v>
+        <v>-1328.424395504868</v>
       </c>
       <c r="F29">
-        <v>3.180778981725064</v>
+        <v>2.825621533031673</v>
       </c>
       <c r="G29">
-        <v>325.5365541898286</v>
+        <v>135.3764383561643</v>
       </c>
       <c r="H29">
-        <v>177.8830831034738</v>
+        <v>72.38197023718324</v>
       </c>
       <c r="I29">
-        <v>189.6092972255067</v>
+        <v>83.47713023290198</v>
       </c>
       <c r="J29">
-        <v>7163.579478562432</v>
+        <v>1589.10354693188</v>
       </c>
       <c r="K29">
-        <v>15055.65623420794</v>
+        <v>-2885.403132452228</v>
       </c>
       <c r="L29">
-        <v>0.01684810929715163</v>
+        <v>0.01951253652373099</v>
       </c>
       <c r="M29">
-        <v>23.57</v>
+        <v>17</v>
       </c>
       <c r="N29">
-        <v>3.181794232444192</v>
+        <v>4.179233770433286</v>
       </c>
       <c r="O29">
-        <v>177.8831863403489</v>
+        <v>72.51578795694348</v>
       </c>
       <c r="P29">
-        <v>189.6094004698281</v>
+        <v>84.80717576430263</v>
       </c>
       <c r="Q29">
-        <v>15055.66497196352</v>
+        <v>-2890.737583372927</v>
       </c>
       <c r="R29">
-        <v>0.0168749203028823</v>
+        <v>0.07480498553985317</v>
       </c>
     </row>
     <row r="30" spans="1:18">
@@ -2060,55 +2060,55 @@
         <v>18</v>
       </c>
       <c r="B30">
-        <v>36.58</v>
+        <v>106</v>
       </c>
       <c r="C30">
-        <v>25.38</v>
+        <v>62</v>
       </c>
       <c r="D30">
-        <v>13261.31364673076</v>
+        <v>112.7222376348481</v>
       </c>
       <c r="E30">
-        <v>-2922.704385014878</v>
+        <v>658.2585217590092</v>
       </c>
       <c r="F30">
-        <v>1.273878322957281</v>
+        <v>0.8665676749363908</v>
       </c>
       <c r="G30">
-        <v>336.8216117467634</v>
+        <v>139.5726027397259</v>
       </c>
       <c r="H30">
-        <v>184.0509409244641</v>
+        <v>74.78228635037462</v>
       </c>
       <c r="I30">
-        <v>195.899427033978</v>
+        <v>85.89354539449175</v>
       </c>
       <c r="J30">
-        <v>9201.219863575741</v>
+        <v>1272.163227322198</v>
       </c>
       <c r="K30">
-        <v>17654.71642479502</v>
+        <v>-2667.289515290374</v>
       </c>
       <c r="L30">
-        <v>0.009742168064365382</v>
+        <v>0.02128146281613487</v>
       </c>
       <c r="M30">
-        <v>21.32</v>
+        <v>57</v>
       </c>
       <c r="N30">
-        <v>1.274529695798266</v>
+        <v>0.4584314451255409</v>
       </c>
       <c r="O30">
-        <v>184.05105946143</v>
+        <v>74.79010161459581</v>
       </c>
       <c r="P30">
-        <v>195.8995455784679</v>
+        <v>87.09932419380777</v>
       </c>
       <c r="Q30">
-        <v>17654.72779521513</v>
+        <v>-2667.568265424045</v>
       </c>
       <c r="R30">
-        <v>0.00976558188658334</v>
+        <v>0.02362274882604187</v>
       </c>
     </row>
     <row r="31" spans="1:18">
@@ -2116,55 +2116,55 @@
         <v>18</v>
       </c>
       <c r="B31">
-        <v>83.33</v>
+        <v>46.24</v>
       </c>
       <c r="C31">
-        <v>44.76</v>
+        <v>31.6</v>
       </c>
       <c r="D31">
-        <v>4679.623979713776</v>
+        <v>2415.027280850384</v>
       </c>
       <c r="E31">
-        <v>-3061.932106905672</v>
+        <v>-1552.916495361537</v>
       </c>
       <c r="F31">
-        <v>28.04607943156623</v>
+        <v>23.32717944282659</v>
       </c>
       <c r="G31">
-        <v>348.1066693036983</v>
+        <v>143.7687671232875</v>
       </c>
       <c r="H31">
-        <v>190.2156381041452</v>
+        <v>77.18181343978431</v>
       </c>
       <c r="I31">
-        <v>202.1927174837585</v>
+        <v>88.31074957986318</v>
       </c>
       <c r="J31">
-        <v>11493.56529671571</v>
+        <v>990.4384987802584</v>
       </c>
       <c r="K31">
-        <v>20392.64703022647</v>
+        <v>-2429.006824610417</v>
       </c>
       <c r="L31">
-        <v>0.004153020797467776</v>
+        <v>0.02288776940569247</v>
       </c>
       <c r="M31">
-        <v>40.7</v>
+        <v>26.6</v>
       </c>
       <c r="N31">
-        <v>28.04369486682699</v>
+        <v>2.072839902534706</v>
       </c>
       <c r="O31">
-        <v>190.2157719411999</v>
+        <v>77.0635411796444</v>
       </c>
       <c r="P31">
-        <v>202.1928513284189</v>
+        <v>89.39234671591669</v>
       </c>
       <c r="Q31">
-        <v>20392.66137863569</v>
+        <v>-2425.284650768699</v>
       </c>
       <c r="R31">
-        <v>0.004170288682814313</v>
+        <v>0.001089975892975079</v>
       </c>
     </row>
     <row r="32" spans="1:18">
@@ -2172,55 +2172,55 @@
         <v>18</v>
       </c>
       <c r="B32">
-        <v>380.579986572266</v>
+        <v>99.13152352268185</v>
       </c>
       <c r="C32">
-        <v>218.779998779297</v>
+        <v>50.13152352268185</v>
       </c>
       <c r="D32">
-        <v>52368.75679617091</v>
+        <v>14.05197537703135</v>
       </c>
       <c r="E32">
-        <v>50066.09828988411</v>
+        <v>187.9228513247178</v>
       </c>
       <c r="F32">
-        <v>21.63719548595194</v>
+        <v>48.93640096237535</v>
       </c>
       <c r="G32">
-        <v>359.3917268606331</v>
+        <v>147.9649315068492</v>
       </c>
       <c r="H32">
-        <v>196.3772753131205</v>
+        <v>79.58055525875315</v>
       </c>
       <c r="I32">
-        <v>208.4890679042447</v>
+        <v>90.72873903567549</v>
       </c>
       <c r="J32">
-        <v>14040.61577798235</v>
+        <v>743.9293613060611</v>
       </c>
       <c r="K32">
-        <v>23269.35297521733</v>
+        <v>-2170.565095405455</v>
       </c>
       <c r="L32">
-        <v>0.0007357915636016385</v>
+        <v>0.02430703683517261</v>
       </c>
       <c r="M32">
-        <v>214.719998779297</v>
+        <v>45.13152352268185</v>
       </c>
       <c r="N32">
-        <v>21.63554078553236</v>
+        <v>77.58533267754265</v>
       </c>
       <c r="O32">
-        <v>196.3774244502621</v>
+        <v>79.33611081009752</v>
       </c>
       <c r="P32">
-        <v>208.4892170490775</v>
+        <v>91.68623917262104</v>
       </c>
       <c r="Q32">
-        <v>23269.37064694021</v>
+        <v>-2163.897856325602</v>
       </c>
       <c r="R32">
-        <v>0.0007439046380328445</v>
+        <v>0.007838854721757552</v>
       </c>
     </row>
     <row r="33" spans="1:18">
@@ -2228,55 +2228,55 @@
         <v>18</v>
       </c>
       <c r="B33">
-        <v>270.5</v>
+        <v>46</v>
       </c>
       <c r="C33">
-        <v>142.300003051758</v>
+        <v>29</v>
       </c>
       <c r="D33">
-        <v>14104.46556740213</v>
+        <v>2438.673485843217</v>
       </c>
       <c r="E33">
-        <v>16899.86466867402</v>
+        <v>-1432.104884983689</v>
       </c>
       <c r="F33">
-        <v>122.4951992671089</v>
+        <v>5.605380956550882</v>
       </c>
       <c r="G33">
-        <v>370.6767844175679</v>
+        <v>152.1610958904108</v>
       </c>
       <c r="H33">
-        <v>202.5359534820523</v>
+        <v>81.97851586707245</v>
       </c>
       <c r="I33">
-        <v>214.7883773647745</v>
+        <v>93.14750970213731</v>
       </c>
       <c r="J33">
-        <v>16842.37130737565</v>
+        <v>532.6358148996062</v>
       </c>
       <c r="K33">
-        <v>26284.74376252681</v>
+        <v>-1891.974306742589</v>
       </c>
       <c r="L33">
-        <v>0.0001729756062536362</v>
+        <v>0.02551879399789034</v>
       </c>
       <c r="M33">
-        <v>138.240003051758</v>
+        <v>24</v>
       </c>
       <c r="N33">
-        <v>122.4958328476762</v>
+        <v>1.060229249873858</v>
       </c>
       <c r="O33">
-        <v>202.5361179192789</v>
+        <v>81.60781500345409</v>
       </c>
       <c r="P33">
-        <v>214.7885418097816</v>
+        <v>93.98099706642195</v>
       </c>
       <c r="Q33">
-        <v>26284.76510288782</v>
+        <v>-1883.418937057799</v>
       </c>
       <c r="R33">
-        <v>0.0001686772827677555</v>
+        <v>0.04450194196279417</v>
       </c>
     </row>
     <row r="34" spans="1:18">
@@ -2284,55 +2284,55 @@
         <v>18</v>
       </c>
       <c r="B34">
-        <v>309.440002441406</v>
+        <v>36.942516326904</v>
       </c>
       <c r="C34">
-        <v>173.740005493164</v>
+        <v>18.942516326904</v>
       </c>
       <c r="D34">
-        <v>24869.99185008183</v>
+        <v>3415.281607635121</v>
       </c>
       <c r="E34">
-        <v>27399.18548192432</v>
+        <v>-1107.008434621822</v>
       </c>
       <c r="F34">
-        <v>1.257535002237749</v>
+        <v>6.207182569878631</v>
       </c>
       <c r="G34">
-        <v>381.9618419745027</v>
+        <v>156.3572602739725</v>
       </c>
       <c r="H34">
-        <v>208.6917732975846</v>
+        <v>84.37569962266733</v>
       </c>
       <c r="I34">
-        <v>221.0905451787038</v>
+        <v>95.56705722132358</v>
       </c>
       <c r="J34">
-        <v>19898.83188489561</v>
+        <v>356.5578595608937</v>
       </c>
       <c r="K34">
-        <v>29438.73341652547</v>
+        <v>-1593.244375176296</v>
       </c>
       <c r="L34">
-        <v>0.003168324276997596</v>
+        <v>0.0265064660045775</v>
       </c>
       <c r="M34">
-        <v>169.680005493164</v>
+        <v>13.942516326904</v>
       </c>
       <c r="N34">
-        <v>1.25771761094449</v>
+        <v>37.93044308932388</v>
       </c>
       <c r="O34">
-        <v>208.6919530348944</v>
+        <v>83.87865858749011</v>
       </c>
       <c r="P34">
-        <v>221.090724923887</v>
+        <v>96.27661556954341</v>
       </c>
       <c r="Q34">
-        <v>29438.75877084904</v>
+        <v>-1583.85887867589</v>
       </c>
       <c r="R34">
-        <v>0.003148122521948395</v>
+        <v>0.111711678403714</v>
       </c>
     </row>
     <row r="35" spans="1:18">
@@ -2340,55 +2340,55 @@
         <v>18</v>
       </c>
       <c r="B35">
-        <v>110.029998779297</v>
+        <v>51.45908113846146</v>
       </c>
       <c r="C35">
-        <v>64.23000335693401</v>
+        <v>27.05908113846145</v>
       </c>
       <c r="D35">
-        <v>1739.53877973504</v>
+        <v>1929.304241277249</v>
       </c>
       <c r="E35">
-        <v>-2678.890747159341</v>
+        <v>-1188.53891093157</v>
       </c>
       <c r="F35">
-        <v>0.3174240527079064</v>
+        <v>7.325467575960849</v>
       </c>
       <c r="G35">
-        <v>393.2468995314375</v>
+        <v>160.5534246575341</v>
       </c>
       <c r="H35">
-        <v>214.8448347492987</v>
+        <v>86.77211117277763</v>
       </c>
       <c r="I35">
-        <v>227.3954713564512</v>
+        <v>97.9873769459944</v>
       </c>
       <c r="J35">
-        <v>23209.99751054224</v>
+        <v>215.6954952899236</v>
       </c>
       <c r="K35">
-        <v>32731.24040040583</v>
+        <v>-1274.385148363815</v>
       </c>
       <c r="L35">
-        <v>0.01044117832187113</v>
+        <v>0.02725731483011533</v>
       </c>
       <c r="M35">
-        <v>60.170003356934</v>
+        <v>22.05908113846145</v>
       </c>
       <c r="N35">
-        <v>0.3172111889711278</v>
+        <v>35.29556118999603</v>
       </c>
       <c r="O35">
-        <v>214.8450297866899</v>
+        <v>86.14864671048895</v>
       </c>
       <c r="P35">
-        <v>227.3956664018123</v>
+        <v>98.57308953370207</v>
       </c>
       <c r="Q35">
-        <v>32731.27011401634</v>
+        <v>-1265.228590565062</v>
       </c>
       <c r="R35">
-        <v>0.01040135770720935</v>
+        <v>0.2100999102948471</v>
       </c>
     </row>
     <row r="36" spans="1:18">
@@ -2396,55 +2396,55 @@
         <v>18</v>
       </c>
       <c r="B36">
-        <v>411.130004882813</v>
+        <v>95</v>
       </c>
       <c r="C36">
-        <v>228.229995727539</v>
+        <v>50.6</v>
       </c>
       <c r="D36">
-        <v>67284.32778881623</v>
+        <v>0.1466331397157752</v>
       </c>
       <c r="E36">
-        <v>59201.08701869292</v>
+        <v>-19.37610966119572</v>
       </c>
       <c r="F36">
-        <v>7.623475713315658</v>
+        <v>17.26995794415407</v>
       </c>
       <c r="G36">
-        <v>404.5319570883723</v>
+        <v>164.7495890410957</v>
       </c>
       <c r="H36">
-        <v>220.9952367278531</v>
+        <v>89.167755444677</v>
       </c>
       <c r="I36">
-        <v>233.7030570073583</v>
+        <v>100.4084639488762</v>
       </c>
       <c r="J36">
-        <v>26775.86818431553</v>
+        <v>110.048722086696</v>
       </c>
       <c r="K36">
-        <v>36162.18751109277</v>
+        <v>-935.4063988977235</v>
       </c>
       <c r="L36">
-        <v>0.02272127288545152</v>
+        <v>0.02776237310469686</v>
       </c>
       <c r="M36">
-        <v>224.169995727539</v>
+        <v>45.6</v>
       </c>
       <c r="N36">
-        <v>7.624686692667408</v>
+        <v>37.1090373179091</v>
       </c>
       <c r="O36">
-        <v>220.9954470653241</v>
+        <v>88.4177848309596</v>
       </c>
       <c r="P36">
-        <v>233.703267352899</v>
+        <v>100.8704135003889</v>
       </c>
       <c r="Q36">
-        <v>36162.22192931454</v>
+        <v>-927.5388989527264</v>
       </c>
       <c r="R36">
-        <v>0.02265790636526348</v>
+        <v>0.3402974178977243</v>
       </c>
     </row>
     <row r="37" spans="1:18">
@@ -2452,55 +2452,55 @@
         <v>18</v>
       </c>
       <c r="B37">
-        <v>319.399993896484</v>
+        <v>123</v>
       </c>
       <c r="C37">
-        <v>177.600006103516</v>
+        <v>76.3</v>
       </c>
       <c r="D37">
-        <v>28110.61891182146</v>
+        <v>762.7027173091434</v>
       </c>
       <c r="E37">
-        <v>29776.81071087166</v>
+        <v>2107.182664680845</v>
       </c>
       <c r="F37">
-        <v>7.612066806844364</v>
+        <v>29.96291324035904</v>
       </c>
       <c r="G37">
-        <v>415.8170146453072</v>
+        <v>168.9457534246574</v>
       </c>
       <c r="H37">
-        <v>227.1430766734426</v>
+        <v>91.56263763597097</v>
       </c>
       <c r="I37">
-        <v>240.0132046912304</v>
+        <v>102.8303130323633</v>
       </c>
       <c r="J37">
-        <v>30596.44390621548</v>
+        <v>39.61753995121077</v>
       </c>
       <c r="K37">
-        <v>39731.50175574544</v>
+        <v>-576.3178183695364</v>
       </c>
       <c r="L37">
-        <v>0.04074402494955186</v>
+        <v>0.02801637143748237</v>
       </c>
       <c r="M37">
-        <v>173.540006103516</v>
+        <v>71.3</v>
       </c>
       <c r="N37">
-        <v>7.612590587965868</v>
+        <v>19.12161862904242</v>
       </c>
       <c r="O37">
-        <v>227.1433023109917</v>
+        <v>90.68607870688896</v>
       </c>
       <c r="P37">
-        <v>240.0134303369522</v>
+        <v>103.168581711617</v>
       </c>
       <c r="Q37">
-        <v>39731.54122390273</v>
+        <v>-570.8005403320761</v>
       </c>
       <c r="R37">
-        <v>0.04065298530984798</v>
+        <v>0.5029334525590814</v>
       </c>
     </row>
     <row r="38" spans="1:18">
@@ -2508,55 +2508,55 @@
         <v>18</v>
       </c>
       <c r="B38">
-        <v>314.140014648438</v>
+        <v>117.2</v>
       </c>
       <c r="C38">
-        <v>180.139999389648</v>
+        <v>73.43000000000001</v>
       </c>
       <c r="D38">
-        <v>26374.48673236844</v>
+        <v>475.9846713026192</v>
       </c>
       <c r="E38">
-        <v>29255.13895711832</v>
+        <v>1602.027665367162</v>
       </c>
       <c r="F38">
-        <v>7.20566813147533</v>
+        <v>35.19713477889055</v>
       </c>
       <c r="G38">
-        <v>427.102072202242</v>
+        <v>173.141917808219</v>
       </c>
       <c r="H38">
-        <v>233.2884502728751</v>
+        <v>93.95676320451703</v>
       </c>
       <c r="I38">
-        <v>246.3258187212595</v>
+        <v>105.2529187385984</v>
       </c>
       <c r="J38">
-        <v>34671.7246762421</v>
+        <v>4.401948883467982</v>
       </c>
       <c r="K38">
-        <v>43439.11421350915</v>
+        <v>-197.1290116767685</v>
       </c>
       <c r="L38">
-        <v>0.06524630308105343</v>
+        <v>0.02801765968211912</v>
       </c>
       <c r="M38">
-        <v>176.079999389648</v>
+        <v>68.43000000000001</v>
       </c>
       <c r="N38">
-        <v>7.205196826829299</v>
+        <v>21.70388414383599</v>
       </c>
       <c r="O38">
-        <v>233.2886912105008</v>
+        <v>92.95353438457492</v>
       </c>
       <c r="P38">
-        <v>246.3260596671641</v>
+        <v>105.4675881210885</v>
       </c>
       <c r="Q38">
-        <v>43439.1590769262</v>
+        <v>-195.0241551553666</v>
       </c>
       <c r="R38">
-        <v>0.06512327402154366</v>
+        <v>0.6986352835428234</v>
       </c>
     </row>
     <row r="39" spans="1:18">
@@ -2564,55 +2564,55 @@
         <v>18</v>
       </c>
       <c r="B39">
-        <v>20.840000152588</v>
+        <v>328.4</v>
       </c>
       <c r="C39">
-        <v>13.340000152588</v>
+        <v>219.7</v>
       </c>
       <c r="D39">
-        <v>17134.2280326416</v>
+        <v>54296.95627760914</v>
       </c>
       <c r="E39">
-        <v>-1746.176365617121</v>
+        <v>51193.85092307183</v>
       </c>
       <c r="F39">
-        <v>4.943316412462525</v>
+        <v>960.1092940735577</v>
       </c>
       <c r="G39">
-        <v>438.3871297591768</v>
+        <v>177.3380821917806</v>
       </c>
       <c r="H39">
-        <v>239.4314512029183</v>
+        <v>96.35013785800921</v>
       </c>
       <c r="I39">
-        <v>252.6408054206779</v>
+        <v>107.6762753598874</v>
       </c>
       <c r="J39">
-        <v>39001.71049439537</v>
+        <v>4.401948883467624</v>
       </c>
       <c r="K39">
-        <v>47284.95988589388</v>
+        <v>202.1505084155119</v>
       </c>
       <c r="L39">
-        <v>0.0969626703527305</v>
+        <v>0.02776812257021829</v>
       </c>
       <c r="M39">
-        <v>9.280000152588002</v>
+        <v>214.7</v>
       </c>
       <c r="N39">
-        <v>4.941938636762619</v>
+        <v>1296.712187517098</v>
       </c>
       <c r="O39">
-        <v>239.431707440619</v>
+        <v>95.22015818708819</v>
       </c>
       <c r="P39">
-        <v>252.6410616667668</v>
+        <v>107.7674264057328</v>
       </c>
       <c r="Q39">
-        <v>47285.0104898949</v>
+        <v>199.7797181908782</v>
       </c>
       <c r="R39">
-        <v>0.09680315716893774</v>
+        <v>0.928027755776903</v>
       </c>
     </row>
     <row r="40" spans="1:18">
@@ -2620,55 +2620,55 @@
         <v>18</v>
       </c>
       <c r="B40">
-        <v>70.23000335693401</v>
+        <v>174.1</v>
       </c>
       <c r="C40">
-        <v>42.729999542236</v>
+        <v>101.69</v>
       </c>
       <c r="D40">
-        <v>6643.517194789833</v>
+        <v>6196.377570918348</v>
       </c>
       <c r="E40">
-        <v>-3482.827138462243</v>
+        <v>8004.73914641409</v>
       </c>
       <c r="F40">
-        <v>0.009038830785578463</v>
+        <v>2.357063139955512</v>
       </c>
       <c r="G40">
-        <v>449.6721873161116</v>
+        <v>181.5342465753423</v>
       </c>
       <c r="H40">
-        <v>245.572170917081</v>
+        <v>98.74276754327092</v>
       </c>
       <c r="I40">
-        <v>258.9580733359768</v>
+        <v>110.1003769494068</v>
       </c>
       <c r="J40">
-        <v>43586.40136067531</v>
+        <v>39.61753995120969</v>
       </c>
       <c r="K40">
-        <v>51268.97753884286</v>
+        <v>621.5113264490649</v>
       </c>
       <c r="L40">
-        <v>0.1366220840693752</v>
+        <v>0.02727309015310366</v>
       </c>
       <c r="M40">
-        <v>38.669999542236</v>
+        <v>96.69</v>
       </c>
       <c r="N40">
-        <v>0.00899270332286399</v>
+        <v>3.834249013379155</v>
       </c>
       <c r="O40">
-        <v>245.5724424548552</v>
+        <v>97.4859567024106</v>
       </c>
       <c r="P40">
-        <v>258.9583448822514</v>
+        <v>110.0680899775678</v>
       </c>
       <c r="Q40">
-        <v>51269.03422875197</v>
+        <v>613.6006491181267</v>
       </c>
       <c r="R40">
-        <v>0.136421423911374</v>
+        <v>1.191732859591683</v>
       </c>
     </row>
     <row r="41" spans="1:18">
@@ -2676,55 +2676,1959 @@
         <v>18</v>
       </c>
       <c r="B41">
-        <v>224.669998168945</v>
+        <v>220.98</v>
       </c>
       <c r="C41">
-        <v>128.470001220703</v>
+        <v>123.33</v>
       </c>
       <c r="D41">
-        <v>5319.108857308576</v>
+        <v>15774.62472898487</v>
       </c>
       <c r="E41">
-        <v>9369.602518534417</v>
+        <v>15489.88700465385</v>
       </c>
       <c r="F41">
-        <v>0.1591615335336428</v>
+        <v>13.9222045879455</v>
       </c>
       <c r="G41">
-        <v>460.9572448730464</v>
+        <v>185.7304109589039</v>
       </c>
       <c r="H41">
-        <v>251.7106984726677</v>
+        <v>101.1346584352993</v>
       </c>
       <c r="I41">
-        <v>265.2775334098516</v>
+        <v>112.5252173321596</v>
       </c>
       <c r="J41">
-        <v>48425.79727508192</v>
+        <v>110.0487220866942</v>
       </c>
       <c r="K41">
-        <v>55391.10953922627</v>
+        <v>1060.944129174681</v>
       </c>
       <c r="L41">
-        <v>0.1849450303632487</v>
+        <v>0.02654124350234074</v>
       </c>
       <c r="M41">
-        <v>124.410001220703</v>
+        <v>118.33</v>
       </c>
       <c r="N41">
-        <v>0.1591882746560856</v>
+        <v>3.64954809143236</v>
       </c>
       <c r="O41">
-        <v>251.7109853105141</v>
+        <v>99.75093677129834</v>
       </c>
       <c r="P41">
-        <v>265.2778202563132</v>
+        <v>112.3695719958376</v>
       </c>
       <c r="Q41">
-        <v>55391.1726603676</v>
+        <v>1046.428320266573</v>
       </c>
       <c r="R41">
-        <v>0.1846984020549281</v>
+        <v>1.490369313441084</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18">
+      <c r="A42" t="s">
+        <v>18</v>
+      </c>
+      <c r="B42">
+        <v>262.66</v>
+      </c>
+      <c r="C42">
+        <v>149.57</v>
+      </c>
+      <c r="D42">
+        <v>27981.6191285628</v>
+      </c>
+      <c r="E42">
+        <v>25019.63179837895</v>
+      </c>
+      <c r="F42">
+        <v>1.997291073034124</v>
+      </c>
+      <c r="G42">
+        <v>189.9265753424656</v>
+      </c>
+      <c r="H42">
+        <v>103.5258169261042</v>
+      </c>
+      <c r="I42">
+        <v>114.9507901161358</v>
+      </c>
+      <c r="J42">
+        <v>215.6954952899211</v>
+      </c>
+      <c r="K42">
+        <v>1520.439710175538</v>
+      </c>
+      <c r="L42">
+        <v>0.02558451612677143</v>
+      </c>
+      <c r="M42">
+        <v>144.57</v>
+      </c>
+      <c r="N42">
+        <v>2.724346693142798</v>
+      </c>
+      <c r="O42">
+        <v>102.0151054749176</v>
+      </c>
+      <c r="P42">
+        <v>114.6718653793757</v>
+      </c>
+      <c r="Q42">
+        <v>1498.252532626962</v>
+      </c>
+      <c r="R42">
+        <v>1.824552160510086</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18">
+      <c r="A43" t="s">
+        <v>18</v>
+      </c>
+      <c r="B43">
+        <v>326.34</v>
+      </c>
+      <c r="C43">
+        <v>170.52</v>
+      </c>
+      <c r="D43">
+        <v>53341.16953713096</v>
+      </c>
+      <c r="E43">
+        <v>39382.80007629591</v>
+      </c>
+      <c r="F43">
+        <v>289.4096343334834</v>
+      </c>
+      <c r="G43">
+        <v>194.1227397260272</v>
+      </c>
+      <c r="H43">
+        <v>105.9162496133847</v>
+      </c>
+      <c r="I43">
+        <v>117.3770887036364</v>
+      </c>
+      <c r="J43">
+        <v>356.5578595608904</v>
+      </c>
+      <c r="K43">
+        <v>1999.988974206485</v>
+      </c>
+      <c r="L43">
+        <v>0.02441799156738589</v>
+      </c>
+      <c r="M43">
+        <v>165.52</v>
+      </c>
+      <c r="N43">
+        <v>145.1836002725411</v>
+      </c>
+      <c r="O43">
+        <v>104.2784701223004</v>
+      </c>
+      <c r="P43">
+        <v>116.9749628191505</v>
+      </c>
+      <c r="Q43">
+        <v>1969.063210347716</v>
+      </c>
+      <c r="R43">
+        <v>2.194892380022269</v>
+      </c>
+    </row>
+    <row r="44" spans="1:18">
+      <c r="A44" t="s">
+        <v>18</v>
+      </c>
+      <c r="B44">
+        <v>77.33</v>
+      </c>
+      <c r="C44">
+        <v>42.03</v>
+      </c>
+      <c r="D44">
+        <v>325.9081757370806</v>
+      </c>
+      <c r="E44">
+        <v>-758.7645246849814</v>
+      </c>
+      <c r="F44">
+        <v>6.677644478235873</v>
+      </c>
+      <c r="G44">
+        <v>198.3189041095888</v>
+      </c>
+      <c r="H44">
+        <v>108.3059632890849</v>
+      </c>
+      <c r="I44">
+        <v>119.8041063027174</v>
+      </c>
+      <c r="J44">
+        <v>532.6358148996022</v>
+      </c>
+      <c r="K44">
+        <v>2499.582941245452</v>
+      </c>
+      <c r="L44">
+        <v>0.0230597976321865</v>
+      </c>
+      <c r="M44">
+        <v>37.03</v>
+      </c>
+      <c r="N44">
+        <v>25.47280517281508</v>
+      </c>
+      <c r="O44">
+        <v>106.5410382376661</v>
+      </c>
+      <c r="P44">
+        <v>119.2788567909423</v>
+      </c>
+      <c r="Q44">
+        <v>2458.850405223146</v>
+      </c>
+      <c r="R44">
+        <v>2.601996513967855</v>
+      </c>
+    </row>
+    <row r="45" spans="1:18">
+      <c r="A45" t="s">
+        <v>18</v>
+      </c>
+      <c r="B45">
+        <v>74.23</v>
+      </c>
+      <c r="C45">
+        <v>47.03</v>
+      </c>
+      <c r="D45">
+        <v>447.4463235611794</v>
+      </c>
+      <c r="E45">
+        <v>-994.8221600269966</v>
+      </c>
+      <c r="F45">
+        <v>17.59898321189333</v>
+      </c>
+      <c r="G45">
+        <v>202.5150684931505</v>
+      </c>
+      <c r="H45">
+        <v>110.6949649278697</v>
+      </c>
+      <c r="I45">
+        <v>122.2318359387136</v>
+      </c>
+      <c r="J45">
+        <v>743.9293613060564</v>
+      </c>
+      <c r="K45">
+        <v>3019.21275025455</v>
+      </c>
+      <c r="L45">
+        <v>0.02153099773061778</v>
+      </c>
+      <c r="M45">
+        <v>42.03</v>
+      </c>
+      <c r="N45">
+        <v>2.688692630211232</v>
+      </c>
+      <c r="O45">
+        <v>108.8028175476551</v>
+      </c>
+      <c r="P45">
+        <v>121.5835395681108</v>
+      </c>
+      <c r="Q45">
+        <v>2967.60430086006</v>
+      </c>
+      <c r="R45">
+        <v>3.046466309880814</v>
+      </c>
+    </row>
+    <row r="46" spans="1:18">
+      <c r="A46" t="s">
+        <v>18</v>
+      </c>
+      <c r="B46">
+        <v>136.43</v>
+      </c>
+      <c r="C46">
+        <v>82.59</v>
+      </c>
+      <c r="D46">
+        <v>1684.862196251837</v>
+      </c>
+      <c r="E46">
+        <v>3390.07775342059</v>
+      </c>
+      <c r="F46">
+        <v>16.44922009709164</v>
+      </c>
+      <c r="G46">
+        <v>206.7112328767121</v>
+      </c>
+      <c r="H46">
+        <v>113.0832616755609</v>
+      </c>
+      <c r="I46">
+        <v>124.6602704658036</v>
+      </c>
+      <c r="J46">
+        <v>990.4384987802531</v>
+      </c>
+      <c r="K46">
+        <v>3558.869662649766</v>
+      </c>
+      <c r="L46">
+        <v>0.01985547976205273</v>
+      </c>
+      <c r="M46">
+        <v>77.59</v>
+      </c>
+      <c r="N46">
+        <v>11.2577068757861</v>
+      </c>
+      <c r="O46">
+        <v>111.0638159685178</v>
+      </c>
+      <c r="P46">
+        <v>123.8890032344055</v>
+      </c>
+      <c r="Q46">
+        <v>3495.315216521535</v>
+      </c>
+      <c r="R46">
+        <v>3.528898380201031</v>
+      </c>
+    </row>
+    <row r="47" spans="1:18">
+      <c r="A47" t="s">
+        <v>18</v>
+      </c>
+      <c r="B47">
+        <v>70.81</v>
+      </c>
+      <c r="C47">
+        <v>45.25</v>
+      </c>
+      <c r="D47">
+        <v>603.8287447090565</v>
+      </c>
+      <c r="E47">
+        <v>-1111.924949845239</v>
+      </c>
+      <c r="F47">
+        <v>19.16692370377475</v>
+      </c>
+      <c r="G47">
+        <v>210.9073972602737</v>
+      </c>
+      <c r="H47">
+        <v>115.4708608375706</v>
+      </c>
+      <c r="I47">
+        <v>127.0894025785751</v>
+      </c>
+      <c r="J47">
+        <v>1272.163227322192</v>
+      </c>
+      <c r="K47">
+        <v>4118.545065479429</v>
+      </c>
+      <c r="L47">
+        <v>0.01805984300480387</v>
+      </c>
+      <c r="M47">
+        <v>40.25</v>
+      </c>
+      <c r="N47">
+        <v>2.960551128774993</v>
+      </c>
+      <c r="O47">
+        <v>113.3240415933016</v>
+      </c>
+      <c r="P47">
+        <v>126.1952396967792</v>
+      </c>
+      <c r="Q47">
+        <v>4041.973610648087</v>
+      </c>
+      <c r="R47">
+        <v>4.04988387866523</v>
+      </c>
+    </row>
+    <row r="48" spans="1:18">
+      <c r="A48" t="s">
+        <v>18</v>
+      </c>
+      <c r="B48">
+        <v>64.33</v>
+      </c>
+      <c r="C48">
+        <v>40.23</v>
+      </c>
+      <c r="D48">
+        <v>964.2842795155607</v>
+      </c>
+      <c r="E48">
+        <v>-1249.259255961856</v>
+      </c>
+      <c r="F48">
+        <v>9.468945387694651</v>
+      </c>
+      <c r="G48">
+        <v>215.1035616438354</v>
+      </c>
+      <c r="H48">
+        <v>117.85776986737</v>
+      </c>
+      <c r="I48">
+        <v>129.5192248235568</v>
+      </c>
+      <c r="J48">
+        <v>1589.103546931874</v>
+      </c>
+      <c r="K48">
+        <v>4698.230474312882</v>
+      </c>
+      <c r="L48">
+        <v>0.01617328344201234</v>
+      </c>
+      <c r="M48">
+        <v>35.23</v>
+      </c>
+      <c r="N48">
+        <v>0.05132243609932438</v>
+      </c>
+      <c r="O48">
+        <v>115.5835026790757</v>
+      </c>
+      <c r="P48">
+        <v>128.5022406981626</v>
+      </c>
+      <c r="Q48">
+        <v>4607.570084057762</v>
+      </c>
+      <c r="R48">
+        <v>4.610008194080068</v>
+      </c>
+    </row>
+    <row r="49" spans="1:18">
+      <c r="A49" t="s">
+        <v>18</v>
+      </c>
+      <c r="B49">
+        <v>161.2</v>
+      </c>
+      <c r="C49">
+        <v>95.86</v>
+      </c>
+      <c r="D49">
+        <v>4331.887089283146</v>
+      </c>
+      <c r="E49">
+        <v>6309.22461122288</v>
+      </c>
+      <c r="F49">
+        <v>9.666860689560771</v>
+      </c>
+      <c r="G49">
+        <v>219.299726027397</v>
+      </c>
+      <c r="H49">
+        <v>120.2439963550278</v>
+      </c>
+      <c r="I49">
+        <v>131.9497296106802</v>
+      </c>
+      <c r="J49">
+        <v>1941.259457609298</v>
+      </c>
+      <c r="K49">
+        <v>5297.917535841864</v>
+      </c>
+      <c r="L49">
+        <v>0.01422747794796233</v>
+      </c>
+      <c r="M49">
+        <v>90.86</v>
+      </c>
+      <c r="N49">
+        <v>9.905592547278086</v>
+      </c>
+      <c r="O49">
+        <v>117.8422076342343</v>
+      </c>
+      <c r="P49">
+        <v>130.8099978301614</v>
+      </c>
+      <c r="Q49">
+        <v>5192.095382828013</v>
+      </c>
+      <c r="R49">
+        <v>5.209850661741479</v>
+      </c>
+    </row>
+    <row r="50" spans="1:18">
+      <c r="A50" t="s">
+        <v>18</v>
+      </c>
+      <c r="B50">
+        <v>198.9</v>
+      </c>
+      <c r="C50">
+        <v>115.8</v>
+      </c>
+      <c r="D50">
+        <v>10715.78438832556</v>
+      </c>
+      <c r="E50">
+        <v>11987.27704547892</v>
+      </c>
+      <c r="F50">
+        <v>1.992186559076929</v>
+      </c>
+      <c r="G50">
+        <v>223.4958904109587</v>
+      </c>
+      <c r="H50">
+        <v>122.6295480158507</v>
+      </c>
+      <c r="I50">
+        <v>134.3809092246383</v>
+      </c>
+      <c r="J50">
+        <v>2328.630959354464</v>
+      </c>
+      <c r="K50">
+        <v>5917.598030198298</v>
+      </c>
+      <c r="L50">
+        <v>0.01225646774404394</v>
+      </c>
+      <c r="M50">
+        <v>110.8</v>
+      </c>
+      <c r="N50">
+        <v>6.62477918546075</v>
+      </c>
+      <c r="O50">
+        <v>120.1001650059121</v>
+      </c>
+      <c r="P50">
+        <v>133.1185025456412</v>
+      </c>
+      <c r="Q50">
+        <v>5795.54040086336</v>
+      </c>
+      <c r="R50">
+        <v>5.849984292682266</v>
+      </c>
+    </row>
+    <row r="51" spans="1:18">
+      <c r="A51" t="s">
+        <v>18</v>
+      </c>
+      <c r="B51">
+        <v>48.63</v>
+      </c>
+      <c r="C51">
+        <v>25.03</v>
+      </c>
+      <c r="D51">
+        <v>2185.836189463417</v>
+      </c>
+      <c r="E51">
+        <v>-1170.225764522129</v>
+      </c>
+      <c r="F51">
+        <v>9.6839562497053</v>
+      </c>
+      <c r="G51">
+        <v>227.6920547945203</v>
+      </c>
+      <c r="H51">
+        <v>125.0144326791581</v>
+      </c>
+      <c r="I51">
+        <v>136.812755836112</v>
+      </c>
+      <c r="J51">
+        <v>2751.218052167373</v>
+      </c>
+      <c r="K51">
+        <v>6557.263872993086</v>
+      </c>
+      <c r="L51">
+        <v>0.01029654151727042</v>
+      </c>
+      <c r="M51">
+        <v>20.03</v>
+      </c>
+      <c r="N51">
+        <v>41.35414384709019</v>
+      </c>
+      <c r="O51">
+        <v>122.3573834675486</v>
+      </c>
+      <c r="P51">
+        <v>135.4277461711621</v>
+      </c>
+      <c r="Q51">
+        <v>6417.896182154007</v>
+      </c>
+      <c r="R51">
+        <v>6.530975520842015</v>
+      </c>
+    </row>
+    <row r="52" spans="1:18">
+      <c r="A52" t="s">
+        <v>18</v>
+      </c>
+      <c r="B52">
+        <v>60.6</v>
+      </c>
+      <c r="C52">
+        <v>26.6</v>
+      </c>
+      <c r="D52">
+        <v>1209.852015445847</v>
+      </c>
+      <c r="E52">
+        <v>-925.2258600195219</v>
+      </c>
+      <c r="F52">
+        <v>70.76210926488493</v>
+      </c>
+      <c r="G52">
+        <v>231.8882191780819</v>
+      </c>
+      <c r="H52">
+        <v>127.3986582772192</v>
+      </c>
+      <c r="I52">
+        <v>139.245261512832</v>
+      </c>
+      <c r="J52">
+        <v>3209.020736048024</v>
+      </c>
+      <c r="K52">
+        <v>7216.907117081492</v>
+      </c>
+      <c r="L52">
+        <v>0.008386118576339609</v>
+      </c>
+      <c r="M52">
+        <v>21.6</v>
+      </c>
+      <c r="N52">
+        <v>129.3650399851072</v>
+      </c>
+      <c r="O52">
+        <v>124.613871806633</v>
+      </c>
+      <c r="P52">
+        <v>137.7377199192352</v>
+      </c>
+      <c r="Q52">
+        <v>7059.153922731567</v>
+      </c>
+      <c r="R52">
+        <v>7.253383968179405</v>
+      </c>
+    </row>
+    <row r="53" spans="1:18">
+      <c r="A53" t="s">
+        <v>18</v>
+      </c>
+      <c r="B53">
+        <v>91.87</v>
+      </c>
+      <c r="C53">
+        <v>42.86</v>
+      </c>
+      <c r="D53">
+        <v>12.34065658791901</v>
+      </c>
+      <c r="E53">
+        <v>-150.5640541517557</v>
+      </c>
+      <c r="F53">
+        <v>101.9952036419057</v>
+      </c>
+      <c r="G53">
+        <v>236.0843835616436</v>
+      </c>
+      <c r="H53">
+        <v>129.7822328343795</v>
+      </c>
+      <c r="I53">
+        <v>141.6784182304529</v>
+      </c>
+      <c r="J53">
+        <v>3702.039010996417</v>
+      </c>
+      <c r="K53">
+        <v>7896.519954061533</v>
+      </c>
+      <c r="L53">
+        <v>0.006565632401310467</v>
+      </c>
+      <c r="M53">
+        <v>37.86</v>
+      </c>
+      <c r="N53">
+        <v>147.1032447443139</v>
+      </c>
+      <c r="O53">
+        <v>126.8696389126577</v>
+      </c>
+      <c r="P53">
+        <v>140.048414900368</v>
+      </c>
+      <c r="Q53">
+        <v>7719.304972328982</v>
+      </c>
+      <c r="R53">
+        <v>8.01776222767152</v>
+      </c>
+    </row>
+    <row r="54" spans="1:18">
+      <c r="A54" t="s">
+        <v>18</v>
+      </c>
+      <c r="B54">
+        <v>50.13</v>
+      </c>
+      <c r="C54">
+        <v>26.13</v>
+      </c>
+      <c r="D54">
+        <v>2047.827408258208</v>
+      </c>
+      <c r="E54">
+        <v>-1182.458984297372</v>
+      </c>
+      <c r="F54">
+        <v>8.2531084032361</v>
+      </c>
+      <c r="G54">
+        <v>240.2805479452052</v>
+      </c>
+      <c r="H54">
+        <v>132.1651644564014</v>
+      </c>
+      <c r="I54">
+        <v>144.1122178832122</v>
+      </c>
+      <c r="J54">
+        <v>4230.272877012554</v>
+      </c>
+      <c r="K54">
+        <v>8596.09471551252</v>
+      </c>
+      <c r="L54">
+        <v>0.004877414922658615</v>
+      </c>
+      <c r="M54">
+        <v>21.13</v>
+      </c>
+      <c r="N54">
+        <v>37.78442631240686</v>
+      </c>
+      <c r="O54">
+        <v>129.1246937653104</v>
+      </c>
+      <c r="P54">
+        <v>142.3598221348728</v>
+      </c>
+      <c r="Q54">
+        <v>8398.340835752626</v>
+      </c>
+      <c r="R54">
+        <v>8.82465566407004</v>
+      </c>
+    </row>
+    <row r="55" spans="1:18">
+      <c r="A55" t="s">
+        <v>18</v>
+      </c>
+      <c r="B55">
+        <v>66.06</v>
+      </c>
+      <c r="C55">
+        <v>42.36</v>
+      </c>
+      <c r="D55">
+        <v>859.8340518588858</v>
+      </c>
+      <c r="E55">
+        <v>-1242.119190617554</v>
+      </c>
+      <c r="F55">
+        <v>17.75982804919753</v>
+      </c>
+      <c r="G55">
+        <v>244.4767123287668</v>
+      </c>
+      <c r="H55">
+        <v>134.5474613200417</v>
+      </c>
+      <c r="I55">
+        <v>146.546652294353</v>
+      </c>
+      <c r="J55">
+        <v>4793.722334096432</v>
+      </c>
+      <c r="K55">
+        <v>9315.623873981627</v>
+      </c>
+      <c r="L55">
+        <v>0.003365581844793041</v>
+      </c>
+      <c r="M55">
+        <v>37.36</v>
+      </c>
+      <c r="N55">
+        <v>2.002822604616649</v>
+      </c>
+      <c r="O55">
+        <v>131.3790454229271</v>
+      </c>
+      <c r="P55">
+        <v>144.6719325644136</v>
+      </c>
+      <c r="Q55">
+        <v>9096.253173975212</v>
+      </c>
+      <c r="R55">
+        <v>9.674602232227585</v>
+      </c>
+    </row>
+    <row r="56" spans="1:18">
+      <c r="A56" t="s">
+        <v>18</v>
+      </c>
+      <c r="B56">
+        <v>46.69</v>
+      </c>
+      <c r="C56">
+        <v>19.91</v>
+      </c>
+      <c r="D56">
+        <v>2371.001146488821</v>
+      </c>
+      <c r="E56">
+        <v>-969.4761779319053</v>
+      </c>
+      <c r="F56">
+        <v>50.67237536045783</v>
+      </c>
+      <c r="G56">
+        <v>248.6728767123285</v>
+      </c>
+      <c r="H56">
+        <v>136.9291316628856</v>
+      </c>
+      <c r="I56">
+        <v>148.9817132262902</v>
+      </c>
+      <c r="J56">
+        <v>5392.387382248053</v>
+      </c>
+      <c r="K56">
+        <v>10055.10004372689</v>
+      </c>
+      <c r="L56">
+        <v>0.002075919307242331</v>
+      </c>
+      <c r="M56">
+        <v>14.91</v>
+      </c>
+      <c r="N56">
+        <v>110.1475324121943</v>
+      </c>
+      <c r="O56">
+        <v>133.6327030112307</v>
+      </c>
+      <c r="P56">
+        <v>146.9847370632674</v>
+      </c>
+      <c r="Q56">
+        <v>9813.033804958926</v>
+      </c>
+      <c r="R56">
+        <v>10.56813231273538</v>
+      </c>
+    </row>
+    <row r="57" spans="1:18">
+      <c r="A57" t="s">
+        <v>18</v>
+      </c>
+      <c r="B57">
+        <v>278.83</v>
+      </c>
+      <c r="C57">
+        <v>156.15</v>
+      </c>
+      <c r="D57">
+        <v>33652.82856717063</v>
+      </c>
+      <c r="E57">
+        <v>28645.26043826886</v>
+      </c>
+      <c r="F57">
+        <v>16.9244916377912</v>
+      </c>
+      <c r="G57">
+        <v>252.8690410958901</v>
+      </c>
+      <c r="H57">
+        <v>139.310183773456</v>
+      </c>
+      <c r="I57">
+        <v>151.4173923905009</v>
+      </c>
+      <c r="J57">
+        <v>6026.268021467416</v>
+      </c>
+      <c r="K57">
+        <v>10814.51598122564</v>
+      </c>
+      <c r="L57">
+        <v>0.001055772155115712</v>
+      </c>
+      <c r="M57">
+        <v>151.15</v>
+      </c>
+      <c r="N57">
+        <v>0.3225276122951685</v>
+      </c>
+      <c r="O57">
+        <v>135.8856757123734</v>
+      </c>
+      <c r="P57">
+        <v>149.2982264492822</v>
+      </c>
+      <c r="Q57">
+        <v>10548.67470421865</v>
+      </c>
+      <c r="R57">
+        <v>11.50576856456696</v>
+      </c>
+    </row>
+    <row r="58" spans="1:18">
+      <c r="A58" t="s">
+        <v>18</v>
+      </c>
+      <c r="B58">
+        <v>171.85</v>
+      </c>
+      <c r="C58">
+        <v>104.07</v>
+      </c>
+      <c r="D58">
+        <v>5847.213242726162</v>
+      </c>
+      <c r="E58">
+        <v>7957.928279991291</v>
+      </c>
+      <c r="F58">
+        <v>27.10918548640631</v>
+      </c>
+      <c r="G58">
+        <v>257.0652054794518</v>
+      </c>
+      <c r="H58">
+        <v>141.6906259816132</v>
+      </c>
+      <c r="I58">
+        <v>153.8536814571248</v>
+      </c>
+      <c r="J58">
+        <v>6695.364251754527</v>
+      </c>
+      <c r="K58">
+        <v>11593.86458545767</v>
+      </c>
+      <c r="L58">
+        <v>0.00035393406800908</v>
+      </c>
+      <c r="M58">
+        <v>99.06999999999999</v>
+      </c>
+      <c r="N58">
+        <v>30.94030933125244</v>
+      </c>
+      <c r="O58">
+        <v>138.1379727543018</v>
+      </c>
+      <c r="P58">
+        <v>151.6123914945114</v>
+      </c>
+      <c r="Q58">
+        <v>11303.16800513567</v>
+      </c>
+      <c r="R58">
+        <v>12.48802579436875</v>
+      </c>
+    </row>
+    <row r="59" spans="1:18">
+      <c r="A59" t="s">
+        <v>18</v>
+      </c>
+      <c r="B59">
+        <v>69.14</v>
+      </c>
+      <c r="C59">
+        <v>43.69</v>
+      </c>
+      <c r="D59">
+        <v>688.6912211175229</v>
+      </c>
+      <c r="E59">
+        <v>-1146.55348361853</v>
+      </c>
+      <c r="F59">
+        <v>14.26189119510814</v>
+      </c>
+      <c r="G59">
+        <v>261.2613698630134</v>
+      </c>
+      <c r="H59">
+        <v>144.0704666492598</v>
+      </c>
+      <c r="I59">
+        <v>156.2905720642595</v>
+      </c>
+      <c r="J59">
+        <v>7399.67607310938</v>
+      </c>
+      <c r="K59">
+        <v>12393.13889797294</v>
+      </c>
+      <c r="L59">
+        <v>2.053977465377576E-05</v>
+      </c>
+      <c r="M59">
+        <v>38.69</v>
+      </c>
+      <c r="N59">
+        <v>1.143426480456997</v>
+      </c>
+      <c r="O59">
+        <v>140.3896034004593</v>
+      </c>
+      <c r="P59">
+        <v>153.9272229355113</v>
+      </c>
+      <c r="Q59">
+        <v>12076.5059990327</v>
+      </c>
+      <c r="R59">
+        <v>13.51541084198702</v>
+      </c>
+    </row>
+    <row r="60" spans="1:18">
+      <c r="A60" t="s">
+        <v>18</v>
+      </c>
+      <c r="B60">
+        <v>177.27</v>
+      </c>
+      <c r="C60">
+        <v>105.05</v>
+      </c>
+      <c r="D60">
+        <v>6705.492713304675</v>
+      </c>
+      <c r="E60">
+        <v>8602.237011464258</v>
+      </c>
+      <c r="F60">
+        <v>9.460968833618937</v>
+      </c>
+      <c r="G60">
+        <v>265.4575342465751</v>
+      </c>
+      <c r="H60">
+        <v>146.4497141613619</v>
+      </c>
+      <c r="I60">
+        <v>158.7280558269385</v>
+      </c>
+      <c r="J60">
+        <v>8139.203485531976</v>
+      </c>
+      <c r="K60">
+        <v>13212.33210275382</v>
+      </c>
+      <c r="L60">
+        <v>0.0001069595584036848</v>
+      </c>
+      <c r="M60">
+        <v>100.05</v>
+      </c>
+      <c r="N60">
+        <v>12.91146578685834</v>
+      </c>
+      <c r="O60">
+        <v>142.6405769398396</v>
+      </c>
+      <c r="P60">
+        <v>156.2427114832885</v>
+      </c>
+      <c r="Q60">
+        <v>12868.68113502123</v>
+      </c>
+      <c r="R60">
+        <v>14.58842248179283</v>
+      </c>
+    </row>
+    <row r="61" spans="1:18">
+      <c r="A61" t="s">
+        <v>18</v>
+      </c>
+      <c r="B61">
+        <v>254.45</v>
+      </c>
+      <c r="C61">
+        <v>152.07</v>
+      </c>
+      <c r="D61">
+        <v>25302.33369102597</v>
+      </c>
+      <c r="E61">
+        <v>24189.32978070794</v>
+      </c>
+      <c r="F61">
+        <v>33.62641993830744</v>
+      </c>
+      <c r="G61">
+        <v>269.6536986301368</v>
+      </c>
+      <c r="H61">
+        <v>148.8283769172967</v>
+      </c>
+      <c r="I61">
+        <v>161.1661243457849</v>
+      </c>
+      <c r="J61">
+        <v>8913.946489022315</v>
+      </c>
+      <c r="K61">
+        <v>14051.43752588207</v>
+      </c>
+      <c r="L61">
+        <v>0.000665696237087297</v>
+      </c>
+      <c r="M61">
+        <v>147.07</v>
+      </c>
+      <c r="N61">
+        <v>74.26668807535557</v>
+      </c>
+      <c r="O61">
+        <v>144.8909026774011</v>
+      </c>
+      <c r="P61">
+        <v>158.5588478328846</v>
+      </c>
+      <c r="Q61">
+        <v>13679.68601963265</v>
+      </c>
+      <c r="R61">
+        <v>15.7075513393141</v>
+      </c>
+    </row>
+    <row r="62" spans="1:18">
+      <c r="A62" t="s">
+        <v>18</v>
+      </c>
+      <c r="B62">
+        <v>98.73</v>
+      </c>
+      <c r="C62">
+        <v>60.17</v>
+      </c>
+      <c r="D62">
+        <v>11.20289720942884</v>
+      </c>
+      <c r="E62">
+        <v>201.3933782941871</v>
+      </c>
+      <c r="F62">
+        <v>10.71562531358003</v>
+      </c>
+      <c r="G62">
+        <v>273.8498630136984</v>
+      </c>
+      <c r="H62">
+        <v>151.2064633225341</v>
+      </c>
+      <c r="I62">
+        <v>163.6047692153287</v>
+      </c>
+      <c r="J62">
+        <v>9723.905083580397</v>
+      </c>
+      <c r="K62">
+        <v>14910.44863502093</v>
+      </c>
+      <c r="L62">
+        <v>0.001750284779440378</v>
+      </c>
+      <c r="M62">
+        <v>55.17</v>
+      </c>
+      <c r="N62">
+        <v>2.098734980935284</v>
+      </c>
+      <c r="O62">
+        <v>147.140589924852</v>
+      </c>
+      <c r="P62">
+        <v>160.8756226725912</v>
+      </c>
+      <c r="Q62">
+        <v>14509.51341624445</v>
+      </c>
+      <c r="R62">
+        <v>16.87327982266986</v>
+      </c>
+    </row>
+    <row r="63" spans="1:18">
+      <c r="A63" t="s">
+        <v>18</v>
+      </c>
+      <c r="B63">
+        <v>50.02</v>
+      </c>
+      <c r="C63">
+        <v>22.83</v>
+      </c>
+      <c r="D63">
+        <v>2057.795152213256</v>
+      </c>
+      <c r="E63">
+        <v>-1035.635624971642</v>
+      </c>
+      <c r="F63">
+        <v>37.32829327921469</v>
+      </c>
+      <c r="G63">
+        <v>278.0460273972601</v>
+      </c>
+      <c r="H63">
+        <v>153.583981780659</v>
+      </c>
+      <c r="I63">
+        <v>166.0439820319849</v>
+      </c>
+      <c r="J63">
+        <v>10569.07926920622</v>
+      </c>
+      <c r="K63">
+        <v>15789.35903872275</v>
+      </c>
+      <c r="L63">
+        <v>0.0034151946997284</v>
+      </c>
+      <c r="M63">
+        <v>17.83</v>
+      </c>
+      <c r="N63">
+        <v>88.11671201640264</v>
+      </c>
+      <c r="O63">
+        <v>149.3896479918117</v>
+      </c>
+      <c r="P63">
+        <v>163.193026692789</v>
+      </c>
+      <c r="Q63">
+        <v>15358.15624431326</v>
+      </c>
+      <c r="R63">
+        <v>18.0860820682627</v>
+      </c>
+    </row>
+    <row r="64" spans="1:18">
+      <c r="A64" t="s">
+        <v>18</v>
+      </c>
+      <c r="B64">
+        <v>286.1</v>
+      </c>
+      <c r="C64">
+        <v>170.3</v>
+      </c>
+      <c r="D64">
+        <v>36373.00190759607</v>
+      </c>
+      <c r="E64">
+        <v>32479.11752025096</v>
+      </c>
+      <c r="F64">
+        <v>34.3804503886354</v>
+      </c>
+      <c r="G64">
+        <v>282.2421917808218</v>
+      </c>
+      <c r="H64">
+        <v>155.9609406857376</v>
+      </c>
+      <c r="I64">
+        <v>168.4837544016875</v>
+      </c>
+      <c r="J64">
+        <v>11449.46904589979</v>
+      </c>
+      <c r="K64">
+        <v>16688.16248557269</v>
+      </c>
+      <c r="L64">
+        <v>0.005715735352030168</v>
+      </c>
+      <c r="M64">
+        <v>165.3</v>
+      </c>
+      <c r="N64">
+        <v>92.66580690408611</v>
+      </c>
+      <c r="O64">
+        <v>151.6380861773553</v>
+      </c>
+      <c r="P64">
+        <v>165.5110505944029</v>
+      </c>
+      <c r="Q64">
+        <v>16225.60757842618</v>
+      </c>
+      <c r="R64">
+        <v>19.34642390016804</v>
+      </c>
+    </row>
+    <row r="65" spans="1:18">
+      <c r="A65" t="s">
+        <v>18</v>
+      </c>
+      <c r="B65">
+        <v>24.19</v>
+      </c>
+      <c r="C65">
+        <v>15.99</v>
+      </c>
+      <c r="D65">
+        <v>5068.43286456696</v>
+      </c>
+      <c r="E65">
+        <v>-1138.374903823765</v>
+      </c>
+      <c r="F65">
+        <v>3.516746320084863</v>
+      </c>
+      <c r="G65">
+        <v>286.4383561643834</v>
+      </c>
+      <c r="H65">
+        <v>158.3373484150316</v>
+      </c>
+      <c r="I65">
+        <v>170.9240779471747</v>
+      </c>
+      <c r="J65">
+        <v>12365.0744136611</v>
+      </c>
+      <c r="K65">
+        <v>17606.85286317878</v>
+      </c>
+      <c r="L65">
+        <v>0.008707964226520594</v>
+      </c>
+      <c r="M65">
+        <v>10.99</v>
+      </c>
+      <c r="N65">
+        <v>4.719078296110589</v>
+      </c>
+      <c r="O65">
+        <v>153.8859137619413</v>
+      </c>
+      <c r="P65">
+        <v>167.8296850969745</v>
+      </c>
+      <c r="Q65">
+        <v>17111.86064718196</v>
+      </c>
+      <c r="R65">
+        <v>20.65476280264676</v>
+      </c>
+    </row>
+    <row r="66" spans="1:18">
+      <c r="A66" t="s">
+        <v>18</v>
+      </c>
+      <c r="B66">
+        <v>42.48</v>
+      </c>
+      <c r="C66">
+        <v>25.08</v>
+      </c>
+      <c r="D66">
+        <v>2798.719692404775</v>
+      </c>
+      <c r="E66">
+        <v>-1326.805410875549</v>
+      </c>
+      <c r="F66">
+        <v>0.2188867627745881</v>
+      </c>
+      <c r="G66">
+        <v>290.6345205479451</v>
+      </c>
+      <c r="H66">
+        <v>160.7132133220604</v>
+      </c>
+      <c r="I66">
+        <v>173.3649443149271</v>
+      </c>
+      <c r="J66">
+        <v>13315.89537249015</v>
+      </c>
+      <c r="K66">
+        <v>18545.4241970188</v>
+      </c>
+      <c r="L66">
+        <v>0.01244859833172377</v>
+      </c>
+      <c r="M66">
+        <v>20.08</v>
+      </c>
+      <c r="N66">
+        <v>9.207341405622854</v>
+      </c>
+      <c r="O66">
+        <v>156.133139999726</v>
+      </c>
+      <c r="P66">
+        <v>170.1489209463473</v>
+      </c>
+      <c r="Q66">
+        <v>18016.90883191359</v>
+      </c>
+      <c r="R66">
+        <v>22.01154790518615</v>
+      </c>
+    </row>
+    <row r="67" spans="1:18">
+      <c r="A67" t="s">
+        <v>18</v>
+      </c>
+      <c r="B67">
+        <v>84.06999999999999</v>
+      </c>
+      <c r="C67">
+        <v>50.67</v>
+      </c>
+      <c r="D67">
+        <v>127.9823188550072</v>
+      </c>
+      <c r="E67">
+        <v>-573.2260145559843</v>
+      </c>
+      <c r="F67">
+        <v>4.785155954571101</v>
+      </c>
+      <c r="G67">
+        <v>294.8306849315068</v>
+      </c>
+      <c r="H67">
+        <v>163.0885437300118</v>
+      </c>
+      <c r="I67">
+        <v>175.8063451817568</v>
+      </c>
+      <c r="J67">
+        <v>14301.93192238695</v>
+      </c>
+      <c r="K67">
+        <v>19503.87064915412</v>
+      </c>
+      <c r="L67">
+        <v>0.01699492872881352</v>
+      </c>
+      <c r="M67">
+        <v>45.67</v>
+      </c>
+      <c r="N67">
+        <v>0.005542873400556926</v>
+      </c>
+      <c r="O67">
+        <v>158.3797741112642</v>
+      </c>
+      <c r="P67">
+        <v>172.4687489219666</v>
+      </c>
+      <c r="Q67">
+        <v>18940.74566526343</v>
+      </c>
+      <c r="R67">
+        <v>23.41721997946801</v>
+      </c>
+    </row>
+    <row r="68" spans="1:18">
+      <c r="A68" t="s">
+        <v>18</v>
+      </c>
+      <c r="B68">
+        <v>112.5</v>
+      </c>
+      <c r="C68">
+        <v>61.34</v>
+      </c>
+      <c r="D68">
+        <v>292.9941857456081</v>
+      </c>
+      <c r="E68">
+        <v>1049.961253624155</v>
+      </c>
+      <c r="F68">
+        <v>11.9698240003591</v>
+      </c>
+      <c r="G68">
+        <v>299.0268493150684</v>
+      </c>
+      <c r="H68">
+        <v>165.4633479254996</v>
+      </c>
+      <c r="I68">
+        <v>178.2482722610502</v>
+      </c>
+      <c r="J68">
+        <v>15323.18406335149</v>
+      </c>
+      <c r="K68">
+        <v>20482.18651682058</v>
+      </c>
+      <c r="L68">
+        <v>0.02240473826805023</v>
+      </c>
+      <c r="M68">
+        <v>56.34</v>
+      </c>
+      <c r="N68">
+        <v>23.75468155375189</v>
+      </c>
+      <c r="O68">
+        <v>160.6258252765933</v>
+      </c>
+      <c r="P68">
+        <v>174.789159843795</v>
+      </c>
+      <c r="Q68">
+        <v>19883.36482962219</v>
+      </c>
+      <c r="R68">
+        <v>24.87221144766192</v>
+      </c>
+    </row>
+    <row r="69" spans="1:18">
+      <c r="A69" t="s">
+        <v>18</v>
+      </c>
+      <c r="B69">
+        <v>29.22</v>
+      </c>
+      <c r="C69">
+        <v>20.72</v>
+      </c>
+      <c r="D69">
+        <v>4377.532918258825</v>
+      </c>
+      <c r="E69">
+        <v>-1370.895848857312</v>
+      </c>
+      <c r="F69">
+        <v>13.82618590417162</v>
+      </c>
+      <c r="G69">
+        <v>303.2230136986301</v>
+      </c>
+      <c r="H69">
+        <v>167.8376341526645</v>
+      </c>
+      <c r="I69">
+        <v>180.6907173086665</v>
+      </c>
+      <c r="J69">
+        <v>16379.65179538377</v>
+      </c>
+      <c r="K69">
+        <v>21480.36623090614</v>
+      </c>
+      <c r="L69">
+        <v>0.02873622256139174</v>
+      </c>
+      <c r="M69">
+        <v>15.72</v>
+      </c>
+      <c r="N69">
+        <v>0.03214291060787704</v>
+      </c>
+      <c r="O69">
+        <v>162.8713026286983</v>
+      </c>
+      <c r="P69">
+        <v>177.1101445788475</v>
+      </c>
+      <c r="Q69">
+        <v>20844.76015544245</v>
+      </c>
+      <c r="R69">
+        <v>26.37694640142984</v>
+      </c>
+    </row>
+    <row r="70" spans="1:18">
+      <c r="A70" t="s">
+        <v>18</v>
+      </c>
+      <c r="B70">
+        <v>69.3</v>
+      </c>
+      <c r="C70">
+        <v>43</v>
+      </c>
+      <c r="D70">
+        <v>680.3190844556341</v>
+      </c>
+      <c r="E70">
+        <v>-1121.565863941333</v>
+      </c>
+      <c r="F70">
+        <v>8.967993247424154</v>
+      </c>
+      <c r="G70">
+        <v>307.4191780821918</v>
+      </c>
+      <c r="H70">
+        <v>170.2114106076153</v>
+      </c>
+      <c r="I70">
+        <v>183.1336721284968</v>
+      </c>
+      <c r="J70">
+        <v>17471.3351184838</v>
+      </c>
+      <c r="K70">
+        <v>22498.40435432507</v>
+      </c>
+      <c r="L70">
+        <v>0.03604791421075953</v>
+      </c>
+      <c r="M70">
+        <v>38</v>
+      </c>
+      <c r="N70">
+        <v>0.08541092810770838</v>
+      </c>
+      <c r="O70">
+        <v>165.1162152473539</v>
+      </c>
+      <c r="P70">
+        <v>179.4316940473493</v>
+      </c>
+      <c r="Q70">
+        <v>21824.92561943753</v>
+      </c>
+      <c r="R70">
+        <v>27.93184063103773</v>
+      </c>
+    </row>
+    <row r="71" spans="1:18">
+      <c r="A71" t="s">
+        <v>18</v>
+      </c>
+      <c r="B71">
+        <v>28.62</v>
+      </c>
+      <c r="C71">
+        <v>16.72</v>
+      </c>
+      <c r="D71">
+        <v>4457.288430740908</v>
+      </c>
+      <c r="E71">
+        <v>-1116.276140583699</v>
+      </c>
+      <c r="F71">
+        <v>0.003934385746920763</v>
+      </c>
+      <c r="G71">
+        <v>311.6153424657534</v>
+      </c>
+      <c r="H71">
+        <v>172.5846854332055</v>
+      </c>
+      <c r="I71">
+        <v>185.5771285776878</v>
+      </c>
+      <c r="J71">
+        <v>18598.23403265157</v>
+      </c>
+      <c r="K71">
+        <v>23536.29558029775</v>
+      </c>
+      <c r="L71">
+        <v>0.0443986102981671</v>
+      </c>
+      <c r="M71">
+        <v>11.72</v>
+      </c>
+      <c r="N71">
+        <v>14.84414818913404</v>
+      </c>
+      <c r="O71">
+        <v>167.3605721533375</v>
+      </c>
+      <c r="P71">
+        <v>181.7537992285233</v>
+      </c>
+      <c r="Q71">
+        <v>22823.85534267587</v>
+      </c>
+      <c r="R71">
+        <v>29.53730166397166</v>
+      </c>
+    </row>
+    <row r="72" spans="1:18">
+      <c r="A72" t="s">
+        <v>18</v>
+      </c>
+      <c r="B72">
+        <v>34.51</v>
+      </c>
+      <c r="C72">
+        <v>24.11</v>
+      </c>
+      <c r="D72">
+        <v>3705.51324987512</v>
+      </c>
+      <c r="E72">
+        <v>-1467.646271619198</v>
+      </c>
+      <c r="F72">
+        <v>16.5827423161926</v>
+      </c>
+      <c r="G72">
+        <v>315.8115068493151</v>
+      </c>
+      <c r="H72">
+        <v>174.957466714138</v>
+      </c>
+      <c r="I72">
+        <v>188.0210785715364</v>
+      </c>
+      <c r="J72">
+        <v>19760.34853788708</v>
+      </c>
+      <c r="K72">
+        <v>24594.0347305453</v>
+      </c>
+      <c r="L72">
+        <v>0.0538473031309705</v>
+      </c>
+      <c r="M72">
+        <v>19.11</v>
+      </c>
+      <c r="N72">
+        <v>0.110425290589403</v>
+      </c>
+      <c r="O72">
+        <v>169.6043823030067</v>
+      </c>
+      <c r="P72">
+        <v>184.0764511660116</v>
+      </c>
+      <c r="Q72">
+        <v>23841.54358858099</v>
+      </c>
+      <c r="R72">
+        <v>31.19372881245569</v>
+      </c>
+    </row>
+    <row r="73" spans="1:18">
+      <c r="A73" t="s">
+        <v>18</v>
+      </c>
+      <c r="B73">
+        <v>97.40000000000001</v>
+      </c>
+      <c r="C73">
+        <v>36.9</v>
+      </c>
+      <c r="D73">
+        <v>4.068583211381027</v>
+      </c>
+      <c r="E73">
+        <v>74.42999117592665</v>
+      </c>
+      <c r="F73">
+        <v>369.9152431978962</v>
+      </c>
+      <c r="G73">
+        <v>320.0076712328768</v>
+      </c>
+      <c r="H73">
+        <v>177.329762472394</v>
+      </c>
+      <c r="I73">
+        <v>190.4655140880616</v>
+      </c>
+      <c r="J73">
+        <v>20957.67863419033</v>
+      </c>
+      <c r="K73">
+        <v>25671.61675340768</v>
+      </c>
+      <c r="L73">
+        <v>0.06445311422421524</v>
+      </c>
+      <c r="M73">
+        <v>31.9</v>
+      </c>
+      <c r="N73">
+        <v>445.1093503204769</v>
+      </c>
+      <c r="O73">
+        <v>171.8476545832347</v>
+      </c>
+      <c r="P73">
+        <v>186.3996409729412</v>
+      </c>
+      <c r="Q73">
+        <v>24877.98476084671</v>
+      </c>
+      <c r="R73">
+        <v>32.9015132292865</v>
+      </c>
+    </row>
+    <row r="74" spans="1:18">
+      <c r="A74" t="s">
+        <v>18</v>
+      </c>
+      <c r="B74">
+        <v>302.4</v>
+      </c>
+      <c r="C74">
+        <v>161.9</v>
+      </c>
+      <c r="D74">
+        <v>42856.06848516611</v>
+      </c>
+      <c r="E74">
+        <v>33516.06410762553</v>
+      </c>
+      <c r="F74">
+        <v>141.4151810343874</v>
+      </c>
+      <c r="G74">
+        <v>324.2038356164384</v>
+      </c>
+      <c r="H74">
+        <v>179.7015806629755</v>
+      </c>
+      <c r="I74">
+        <v>192.9104271722613</v>
+      </c>
+      <c r="J74">
+        <v>22190.22432156133</v>
+      </c>
+      <c r="K74">
+        <v>26769.03672189366</v>
+      </c>
+      <c r="L74">
+        <v>0.07627523149147804</v>
+      </c>
+      <c r="M74">
+        <v>156.9</v>
+      </c>
+      <c r="N74">
+        <v>58.41396059109643</v>
+      </c>
+      <c r="O74">
+        <v>174.0903978066943</v>
+      </c>
+      <c r="P74">
+        <v>188.723359836639</v>
+      </c>
+      <c r="Q74">
+        <v>25933.17340127681</v>
+      </c>
+      <c r="R74">
+        <v>34.66103797141086</v>
+      </c>
+    </row>
+    <row r="75" spans="1:18">
+      <c r="A75" t="s">
+        <v>18</v>
+      </c>
+      <c r="B75">
+        <v>25.32</v>
+      </c>
+      <c r="C75">
+        <v>15.02</v>
+      </c>
+      <c r="D75">
+        <v>4908.813749392368</v>
+      </c>
+      <c r="E75">
+        <v>-1052.345164567414</v>
+      </c>
+      <c r="F75">
+        <v>0.06591628229763695</v>
+      </c>
+      <c r="G75">
+        <v>328.4000000000001</v>
+      </c>
+      <c r="H75">
+        <v>182.0729291699564</v>
+      </c>
+      <c r="I75">
+        <v>195.3558099400616</v>
+      </c>
+      <c r="J75">
+        <v>23457.98560000007</v>
+      </c>
+      <c r="K75">
+        <v>27886.28983167056</v>
+      </c>
+      <c r="L75">
+        <v>0.08937284960587358</v>
+      </c>
+      <c r="M75">
+        <v>10.02</v>
+      </c>
+      <c r="N75">
+        <v>14.11657705096085</v>
+      </c>
+      <c r="O75">
+        <v>176.3326207074832</v>
+      </c>
+      <c r="P75">
+        <v>191.0475990230077</v>
+      </c>
+      <c r="Q75">
+        <v>27007.10418755816</v>
+      </c>
+      <c r="R75">
+        <v>36.47267807066655</v>
       </c>
     </row>
   </sheetData>

--- a/import/c_phi_data_geforceerd.xlsx
+++ b/import/c_phi_data_geforceerd.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="19">
   <si>
     <t>PV_NAAM</t>
   </si>
@@ -70,7 +70,7 @@
     <t>kappa_2_ondergrens_cor</t>
   </si>
   <si>
-    <t>TXT_SAFE_klei_licht_16_175</t>
+    <t>TXT_klei_14_16</t>
   </si>
 </sst>
 </file>
@@ -428,7 +428,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R41"/>
+  <dimension ref="A1:R76"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:18">
@@ -492,55 +492,55 @@
         <v>18</v>
       </c>
       <c r="B2">
-        <v>102.98</v>
+        <v>156.55</v>
       </c>
       <c r="C2">
-        <v>62.56</v>
+        <v>98.11</v>
       </c>
       <c r="D2">
-        <v>2377.32083625102</v>
+        <v>2742.382475148553</v>
       </c>
       <c r="E2">
-        <v>-3050.286540840457</v>
+        <v>5137.801109455178</v>
       </c>
       <c r="F2">
-        <v>2.748859081039612</v>
+        <v>97.90222834493665</v>
       </c>
       <c r="G2">
-        <v>20.840000152588</v>
+        <v>14.609999656677</v>
       </c>
       <c r="H2">
-        <v>9.9020746549891</v>
+        <v>4.962646844070811</v>
       </c>
       <c r="I2">
-        <v>21.22463967852851</v>
+        <v>20.92551262276611</v>
       </c>
       <c r="J2">
-        <v>48425.79727508202</v>
+        <v>15218.92326735403</v>
       </c>
       <c r="K2">
-        <v>-2179.036907085044</v>
+        <v>-612.2169287706906</v>
       </c>
       <c r="L2">
-        <v>0.2298293414006464</v>
+        <v>0.1640454856939666</v>
       </c>
       <c r="M2">
-        <v>57.56</v>
+        <v>92.91</v>
       </c>
       <c r="N2">
-        <v>1.223946562398151</v>
+        <v>97.90624041879839</v>
       </c>
       <c r="O2">
-        <v>10.7355162601013</v>
+        <v>4.965948916814201</v>
       </c>
       <c r="P2">
-        <v>22.11347723644985</v>
+        <v>20.92881510448303</v>
       </c>
       <c r="Q2">
-        <v>-2362.442918523732</v>
+        <v>-612.6242889752458</v>
       </c>
       <c r="R2">
-        <v>0.1253417793840787</v>
+        <v>0.1613815434361256</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -548,55 +548,55 @@
         <v>18</v>
       </c>
       <c r="B3">
-        <v>196.28</v>
+        <v>121.67</v>
       </c>
       <c r="C3">
-        <v>110.19</v>
+        <v>75.73999999999999</v>
       </c>
       <c r="D3">
-        <v>1984.009613091984</v>
+        <v>305.821812508728</v>
       </c>
       <c r="E3">
-        <v>4908.107531726183</v>
+        <v>1324.523078158547</v>
       </c>
       <c r="F3">
-        <v>4.88707161375546</v>
+        <v>36.2592168130079</v>
       </c>
       <c r="G3">
-        <v>32.12505770952285</v>
+        <v>17.94418885050569</v>
       </c>
       <c r="H3">
-        <v>16.17567064198671</v>
+        <v>6.754473738535239</v>
       </c>
       <c r="I3">
-        <v>27.40903132099251</v>
+        <v>22.6699541577188</v>
       </c>
       <c r="J3">
-        <v>43586.4013606754</v>
+        <v>14407.39558399621</v>
       </c>
       <c r="K3">
-        <v>-3377.052423011561</v>
+        <v>-810.7449605648585</v>
       </c>
       <c r="L3">
-        <v>0.1638346036939383</v>
+        <v>0.1386375578472106</v>
       </c>
       <c r="M3">
-        <v>105.19</v>
+        <v>70.53999999999999</v>
       </c>
       <c r="N3">
-        <v>5.81184867112099</v>
+        <v>36.25128594442901</v>
       </c>
       <c r="O3">
-        <v>16.96680989438042</v>
+        <v>6.757693478585729</v>
       </c>
       <c r="P3">
-        <v>28.25513009154916</v>
+        <v>22.67317430552879</v>
       </c>
       <c r="Q3">
-        <v>-3542.221384989608</v>
+        <v>-811.1314285742567</v>
       </c>
       <c r="R3">
-        <v>0.1492851598307607</v>
+        <v>0.1362502443822662</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -604,55 +604,55 @@
         <v>18</v>
       </c>
       <c r="B4">
-        <v>94.59</v>
+        <v>233.82</v>
       </c>
       <c r="C4">
-        <v>58.31</v>
+        <v>143.77</v>
       </c>
       <c r="D4">
-        <v>3265.868437454711</v>
+        <v>16805.94928255047</v>
       </c>
       <c r="E4">
-        <v>-3332.286887794231</v>
+        <v>18638.02101289747</v>
       </c>
       <c r="F4">
-        <v>4.157448545031228</v>
+        <v>212.5168400416074</v>
       </c>
       <c r="G4">
-        <v>43.41011526645769</v>
+        <v>21.27837804433438</v>
       </c>
       <c r="H4">
-        <v>22.44555813639322</v>
+        <v>8.545468753367407</v>
       </c>
       <c r="I4">
-        <v>33.59713145604758</v>
+        <v>24.41522757230374</v>
       </c>
       <c r="J4">
-        <v>39001.71049439544</v>
+        <v>13618.10153579889</v>
       </c>
       <c r="K4">
-        <v>-4432.739770667679</v>
+        <v>-997.227335078741</v>
       </c>
       <c r="L4">
-        <v>0.1114445028195387</v>
+        <v>0.1159319995731741</v>
       </c>
       <c r="M4">
-        <v>53.31</v>
+        <v>138.57</v>
       </c>
       <c r="N4">
-        <v>2.11912849895872</v>
+        <v>212.578387318613</v>
       </c>
       <c r="O4">
-        <v>23.19437689216907</v>
+        <v>8.548606160703683</v>
       </c>
       <c r="P4">
-        <v>34.40050958313893</v>
+        <v>24.41836538622812</v>
       </c>
       <c r="Q4">
-        <v>-4580.622868943928</v>
+        <v>-997.5934599160447</v>
       </c>
       <c r="R4">
-        <v>0.1722131390472899</v>
+        <v>0.1138053445237268</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -660,55 +660,55 @@
         <v>18</v>
       </c>
       <c r="B5">
-        <v>35.7</v>
+        <v>92.25</v>
       </c>
       <c r="C5">
-        <v>22.88</v>
+        <v>55.06</v>
       </c>
       <c r="D5">
-        <v>13464.76573458049</v>
+        <v>142.3783086422251</v>
       </c>
       <c r="E5">
-        <v>-2654.94434204651</v>
+        <v>-656.9890357088775</v>
       </c>
       <c r="F5">
-        <v>0.7842975096314581</v>
+        <v>0.8894553595434637</v>
       </c>
       <c r="G5">
-        <v>54.69517282339254</v>
+        <v>24.61256723816307</v>
       </c>
       <c r="H5">
-        <v>28.71165499502634</v>
+        <v>10.33562467848846</v>
       </c>
       <c r="I5">
-        <v>39.78902222687607</v>
+        <v>26.1613400765998</v>
       </c>
       <c r="J5">
-        <v>34671.72467624215</v>
+        <v>12851.04112276206</v>
       </c>
       <c r="K5">
-        <v>-5346.209206366509</v>
+        <v>-1171.671555892501</v>
       </c>
       <c r="L5">
-        <v>0.07112454490776596</v>
+        <v>0.09577428749833727</v>
       </c>
       <c r="M5">
-        <v>17.88</v>
+        <v>49.86</v>
       </c>
       <c r="N5">
-        <v>2.858651938974712</v>
+        <v>0.8868447474376222</v>
       </c>
       <c r="O5">
-        <v>29.41813470839721</v>
+        <v>10.33867975308902</v>
       </c>
       <c r="P5">
-        <v>40.54969825628923</v>
+        <v>26.16439555666006</v>
       </c>
       <c r="Q5">
-        <v>-5477.758166131761</v>
+        <v>-1172.017886580966</v>
       </c>
       <c r="R5">
-        <v>0.1934133613855542</v>
+        <v>0.09389268737382717</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -716,55 +716,55 @@
         <v>18</v>
       </c>
       <c r="B6">
-        <v>90.70999999999999</v>
+        <v>182.31</v>
       </c>
       <c r="C6">
-        <v>53.42</v>
+        <v>110.99</v>
       </c>
       <c r="D6">
-        <v>3724.389588428528</v>
+        <v>6103.947162694477</v>
       </c>
       <c r="E6">
-        <v>-3260.103857348102</v>
+        <v>8671.400281341657</v>
       </c>
       <c r="F6">
-        <v>0.5032211749185612</v>
+        <v>83.06356980676534</v>
       </c>
       <c r="G6">
-        <v>65.98023038032738</v>
+        <v>27.94675643199175</v>
       </c>
       <c r="H6">
-        <v>34.9738845782874</v>
+        <v>12.12493448946485</v>
       </c>
       <c r="I6">
-        <v>45.9847802730766</v>
+        <v>27.90829869504053</v>
       </c>
       <c r="J6">
-        <v>30596.44390621552</v>
+        <v>12106.21434488571</v>
       </c>
       <c r="K6">
-        <v>-6117.575657061318</v>
+        <v>-1334.085243171596</v>
       </c>
       <c r="L6">
-        <v>0.04137885698653937</v>
+        <v>0.07801220599058833</v>
       </c>
       <c r="M6">
-        <v>48.42</v>
+        <v>105.79</v>
       </c>
       <c r="N6">
-        <v>1.708927960917981</v>
+        <v>83.07886089739996</v>
       </c>
       <c r="O6">
-        <v>35.6380063285049</v>
+        <v>12.12790723130802</v>
       </c>
       <c r="P6">
-        <v>46.70277312555996</v>
+        <v>27.91127184125835</v>
       </c>
       <c r="Q6">
-        <v>-6233.742765789579</v>
+        <v>-1334.412328734672</v>
       </c>
       <c r="R6">
-        <v>0.2122480037550166</v>
+        <v>0.07636043004021852</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -772,55 +772,55 @@
         <v>18</v>
       </c>
       <c r="B7">
-        <v>172.76</v>
+        <v>39.85</v>
       </c>
       <c r="C7">
-        <v>100.26</v>
+        <v>25.77</v>
       </c>
       <c r="D7">
-        <v>441.9338519848084</v>
+        <v>4138.6368727957</v>
       </c>
       <c r="E7">
-        <v>2107.688059196543</v>
+        <v>-1657.841778609113</v>
       </c>
       <c r="F7">
-        <v>0.7083271669301493</v>
+        <v>0.312431265937239</v>
       </c>
       <c r="G7">
-        <v>77.26528793726223</v>
+        <v>31.28094562582044</v>
       </c>
       <c r="H7">
-        <v>41.23217647208939</v>
+        <v>13.9133913576238</v>
       </c>
       <c r="I7">
-        <v>52.18447600873621</v>
+        <v>29.65611025629869</v>
       </c>
       <c r="J7">
-        <v>26775.86818431555</v>
+        <v>11383.62120216985</v>
       </c>
       <c r="K7">
-        <v>-6746.958527935734</v>
+        <v>-1484.476131651159</v>
       </c>
       <c r="L7">
-        <v>0.02075953889376583</v>
+        <v>0.06249601804005545</v>
       </c>
       <c r="M7">
-        <v>95.26000000000001</v>
+        <v>20.57</v>
       </c>
       <c r="N7">
-        <v>0.3056941767257401</v>
+        <v>0.3154333372942313</v>
       </c>
       <c r="O7">
-        <v>41.85392099390231</v>
+        <v>13.91628176668773</v>
       </c>
       <c r="P7">
-        <v>52.85980494954097</v>
+        <v>29.65900106869592</v>
       </c>
       <c r="Q7">
-        <v>-6848.696657294066</v>
+        <v>-1484.784521112494</v>
       </c>
       <c r="R7">
-        <v>0.2281617626601283</v>
+        <v>0.06105921401135125</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -828,55 +828,55 @@
         <v>18</v>
       </c>
       <c r="B8">
-        <v>79.28</v>
+        <v>145.4</v>
       </c>
       <c r="C8">
-        <v>51.57</v>
+        <v>87.65000000000001</v>
       </c>
       <c r="D8">
-        <v>5250.12947493129</v>
+        <v>1698.903887177393</v>
       </c>
       <c r="E8">
-        <v>-3736.647569551509</v>
+        <v>3612.736821106374</v>
       </c>
       <c r="F8">
-        <v>14.05962469702511</v>
+        <v>28.59518145360893</v>
       </c>
       <c r="G8">
-        <v>88.55034549419707</v>
+        <v>34.61513481964914</v>
       </c>
       <c r="H8">
-        <v>47.48646718137286</v>
+        <v>15.70098866008043</v>
       </c>
       <c r="I8">
-        <v>58.38817292891434</v>
+        <v>31.40478138325918</v>
       </c>
       <c r="J8">
-        <v>23209.99751054226</v>
+        <v>10683.26169461447</v>
       </c>
       <c r="K8">
-        <v>-7234.481456783412</v>
+        <v>-1622.852068408875</v>
       </c>
       <c r="L8">
-        <v>0.007875970718547069</v>
+        <v>0.04907863588228991</v>
       </c>
       <c r="M8">
-        <v>46.57</v>
+        <v>82.45</v>
       </c>
       <c r="N8">
-        <v>9.663835621446891</v>
+        <v>28.59440506550794</v>
       </c>
       <c r="O8">
-        <v>48.06581489887873</v>
+        <v>15.70379673634309</v>
       </c>
       <c r="P8">
-        <v>59.02085753394299</v>
+        <v>31.40758986185784</v>
       </c>
       <c r="Q8">
-        <v>-7322.744083340101</v>
+        <v>-1623.142310792318</v>
       </c>
       <c r="R8">
-        <v>0.2406893917805031</v>
+        <v>0.04784233567480523</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -884,55 +884,55 @@
         <v>18</v>
       </c>
       <c r="B9">
-        <v>107.4</v>
+        <v>32.94</v>
       </c>
       <c r="C9">
-        <v>67.56</v>
+        <v>24.39</v>
       </c>
       <c r="D9">
-        <v>1965.838485914868</v>
+        <v>5075.456504824337</v>
       </c>
       <c r="E9">
-        <v>-2995.460226777194</v>
+        <v>-1737.598189882665</v>
       </c>
       <c r="F9">
-        <v>17.79378964254533</v>
+        <v>2.977163377147809</v>
       </c>
       <c r="G9">
-        <v>99.83540305113192</v>
+        <v>37.94932401347783</v>
       </c>
       <c r="H9">
-        <v>53.73670078057049</v>
+        <v>17.48771998964575</v>
       </c>
       <c r="I9">
-        <v>64.59592695917831</v>
+        <v>33.15431848311098</v>
       </c>
       <c r="J9">
-        <v>19898.83188489562</v>
+        <v>10005.13582221959</v>
       </c>
       <c r="K9">
-        <v>-7580.272015356536</v>
+        <v>-1749.221010425364</v>
       </c>
       <c r="L9">
-        <v>0.001403905946059814</v>
+        <v>0.03761579088474933</v>
       </c>
       <c r="M9">
-        <v>62.56</v>
+        <v>19.19</v>
       </c>
       <c r="N9">
-        <v>13.56651727743668</v>
+        <v>2.967337689541814</v>
       </c>
       <c r="O9">
-        <v>54.27363184424946</v>
+        <v>17.49044573308497</v>
       </c>
       <c r="P9">
-        <v>65.18598707795067</v>
+        <v>33.15704462793326</v>
       </c>
       <c r="Q9">
-        <v>-7656.01323982808</v>
+        <v>-1749.493654754969</v>
       </c>
       <c r="R9">
-        <v>0.249462619854795</v>
+        <v>0.03656591608835192</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -940,55 +940,55 @@
         <v>18</v>
       </c>
       <c r="B10">
-        <v>202.3</v>
+        <v>48.49</v>
       </c>
       <c r="C10">
-        <v>124.9</v>
+        <v>39.72</v>
       </c>
       <c r="D10">
-        <v>2556.538375756322</v>
+        <v>3101.625396568868</v>
       </c>
       <c r="E10">
-        <v>6315.221629300304</v>
+        <v>-2212.095701604733</v>
       </c>
       <c r="F10">
-        <v>84.20776212045369</v>
+        <v>77.60230456945912</v>
       </c>
       <c r="G10">
-        <v>111.1204606080668</v>
+        <v>41.28351320730652</v>
       </c>
       <c r="H10">
-        <v>59.9828295064279</v>
+        <v>19.27357916458453</v>
       </c>
       <c r="I10">
-        <v>70.80778586278251</v>
+        <v>34.90472773758933</v>
       </c>
       <c r="J10">
-        <v>16842.37130737565</v>
+        <v>9349.243584985194</v>
       </c>
       <c r="K10">
-        <v>-7784.461359190249</v>
+        <v>-1863.591021931824</v>
       </c>
       <c r="L10">
-        <v>9.417395849304534E-05</v>
+        <v>0.02796620220424311</v>
       </c>
       <c r="M10">
-        <v>119.9</v>
+        <v>34.52</v>
       </c>
       <c r="N10">
-        <v>80.98300690996652</v>
+        <v>77.55886964477246</v>
       </c>
       <c r="O10">
-        <v>60.47732383307718</v>
+        <v>19.27622257517794</v>
       </c>
       <c r="P10">
-        <v>71.35524157850139</v>
+        <v>34.90737154865758</v>
       </c>
       <c r="Q10">
-        <v>-7848.63592397512</v>
+        <v>-1863.846617231851</v>
       </c>
       <c r="R10">
-        <v>0.2542162821323711</v>
+        <v>0.02708906951142533</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -996,55 +996,55 @@
         <v>18</v>
       </c>
       <c r="B11">
-        <v>58.33</v>
+        <v>14.609999656677</v>
       </c>
       <c r="C11">
-        <v>35.63</v>
+        <v>10.710000038147</v>
       </c>
       <c r="D11">
-        <v>8725.01283908115</v>
+        <v>8023.18591901832</v>
       </c>
       <c r="E11">
-        <v>-3328.11910118519</v>
+        <v>-959.3186782969904</v>
       </c>
       <c r="F11">
-        <v>0.3926876124277968</v>
+        <v>4.991112084824217</v>
       </c>
       <c r="G11">
-        <v>122.4055181650016</v>
+        <v>44.61770240113521</v>
       </c>
       <c r="H11">
-        <v>66.22481427918164</v>
+        <v>21.05856023819116</v>
       </c>
       <c r="I11">
-        <v>77.02378871949033</v>
+        <v>36.65601509339981</v>
       </c>
       <c r="J11">
-        <v>14040.61577798234</v>
+        <v>8715.584982911289</v>
       </c>
       <c r="K11">
-        <v>-7847.183828797787</v>
+        <v>-1965.970271545488</v>
       </c>
       <c r="L11">
-        <v>0.002780814997462076</v>
+        <v>0.01999174371212874</v>
       </c>
       <c r="M11">
-        <v>30.63</v>
+        <v>5.510000038146999</v>
       </c>
       <c r="N11">
-        <v>1.813143719034177</v>
+        <v>5.005878090875219</v>
       </c>
       <c r="O11">
-        <v>66.67685159439962</v>
+        <v>21.06112131591628</v>
       </c>
       <c r="P11">
-        <v>77.52866030655737</v>
+        <v>36.65857657073652</v>
       </c>
       <c r="Q11">
-        <v>-7900.747133559017</v>
+        <v>-1966.209366840406</v>
       </c>
       <c r="R11">
-        <v>0.2547935086537483</v>
+        <v>0.01927407019373909</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -1052,55 +1052,55 @@
         <v>18</v>
       </c>
       <c r="B12">
-        <v>312.6</v>
+        <v>17.920000076294</v>
       </c>
       <c r="C12">
-        <v>171.5</v>
+        <v>12.319999694824</v>
       </c>
       <c r="D12">
-        <v>25876.65472822748</v>
+        <v>7441.173727417196</v>
       </c>
       <c r="E12">
-        <v>27587.87121236992</v>
+        <v>-1062.750747452172</v>
       </c>
       <c r="F12">
-        <v>26.0673820631274</v>
+        <v>5.661481767940387</v>
       </c>
       <c r="G12">
-        <v>133.6905757219365</v>
+        <v>47.9518915949639</v>
       </c>
       <c r="H12">
-        <v>72.46262513925232</v>
+        <v>22.84265750815196</v>
       </c>
       <c r="I12">
-        <v>83.24396548888124</v>
+        <v>38.40818625285614</v>
       </c>
       <c r="J12">
-        <v>11493.5652967157</v>
+        <v>8104.160015997865</v>
       </c>
       <c r="K12">
-        <v>-7768.576506519023</v>
+        <v>-2056.367029194269</v>
       </c>
       <c r="L12">
-        <v>0.008388476652801321</v>
+        <v>0.01355760867538342</v>
       </c>
       <c r="M12">
-        <v>166.5</v>
+        <v>7.119999694824</v>
       </c>
       <c r="N12">
-        <v>23.69206920462658</v>
+        <v>5.676817966756909</v>
       </c>
       <c r="O12">
-        <v>72.87218502205933</v>
+        <v>22.84513625298614</v>
       </c>
       <c r="P12">
-        <v>83.70627336827609</v>
+        <v>38.41066539648396</v>
       </c>
       <c r="Q12">
-        <v>-7812.484621598664</v>
+        <v>-2056.59017350876</v>
       </c>
       <c r="R12">
-        <v>0.2511498291939754</v>
+        <v>0.01298651690926945</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -1108,55 +1108,55 @@
         <v>18</v>
       </c>
       <c r="B13">
-        <v>127.6</v>
+        <v>96.98999786377</v>
       </c>
       <c r="C13">
-        <v>66.86</v>
+        <v>59.290000915527</v>
       </c>
       <c r="D13">
-        <v>582.6322875460318</v>
+        <v>51.72832116300348</v>
       </c>
       <c r="E13">
-        <v>-1613.851782746052</v>
+        <v>-426.4279365686712</v>
       </c>
       <c r="F13">
-        <v>58.23965039185672</v>
+        <v>7.072780697682392</v>
       </c>
       <c r="G13">
-        <v>144.9756332788713</v>
+        <v>51.2860807887926</v>
       </c>
       <c r="H13">
-        <v>78.69624158831694</v>
+        <v>24.62586552566153</v>
       </c>
       <c r="I13">
-        <v>89.46833666927823</v>
+        <v>40.16124666476368</v>
       </c>
       <c r="J13">
-        <v>9201.219863575725</v>
+        <v>7514.968684244936</v>
       </c>
       <c r="K13">
-        <v>-7548.778734628141</v>
+        <v>-2134.789662832815</v>
       </c>
       <c r="L13">
-        <v>0.0159389135817621</v>
+        <v>0.008532471675788614</v>
       </c>
       <c r="M13">
-        <v>61.86</v>
+        <v>54.090000915527</v>
       </c>
       <c r="N13">
-        <v>65.45413612262057</v>
+        <v>7.066037812948337</v>
       </c>
       <c r="O13">
-        <v>79.06330351744471</v>
+        <v>24.628261937582</v>
       </c>
       <c r="P13">
-        <v>89.88810136226913</v>
+        <v>40.1636434747054</v>
       </c>
       <c r="Q13">
-        <v>-7583.988412104056</v>
+        <v>-2134.997405191775</v>
       </c>
       <c r="R13">
-        <v>0.2433560775324694</v>
+        <v>0.008095494717937005</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -1164,55 +1164,55 @@
         <v>18</v>
       </c>
       <c r="B14">
-        <v>100.9</v>
+        <v>67.889999389648</v>
       </c>
       <c r="C14">
-        <v>58.73</v>
+        <v>44.590000152588</v>
       </c>
       <c r="D14">
-        <v>2584.479589350386</v>
+        <v>1317.126598417181</v>
       </c>
       <c r="E14">
-        <v>-2985.702654212916</v>
+        <v>-1618.270934428961</v>
       </c>
       <c r="F14">
-        <v>1.048448243788287</v>
+        <v>11.50103691132338</v>
       </c>
       <c r="G14">
-        <v>156.2606908358061</v>
+        <v>54.62026998262129</v>
       </c>
       <c r="H14">
-        <v>84.92565282582993</v>
+        <v>26.40817910426169</v>
       </c>
       <c r="I14">
-        <v>95.69691306122684</v>
+        <v>41.91520151558063</v>
       </c>
       <c r="J14">
-        <v>7163.579478562413</v>
+        <v>6948.010987652488</v>
       </c>
       <c r="K14">
-        <v>-7187.931601498165</v>
+        <v>-2201.246634953045</v>
       </c>
       <c r="L14">
-        <v>0.02455645125316587</v>
+        <v>0.00478864724625395</v>
       </c>
       <c r="M14">
-        <v>53.73</v>
+        <v>39.39000015258799</v>
       </c>
       <c r="N14">
-        <v>2.507225075212685</v>
+        <v>11.48756647656693</v>
       </c>
       <c r="O14">
-        <v>85.25019622716827</v>
+        <v>26.41049318324552</v>
       </c>
       <c r="P14">
-        <v>96.07415514192401</v>
+        <v>41.91751599185915</v>
       </c>
       <c r="Q14">
-        <v>-7215.400283726864</v>
+        <v>-2201.439524381585</v>
       </c>
       <c r="R14">
-        <v>0.2316000060651398</v>
+        <v>0.004473733434117001</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -1220,55 +1220,55 @@
         <v>18</v>
       </c>
       <c r="B15">
-        <v>24.93</v>
+        <v>193.559997558594</v>
       </c>
       <c r="C15">
-        <v>16.92</v>
+        <v>130.360000610352</v>
       </c>
       <c r="D15">
-        <v>16080.21235519596</v>
+        <v>7988.383866609322</v>
       </c>
       <c r="E15">
-        <v>-2145.587590009919</v>
+        <v>11651.28476355121</v>
       </c>
       <c r="F15">
-        <v>0.8116340526826602</v>
+        <v>507.0604360065518</v>
       </c>
       <c r="G15">
-        <v>167.545748392741</v>
+        <v>57.95445917644998</v>
       </c>
       <c r="H15">
-        <v>91.15085787468156</v>
+        <v>28.18959332837105</v>
       </c>
       <c r="I15">
-        <v>101.9296956418368</v>
+        <v>43.6700557208884</v>
       </c>
       <c r="J15">
-        <v>5380.644141675764</v>
+        <v>6403.286926220535</v>
       </c>
       <c r="K15">
-        <v>-6686.177403618485</v>
+        <v>-2255.74649889312</v>
       </c>
       <c r="L15">
-        <v>0.03347229941010008</v>
+        <v>0.002202244702911928</v>
       </c>
       <c r="M15">
-        <v>11.92</v>
+        <v>125.160000610352</v>
       </c>
       <c r="N15">
-        <v>3.050738591967054</v>
+        <v>507.1107267682269</v>
       </c>
       <c r="O15">
-        <v>91.43286216933971</v>
+        <v>28.1918250743952</v>
       </c>
       <c r="P15">
-        <v>102.264435689131</v>
+        <v>43.67228786352675</v>
       </c>
       <c r="Q15">
-        <v>-6706.863229145866</v>
+        <v>-2255.92508441657</v>
       </c>
       <c r="R15">
-        <v>0.216186554524108</v>
+        <v>0.001997762280810041</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -1276,55 +1276,55 @@
         <v>18</v>
       </c>
       <c r="B16">
-        <v>70.91</v>
+        <v>70.56999969482401</v>
       </c>
       <c r="C16">
-        <v>49.13</v>
+        <v>45.270000457764</v>
       </c>
       <c r="D16">
-        <v>6533.129565047488</v>
+        <v>1129.782577837814</v>
       </c>
       <c r="E16">
-        <v>-3971.068693214381</v>
+        <v>-1521.626052858544</v>
       </c>
       <c r="F16">
-        <v>35.16005078187658</v>
+        <v>7.023045993275507</v>
       </c>
       <c r="G16">
-        <v>178.8308059496758</v>
+        <v>61.28864837027867</v>
       </c>
       <c r="H16">
-        <v>97.37186559260125</v>
+        <v>29.97010356147428</v>
       </c>
       <c r="I16">
-        <v>108.1666755533787</v>
+        <v>45.42581391720229</v>
       </c>
       <c r="J16">
-        <v>3852.413852915781</v>
+        <v>5880.796499949064</v>
       </c>
       <c r="K16">
-        <v>-6043.659092012444</v>
+        <v>-2298.297894949665</v>
       </c>
       <c r="L16">
-        <v>0.0420276306215713</v>
+        <v>0.0006533186542947888</v>
       </c>
       <c r="M16">
-        <v>44.13</v>
+        <v>40.070000457764</v>
       </c>
       <c r="N16">
-        <v>27.63718996810901</v>
+        <v>7.012871056480323</v>
       </c>
       <c r="O16">
-        <v>97.61131024502517</v>
+        <v>29.97225297451559</v>
       </c>
       <c r="P16">
-        <v>108.458934102824</v>
+        <v>45.42796372622366</v>
       </c>
       <c r="Q16">
-        <v>-6058.520898776116</v>
+        <v>-2298.46272559358</v>
       </c>
       <c r="R16">
-        <v>0.1975367522673981</v>
+        <v>0.0005480602110157035</v>
       </c>
     </row>
     <row r="17" spans="1:18">
@@ -1332,55 +1332,55 @@
         <v>18</v>
       </c>
       <c r="B17">
-        <v>319.549987792969</v>
+        <v>101.110000610352</v>
       </c>
       <c r="C17">
-        <v>209.050003051758</v>
+        <v>70.80999755859401</v>
       </c>
       <c r="D17">
-        <v>28160.93802834547</v>
+        <v>9.438643853767987</v>
       </c>
       <c r="E17">
-        <v>35081.14313922744</v>
+        <v>-217.5451367585213</v>
       </c>
       <c r="F17">
-        <v>818.4295447895945</v>
+        <v>143.870723726105</v>
       </c>
       <c r="G17">
-        <v>190.1158635066107</v>
+        <v>64.62283756410736</v>
       </c>
       <c r="H17">
-        <v>103.5886945689971</v>
+        <v>31.74970545394047</v>
       </c>
       <c r="I17">
-        <v>114.4078342064445</v>
+        <v>47.1824804541532</v>
       </c>
       <c r="J17">
-        <v>2578.888612282462</v>
+        <v>5380.539708838087</v>
       </c>
       <c r="K17">
-        <v>-5260.519712064926</v>
+        <v>-2328.909546298984</v>
       </c>
       <c r="L17">
-        <v>0.04967537239241795</v>
+        <v>2.6014674542777E-05</v>
       </c>
       <c r="M17">
-        <v>204.050003051758</v>
+        <v>65.609997558594</v>
       </c>
       <c r="N17">
-        <v>833.6251185092335</v>
+        <v>143.8427470172252</v>
       </c>
       <c r="O17">
-        <v>103.7855591345818</v>
+        <v>31.75177253397569</v>
       </c>
       <c r="P17">
-        <v>114.6576317026457</v>
+        <v>47.18454792958085</v>
       </c>
       <c r="Q17">
-        <v>-5270.517037855878</v>
+        <v>-2329.06117108914</v>
       </c>
       <c r="R17">
-        <v>0.1761852705639047</v>
+        <v>9.201383502621551E-06</v>
       </c>
     </row>
     <row r="18" spans="1:18">
@@ -1388,55 +1388,55 @@
         <v>18</v>
       </c>
       <c r="B18">
-        <v>87.389999389648</v>
+        <v>129.059997558594</v>
       </c>
       <c r="C18">
-        <v>51.990001678467</v>
+        <v>81.459999084473</v>
       </c>
       <c r="D18">
-        <v>4140.636507502104</v>
+        <v>618.9029103273962</v>
       </c>
       <c r="E18">
-        <v>-3345.441075708017</v>
+        <v>2026.542253958047</v>
       </c>
       <c r="F18">
-        <v>0.09415332170862969</v>
+        <v>61.19331642464389</v>
       </c>
       <c r="G18">
-        <v>201.4009210635455</v>
+        <v>67.95702675793605</v>
       </c>
       <c r="H18">
-        <v>109.8013729100198</v>
+        <v>33.5283949504411</v>
       </c>
       <c r="I18">
-        <v>120.6531434948833</v>
+        <v>48.94005938706969</v>
       </c>
       <c r="J18">
-        <v>1560.068419775808</v>
+        <v>4902.516552887594</v>
       </c>
       <c r="K18">
-        <v>-4336.901845920123</v>
+        <v>-2347.590254733801</v>
       </c>
       <c r="L18">
-        <v>0.05598069623610943</v>
+        <v>0.0002087096364081436</v>
       </c>
       <c r="M18">
-        <v>46.990001678467</v>
+        <v>76.25999908447299</v>
       </c>
       <c r="N18">
-        <v>0.8413151306761635</v>
+        <v>61.18586812753796</v>
       </c>
       <c r="O18">
-        <v>109.9556370816707</v>
+        <v>33.53037969744683</v>
       </c>
       <c r="P18">
-        <v>120.8605002449353</v>
+        <v>48.94204452892698</v>
       </c>
       <c r="Q18">
-        <v>-4342.994926116307</v>
+        <v>-2347.729222696199</v>
       </c>
       <c r="R18">
-        <v>0.1527766777432548</v>
+        <v>0.0002699952890637222</v>
       </c>
     </row>
     <row r="19" spans="1:18">
@@ -1444,55 +1444,55 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>42.080001831055</v>
+        <v>34.22598169875913</v>
       </c>
       <c r="C19">
-        <v>27.079999923706</v>
+        <v>22.62598169875913</v>
       </c>
       <c r="D19">
-        <v>12024.8276960911</v>
+        <v>4893.87782472673</v>
       </c>
       <c r="E19">
-        <v>-2969.53254828217</v>
+        <v>-1582.828979482084</v>
       </c>
       <c r="F19">
-        <v>0.04291710799402142</v>
+        <v>0.5191689938609473</v>
       </c>
       <c r="G19">
-        <v>212.6859786204804</v>
+        <v>71.29121595176474</v>
       </c>
       <c r="H19">
-        <v>116.0099379176039</v>
+        <v>35.30616829693878</v>
       </c>
       <c r="I19">
-        <v>126.9025661167609</v>
+        <v>50.69855446998913</v>
       </c>
       <c r="J19">
-        <v>795.9532753958177</v>
+        <v>4446.72703209759</v>
       </c>
       <c r="K19">
-        <v>-3272.947066441477</v>
+        <v>-2354.348896223004</v>
       </c>
       <c r="L19">
-        <v>0.06062022219138373</v>
+        <v>0.001094146211722599</v>
       </c>
       <c r="M19">
-        <v>22.079999923706</v>
+        <v>17.42598169875913</v>
       </c>
       <c r="N19">
-        <v>0.9766866368569316</v>
+        <v>0.5232377002086762</v>
       </c>
       <c r="O19">
-        <v>116.1215815707267</v>
+        <v>35.30807071089154</v>
       </c>
       <c r="P19">
-        <v>127.0675022452577</v>
+        <v>50.70045727829957</v>
       </c>
       <c r="Q19">
-        <v>-3276.09682906987</v>
+        <v>-2354.475756383873</v>
       </c>
       <c r="R19">
-        <v>0.1280604842439406</v>
+        <v>0.001223621035270405</v>
       </c>
     </row>
     <row r="20" spans="1:18">
@@ -1500,55 +1500,55 @@
         <v>18</v>
       </c>
       <c r="B20">
-        <v>65.330001831055</v>
+        <v>100.9447398432487</v>
       </c>
       <c r="C20">
-        <v>39.830001831055</v>
+        <v>56.67622390165465</v>
       </c>
       <c r="D20">
-        <v>7466.303642023503</v>
+        <v>10.48139565899172</v>
       </c>
       <c r="E20">
-        <v>-3441.621850658518</v>
+        <v>-183.4891821775902</v>
       </c>
       <c r="F20">
-        <v>0.08434671569162262</v>
+        <v>4.208746269631753</v>
       </c>
       <c r="G20">
-        <v>223.9710361774152</v>
+        <v>74.62540514559343</v>
       </c>
       <c r="H20">
-        <v>122.2144356709254</v>
+        <v>37.08302204721964</v>
       </c>
       <c r="I20">
-        <v>133.156055992901</v>
+        <v>52.45796914912539</v>
       </c>
       <c r="J20">
-        <v>286.5431791424922</v>
+        <v>4013.171146468074</v>
       </c>
       <c r="K20">
-        <v>-2068.795411252037</v>
+        <v>-2349.194416302661</v>
       </c>
       <c r="L20">
-        <v>0.06337999080047554</v>
+        <v>0.002579561062056676</v>
       </c>
       <c r="M20">
-        <v>34.830001831055</v>
+        <v>51.47622390165465</v>
       </c>
       <c r="N20">
-        <v>0.9681228397038889</v>
+        <v>4.213549669420813</v>
       </c>
       <c r="O20">
-        <v>122.2834389063697</v>
+        <v>37.08484212809589</v>
       </c>
       <c r="P20">
-        <v>133.2785913989931</v>
+        <v>52.45978962391251</v>
       </c>
       <c r="Q20">
-        <v>-2069.963469477443</v>
+        <v>-2349.309717688461</v>
       </c>
       <c r="R20">
-        <v>0.1028850948805844</v>
+        <v>0.002767755312856658</v>
       </c>
     </row>
     <row r="21" spans="1:18">
@@ -1556,55 +1556,55 @@
         <v>18</v>
       </c>
       <c r="B21">
-        <v>250.683853149414</v>
+        <v>201.2775689479204</v>
       </c>
       <c r="C21">
-        <v>139.483856201172</v>
+        <v>81.83032105706009</v>
       </c>
       <c r="D21">
-        <v>9790.325948291043</v>
+        <v>9427.503251577775</v>
       </c>
       <c r="E21">
-        <v>13801.38023116313</v>
+        <v>7945.342087624201</v>
       </c>
       <c r="F21">
-        <v>8.679017821972542</v>
+        <v>906.2710972309608</v>
       </c>
       <c r="G21">
-        <v>235.2560937343501</v>
+        <v>77.95959433942213</v>
       </c>
       <c r="H21">
-        <v>128.4149205210134</v>
+        <v>38.85895306894344</v>
       </c>
       <c r="I21">
-        <v>139.4135587722746</v>
+        <v>54.21830655681872</v>
       </c>
       <c r="J21">
-        <v>31.8381310158313</v>
+        <v>3601.848895999046</v>
       </c>
       <c r="K21">
-        <v>-724.5848846244047</v>
+        <v>-2332.13582530741</v>
       </c>
       <c r="L21">
-        <v>0.06415228502825564</v>
+        <v>0.004566806260449334</v>
       </c>
       <c r="M21">
-        <v>134.483856201172</v>
+        <v>76.63032105706009</v>
       </c>
       <c r="N21">
-        <v>8.650282864125289</v>
+        <v>906.1923925761039</v>
       </c>
       <c r="O21">
-        <v>128.4412637055426</v>
+        <v>38.86069081671953</v>
       </c>
       <c r="P21">
-        <v>139.4937130891987</v>
+        <v>54.22004469810616</v>
       </c>
       <c r="Q21">
-        <v>-724.7335268012272</v>
+        <v>-2332.240116944829</v>
       </c>
       <c r="R21">
-        <v>0.07819081073534227</v>
+        <v>0.004804693585038598</v>
       </c>
     </row>
     <row r="22" spans="1:18">
@@ -1612,55 +1612,55 @@
         <v>18</v>
       </c>
       <c r="B22">
-        <v>460.957244873047</v>
+        <v>70.31999999999999</v>
       </c>
       <c r="C22">
-        <v>250.057250976563</v>
+        <v>42.54</v>
       </c>
       <c r="D22">
-        <v>95616.6791958274</v>
+        <v>1146.651176426304</v>
       </c>
       <c r="E22">
-        <v>77322.5700379222</v>
+        <v>-1440.499613350085</v>
       </c>
       <c r="F22">
-        <v>71.18069043253089</v>
+        <v>0.002775016157569029</v>
       </c>
       <c r="G22">
-        <v>246.5411512912849</v>
+        <v>81.29378353325082</v>
       </c>
       <c r="H22">
-        <v>134.61145451106</v>
+        <v>40.63395854918684</v>
       </c>
       <c r="I22">
-        <v>145.6750124116895</v>
+        <v>55.97956950599244</v>
       </c>
       <c r="J22">
-        <v>31.83813101583483</v>
+        <v>3212.760280690507</v>
       </c>
       <c r="K22">
-        <v>759.5490059900357</v>
+        <v>-2303.182193452084</v>
       </c>
       <c r="L22">
-        <v>0.06293141069874647</v>
+        <v>0.006962463506261465</v>
       </c>
       <c r="M22">
-        <v>245.057250976563</v>
+        <v>37.34</v>
       </c>
       <c r="N22">
-        <v>58.36505145558106</v>
+        <v>0.002575748058214322</v>
       </c>
       <c r="O22">
-        <v>134.5951183149855</v>
+        <v>40.63561396383906</v>
       </c>
       <c r="P22">
-        <v>145.7128049691342</v>
+        <v>55.98122531380393</v>
       </c>
       <c r="Q22">
-        <v>759.4568285335542</v>
+        <v>-2303.276024368045</v>
       </c>
       <c r="R22">
-        <v>0.05500204200406067</v>
+        <v>0.00724146406230094</v>
       </c>
     </row>
     <row r="23" spans="1:18">
@@ -1668,55 +1668,55 @@
         <v>18</v>
       </c>
       <c r="B23">
-        <v>76.209999084473</v>
+        <v>29.95221198722829</v>
       </c>
       <c r="C23">
-        <v>44.909999847412</v>
+        <v>20.25221198722829</v>
       </c>
       <c r="D23">
-        <v>5704.445265157044</v>
+        <v>5510.096792672814</v>
       </c>
       <c r="E23">
-        <v>-3391.95250307546</v>
+        <v>-1503.322226831901</v>
       </c>
       <c r="F23">
-        <v>1.478267925751405</v>
+        <v>0.6854282080389739</v>
       </c>
       <c r="G23">
-        <v>257.8262088482197</v>
+        <v>84.62797272707951</v>
       </c>
       <c r="H23">
-        <v>140.8041067362444</v>
+        <v>42.40803599945765</v>
       </c>
       <c r="I23">
-        <v>151.9403478159667</v>
+        <v>57.74176048513874</v>
       </c>
       <c r="J23">
-        <v>286.5431791425019</v>
+        <v>2845.905300542455</v>
       </c>
       <c r="K23">
-        <v>2383.473673156991</v>
+        <v>-2262.342645774232</v>
       </c>
       <c r="L23">
-        <v>0.0598085648013368</v>
+        <v>0.009677950719346439</v>
       </c>
       <c r="M23">
-        <v>39.909999847412</v>
+        <v>15.05221198722829</v>
       </c>
       <c r="N23">
-        <v>3.49074418983935</v>
+        <v>0.690277391203326</v>
       </c>
       <c r="O23">
-        <v>140.7450721679276</v>
+        <v>42.40960908096223</v>
       </c>
       <c r="P23">
-        <v>151.9357976055705</v>
+        <v>57.74333395949805</v>
       </c>
       <c r="Q23">
-        <v>2382.474360405035</v>
+        <v>-2262.426564995889</v>
       </c>
       <c r="R23">
-        <v>0.03441890534629645</v>
+        <v>0.009989934049366028</v>
       </c>
     </row>
     <row r="24" spans="1:18">
@@ -1724,55 +1724,55 @@
         <v>18</v>
       </c>
       <c r="B24">
-        <v>27.590000152588</v>
+        <v>64.300003051758</v>
       </c>
       <c r="C24">
-        <v>18.590000152588</v>
+        <v>28.680000305176</v>
       </c>
       <c r="D24">
-        <v>15412.67054267235</v>
+        <v>1590.592681023593</v>
       </c>
       <c r="E24">
-        <v>-2307.90719401964</v>
+        <v>-1143.822516439827</v>
       </c>
       <c r="F24">
-        <v>0.488800804908938</v>
+        <v>112.6759360332276</v>
       </c>
       <c r="G24">
-        <v>269.1112664051545</v>
+        <v>87.9621619209082</v>
       </c>
       <c r="H24">
-        <v>146.9929526575888</v>
+        <v>44.18118326015914</v>
       </c>
       <c r="I24">
-        <v>158.2094895240839</v>
+        <v>59.50488165385437</v>
       </c>
       <c r="J24">
-        <v>795.9532753958322</v>
+        <v>2501.283955554891</v>
       </c>
       <c r="K24">
-        <v>4147.059828011735</v>
+        <v>-2209.62635694881</v>
       </c>
       <c r="L24">
-        <v>0.05496593588997659</v>
+        <v>0.01262962062661774</v>
       </c>
       <c r="M24">
-        <v>13.590000152588</v>
+        <v>23.480000305176</v>
       </c>
       <c r="N24">
-        <v>2.355762687214461</v>
+        <v>112.7199974433888</v>
       </c>
       <c r="O24">
-        <v>146.891201094586</v>
+        <v>44.18267400849223</v>
       </c>
       <c r="P24">
-        <v>158.1626151682905</v>
+        <v>59.50637279478532</v>
       </c>
       <c r="Q24">
-        <v>4144.189147399249</v>
+        <v>-2209.700913503553</v>
       </c>
       <c r="R24">
-        <v>0.01760838468268685</v>
+        <v>0.01296690827795444</v>
       </c>
     </row>
     <row r="25" spans="1:18">
@@ -1780,55 +1780,55 @@
         <v>18</v>
       </c>
       <c r="B25">
-        <v>242.449996948242</v>
+        <v>62.76554666182879</v>
       </c>
       <c r="C25">
-        <v>131.449996948242</v>
+        <v>35.19716323589712</v>
       </c>
       <c r="D25">
-        <v>8228.706813948824</v>
+        <v>1715.342338595181</v>
       </c>
       <c r="E25">
-        <v>11924.12101073784</v>
+        <v>-1457.7500530263</v>
       </c>
       <c r="F25">
-        <v>41.40985672966868</v>
+        <v>10.78466079068451</v>
       </c>
       <c r="G25">
-        <v>280.3963239620894</v>
+        <v>91.29635111473689</v>
       </c>
       <c r="H25">
-        <v>153.1780733845188</v>
+        <v>45.95339850448607</v>
       </c>
       <c r="I25">
-        <v>164.4823564266154</v>
+        <v>61.26893483894457</v>
       </c>
       <c r="J25">
-        <v>1560.068419775826</v>
+        <v>2178.896245727815</v>
       </c>
       <c r="K25">
-        <v>6050.181811116407</v>
+        <v>-2145.042545987048</v>
       </c>
       <c r="L25">
-        <v>0.04867018957082105</v>
+        <v>0.01573885098373788</v>
       </c>
       <c r="M25">
-        <v>126.449996948242</v>
+        <v>29.99716323589712</v>
       </c>
       <c r="N25">
-        <v>41.74700441256261</v>
+        <v>10.79854436936671</v>
       </c>
       <c r="O25">
-        <v>153.0335866012167</v>
+        <v>45.9548069196238</v>
       </c>
       <c r="P25">
-        <v>164.3931761510382</v>
+        <v>61.27034364647104</v>
       </c>
       <c r="Q25">
-        <v>6044.474915286171</v>
+        <v>-2145.108288902505</v>
       </c>
       <c r="R25">
-        <v>0.005795233236646507</v>
+        <v>0.01609421886867671</v>
       </c>
     </row>
     <row r="26" spans="1:18">
@@ -1836,55 +1836,55 @@
         <v>18</v>
       </c>
       <c r="B26">
-        <v>29.979999542236</v>
+        <v>120.7171514266197</v>
       </c>
       <c r="C26">
-        <v>18.979999542236</v>
+        <v>57.82884417099326</v>
       </c>
       <c r="D26">
-        <v>14824.9564170764</v>
+        <v>273.4033551614603</v>
       </c>
       <c r="E26">
-        <v>-2310.962563967888</v>
+        <v>956.1949199252442</v>
       </c>
       <c r="F26">
-        <v>2.651515161109947</v>
+        <v>129.6021422317419</v>
       </c>
       <c r="G26">
-        <v>291.6813815190242</v>
+        <v>94.63054030856559</v>
       </c>
       <c r="H26">
-        <v>159.359554940443</v>
+        <v>47.72468024173616</v>
       </c>
       <c r="I26">
-        <v>170.7588625001528</v>
+        <v>63.0339215311116</v>
       </c>
       <c r="J26">
-        <v>2578.888612282482</v>
+        <v>1878.742171061228</v>
       </c>
       <c r="K26">
-        <v>8092.717873876894</v>
+        <v>-2068.600470832037</v>
       </c>
       <c r="L26">
-        <v>0.04126549490965226</v>
+        <v>0.01893212610668204</v>
       </c>
       <c r="M26">
-        <v>13.979999542236</v>
+        <v>52.62884417099325</v>
       </c>
       <c r="N26">
-        <v>6.027263979794129</v>
+        <v>129.617673250514</v>
       </c>
       <c r="O26">
-        <v>159.1723151320997</v>
+        <v>47.72600632365462</v>
       </c>
       <c r="P26">
-        <v>170.6273941095336</v>
+        <v>63.03524800525751</v>
       </c>
       <c r="Q26">
-        <v>8083.209319813432</v>
+        <v>-2068.657949136071</v>
       </c>
       <c r="R26">
-        <v>0.0002527875503900605</v>
+        <v>0.01929880659736137</v>
       </c>
     </row>
     <row r="27" spans="1:18">
@@ -1892,55 +1892,55 @@
         <v>18</v>
       </c>
       <c r="B27">
-        <v>67.84</v>
+        <v>29.67361600469638</v>
       </c>
       <c r="C27">
-        <v>43.64</v>
+        <v>23.9736160046964</v>
       </c>
       <c r="D27">
-        <v>7038.8370169778</v>
+        <v>5551.534782570749</v>
       </c>
       <c r="E27">
-        <v>-3661.298996455843</v>
+        <v>-1786.24109773072</v>
       </c>
       <c r="F27">
-        <v>4.554526800029939</v>
+        <v>9.249132788540923</v>
       </c>
       <c r="G27">
-        <v>302.966439075959</v>
+        <v>97.96472950239428</v>
       </c>
       <c r="H27">
-        <v>165.5374875248642</v>
+        <v>49.49502732002303</v>
       </c>
       <c r="I27">
-        <v>177.0389175451931</v>
+        <v>64.79984288224185</v>
       </c>
       <c r="J27">
-        <v>3852.413852915803</v>
+        <v>1600.821731555128</v>
       </c>
       <c r="K27">
-        <v>10274.55041001663</v>
+        <v>-1980.309422864113</v>
       </c>
       <c r="L27">
-        <v>0.03316624497142829</v>
+        <v>0.02214110942218309</v>
       </c>
       <c r="M27">
-        <v>38.64</v>
+        <v>18.7736160046964</v>
       </c>
       <c r="N27">
-        <v>2.102743010283889</v>
+        <v>9.231317882203218</v>
       </c>
       <c r="O27">
-        <v>165.3074773280417</v>
+        <v>49.49627106869826</v>
       </c>
       <c r="P27">
-        <v>176.8651784029699</v>
+        <v>64.80108702303116</v>
       </c>
       <c r="Q27">
-        <v>10260.27417931259</v>
+        <v>-1980.359185584827</v>
       </c>
       <c r="R27">
-        <v>0.002293852112812483</v>
+        <v>0.02251279317554691</v>
       </c>
     </row>
     <row r="28" spans="1:18">
@@ -1948,55 +1948,55 @@
         <v>18</v>
       </c>
       <c r="B28">
-        <v>31.84</v>
+        <v>79.76943509032981</v>
       </c>
       <c r="C28">
-        <v>19.78</v>
+        <v>40.66943509032978</v>
       </c>
       <c r="D28">
-        <v>14375.47697446682</v>
+        <v>595.9849560411974</v>
       </c>
       <c r="E28">
-        <v>-2371.578032765733</v>
+        <v>-992.8549117496545</v>
       </c>
       <c r="F28">
-        <v>3.441055302341098</v>
+        <v>46.63470425951216</v>
       </c>
       <c r="G28">
-        <v>314.2514966328938</v>
+        <v>101.298918696223</v>
       </c>
       <c r="H28">
-        <v>171.7119647843776</v>
+        <v>51.26443892837909</v>
       </c>
       <c r="I28">
-        <v>183.3224279151414</v>
+        <v>66.56669970330289</v>
       </c>
       <c r="J28">
-        <v>5380.644141675785</v>
+        <v>1345.134927209516</v>
       </c>
       <c r="K28">
-        <v>12595.56613773945</v>
+        <v>-1880.17872132961</v>
       </c>
       <c r="L28">
-        <v>0.0248496173458238</v>
+        <v>0.02530270678251375</v>
       </c>
       <c r="M28">
-        <v>14.78</v>
+        <v>35.46943509032977</v>
       </c>
       <c r="N28">
-        <v>7.154026713019796</v>
+        <v>46.6578334424367</v>
       </c>
       <c r="O28">
-        <v>171.4391672938061</v>
+        <v>51.26560034378714</v>
       </c>
       <c r="P28">
-        <v>183.106434926584</v>
+        <v>66.56786151075957</v>
       </c>
       <c r="Q28">
-        <v>12575.55565775329</v>
+        <v>-1880.221317495344</v>
       </c>
       <c r="R28">
-        <v>0.01326179717326171</v>
+        <v>0.02567354429118321</v>
       </c>
     </row>
     <row r="29" spans="1:18">
@@ -2004,55 +2004,55 @@
         <v>18</v>
       </c>
       <c r="B29">
-        <v>39.47</v>
+        <v>22.76077641994059</v>
       </c>
       <c r="C29">
-        <v>27.63</v>
+        <v>16.56077641994059</v>
       </c>
       <c r="D29">
-        <v>12604.0537945879</v>
+        <v>6629.454439634612</v>
       </c>
       <c r="E29">
-        <v>-3101.95868368641</v>
+        <v>-1348.402624449689</v>
       </c>
       <c r="F29">
-        <v>3.180778981725064</v>
+        <v>0.4980035784625406</v>
       </c>
       <c r="G29">
-        <v>325.5365541898286</v>
+        <v>104.6331078900517</v>
       </c>
       <c r="H29">
-        <v>177.8830831034738</v>
+        <v>53.03291459823959</v>
       </c>
       <c r="I29">
-        <v>189.6092972255067</v>
+        <v>68.3344924628595</v>
       </c>
       <c r="J29">
-        <v>7163.579478562432</v>
+        <v>1111.681758024393</v>
       </c>
       <c r="K29">
-        <v>15055.65623420794</v>
+        <v>-1768.217707706896</v>
       </c>
       <c r="L29">
-        <v>0.01684810929715163</v>
+        <v>0.02835912032803356</v>
       </c>
       <c r="M29">
-        <v>22.63</v>
+        <v>11.36077641994059</v>
       </c>
       <c r="N29">
-        <v>0.9851149862236884</v>
+        <v>0.5023899137144384</v>
       </c>
       <c r="O29">
-        <v>177.5674818854473</v>
+        <v>53.03399368035647</v>
       </c>
       <c r="P29">
-        <v>189.3510668243211</v>
+        <v>68.33557193700751</v>
       </c>
       <c r="Q29">
-        <v>15028.94439987943</v>
+        <v>-1768.253686346229</v>
       </c>
       <c r="R29">
-        <v>0.03452199342541589</v>
+        <v>0.02872372319369493</v>
       </c>
     </row>
     <row r="30" spans="1:18">
@@ -2060,55 +2060,55 @@
         <v>18</v>
       </c>
       <c r="B30">
-        <v>36.58</v>
+        <v>25.032730102539</v>
       </c>
       <c r="C30">
-        <v>25.38</v>
+        <v>13.332730293274</v>
       </c>
       <c r="D30">
-        <v>13261.31364673076</v>
+        <v>6264.64463326858</v>
       </c>
       <c r="E30">
-        <v>-2922.704385014878</v>
+        <v>-1055.279044409701</v>
       </c>
       <c r="F30">
-        <v>1.273878322957281</v>
+        <v>26.40486234320342</v>
       </c>
       <c r="G30">
-        <v>336.8216117467634</v>
+        <v>107.9672970838804</v>
       </c>
       <c r="H30">
-        <v>184.0509409244641</v>
+        <v>54.8004542043013</v>
       </c>
       <c r="I30">
-        <v>195.899427033978</v>
+        <v>70.10322128621492</v>
       </c>
       <c r="J30">
-        <v>9201.219863575741</v>
+        <v>900.4622239997574</v>
       </c>
       <c r="K30">
-        <v>17654.71642479502</v>
+        <v>-1644.435740023962</v>
       </c>
       <c r="L30">
-        <v>0.009742168064365382</v>
+        <v>0.03125789272056149</v>
       </c>
       <c r="M30">
-        <v>20.38</v>
+        <v>8.132730293274001</v>
       </c>
       <c r="N30">
-        <v>0.1068170587367062</v>
+        <v>26.43616447523478</v>
       </c>
       <c r="O30">
-        <v>183.6925200269084</v>
+        <v>54.80145095310303</v>
       </c>
       <c r="P30">
-        <v>195.5989751722385</v>
+        <v>70.10421842707825</v>
       </c>
       <c r="Q30">
-        <v>17620.33562089756</v>
+        <v>-1644.465650165715</v>
       </c>
       <c r="R30">
-        <v>0.06745368666157765</v>
+        <v>0.03161133464715833</v>
       </c>
     </row>
     <row r="31" spans="1:18">
@@ -2116,55 +2116,55 @@
         <v>18</v>
       </c>
       <c r="B31">
-        <v>83.33</v>
+        <v>75.35563919135829</v>
       </c>
       <c r="C31">
-        <v>44.76</v>
+        <v>48.95563919135829</v>
       </c>
       <c r="D31">
-        <v>4679.623979713776</v>
+        <v>830.9728108415345</v>
       </c>
       <c r="E31">
-        <v>-3061.932106905672</v>
+        <v>-1411.224580551689</v>
       </c>
       <c r="F31">
-        <v>28.04607943156623</v>
+        <v>14.42402527969466</v>
       </c>
       <c r="G31">
-        <v>348.1066693036983</v>
+        <v>111.301486277709</v>
       </c>
       <c r="H31">
-        <v>190.2156381041452</v>
+        <v>56.56705796475232</v>
       </c>
       <c r="I31">
-        <v>202.1927174837585</v>
+        <v>71.87288595518102</v>
       </c>
       <c r="J31">
-        <v>11493.56529671571</v>
+        <v>711.47632513561</v>
       </c>
       <c r="K31">
-        <v>20392.64703022647</v>
+        <v>-1508.842187142059</v>
       </c>
       <c r="L31">
-        <v>0.004153020797467776</v>
+        <v>0.03395194161133768</v>
       </c>
       <c r="M31">
-        <v>39.76</v>
+        <v>43.75563919135828</v>
       </c>
       <c r="N31">
-        <v>35.06464362263272</v>
+        <v>14.4103390390655</v>
       </c>
       <c r="O31">
-        <v>189.8143820635377</v>
+        <v>56.56797238021492</v>
       </c>
       <c r="P31">
-        <v>201.8500596249875</v>
+        <v>71.87380076278365</v>
       </c>
       <c r="Q31">
-        <v>20349.62915384991</v>
+        <v>-1508.866577815292</v>
       </c>
       <c r="R31">
-        <v>0.1134423942789337</v>
+        <v>0.03428975911605813</v>
       </c>
     </row>
     <row r="32" spans="1:18">
@@ -2172,55 +2172,55 @@
         <v>18</v>
       </c>
       <c r="B32">
-        <v>380.579986572266</v>
+        <v>41.68</v>
       </c>
       <c r="C32">
-        <v>218.779998779297</v>
+        <v>26.89</v>
       </c>
       <c r="D32">
-        <v>52368.75679617091</v>
+        <v>3906.529780955989</v>
       </c>
       <c r="E32">
-        <v>50066.09828988411</v>
+        <v>-1680.685185401593</v>
       </c>
       <c r="F32">
-        <v>21.63719548595194</v>
+        <v>0.1676182059175912</v>
       </c>
       <c r="G32">
-        <v>359.3917268606331</v>
+        <v>114.6356754715377</v>
       </c>
       <c r="H32">
-        <v>196.3772753131205</v>
+        <v>58.33272644087201</v>
       </c>
       <c r="I32">
-        <v>208.4890679042447</v>
+        <v>73.64348590847847</v>
       </c>
       <c r="J32">
-        <v>14040.61577798235</v>
+        <v>544.7240614319505</v>
       </c>
       <c r="K32">
-        <v>23269.35297521733</v>
+        <v>-1361.446423020036</v>
       </c>
       <c r="L32">
-        <v>0.0007357915636016385</v>
+        <v>0.03639958424899981</v>
       </c>
       <c r="M32">
-        <v>213.779998779297</v>
+        <v>21.69</v>
       </c>
       <c r="N32">
-        <v>26.48020351858564</v>
+        <v>0.1697817781857487</v>
       </c>
       <c r="O32">
-        <v>195.9331691584728</v>
+        <v>58.33355852297152</v>
       </c>
       <c r="P32">
-        <v>208.1042190194309</v>
+        <v>73.64431838284435</v>
       </c>
       <c r="Q32">
-        <v>23216.72945829315</v>
+        <v>-1361.465843254048</v>
       </c>
       <c r="R32">
-        <v>0.173872884591964</v>
+        <v>0.03671777708980879</v>
       </c>
     </row>
     <row r="33" spans="1:18">
@@ -2228,55 +2228,55 @@
         <v>18</v>
       </c>
       <c r="B33">
-        <v>270.5</v>
+        <v>22.12931987017325</v>
       </c>
       <c r="C33">
-        <v>142.300003051758</v>
+        <v>17.42931987017325</v>
       </c>
       <c r="D33">
-        <v>14104.46556740213</v>
+        <v>6732.681407683718</v>
       </c>
       <c r="E33">
-        <v>16899.86466867402</v>
+        <v>-1430.126559983715</v>
       </c>
       <c r="F33">
-        <v>122.4951992671089</v>
+        <v>0.2477189912672105</v>
       </c>
       <c r="G33">
-        <v>370.6767844175679</v>
+        <v>117.9698646653664</v>
       </c>
       <c r="H33">
-        <v>202.5359534820523</v>
+        <v>60.09746053600261</v>
       </c>
       <c r="I33">
-        <v>214.7883773647745</v>
+        <v>75.41502024276497</v>
       </c>
       <c r="J33">
-        <v>16842.37130737565</v>
+        <v>400.2054328887792</v>
       </c>
       <c r="K33">
-        <v>26284.74376252681</v>
+        <v>-1202.257820974109</v>
       </c>
       <c r="L33">
-        <v>0.0001729756062536362</v>
+        <v>0.03856455217516374</v>
       </c>
       <c r="M33">
-        <v>137.300003051758</v>
+        <v>12.22931987017325</v>
       </c>
       <c r="N33">
-        <v>120.7407461207967</v>
+        <v>0.2446263572314825</v>
       </c>
       <c r="O33">
-        <v>202.0489827361815</v>
+        <v>60.0982102847151</v>
       </c>
       <c r="P33">
-        <v>214.3613519311005</v>
+        <v>75.41577038391804</v>
       </c>
       <c r="Q33">
-        <v>26221.54559422631</v>
+        <v>-1202.27281979844</v>
       </c>
       <c r="R33">
-        <v>0.2501227800362073</v>
+        <v>0.03885958349429459</v>
       </c>
     </row>
     <row r="34" spans="1:18">
@@ -2284,55 +2284,55 @@
         <v>18</v>
       </c>
       <c r="B34">
-        <v>309.440002441406</v>
+        <v>36.57060571590704</v>
       </c>
       <c r="C34">
-        <v>173.740005493164</v>
+        <v>24.27060571590705</v>
       </c>
       <c r="D34">
-        <v>24869.99185008183</v>
+        <v>4571.332848187875</v>
       </c>
       <c r="E34">
-        <v>27399.18548192432</v>
+        <v>-1640.975274013994</v>
       </c>
       <c r="F34">
-        <v>1.257535002237749</v>
+        <v>0.1019355986460211</v>
       </c>
       <c r="G34">
-        <v>381.9618419745027</v>
+        <v>121.3040538591951</v>
       </c>
       <c r="H34">
-        <v>208.6917732975846</v>
+        <v>61.86126149389725</v>
       </c>
       <c r="I34">
-        <v>221.0905451787038</v>
+        <v>77.18748771428747</v>
       </c>
       <c r="J34">
-        <v>19898.83188489561</v>
+        <v>277.9204395060959</v>
       </c>
       <c r="K34">
-        <v>29438.73341652547</v>
+        <v>-1031.285747947807</v>
       </c>
       <c r="L34">
-        <v>0.003168324276997596</v>
+        <v>0.0404159959975564</v>
       </c>
       <c r="M34">
-        <v>168.740005493164</v>
+        <v>19.07060571590705</v>
       </c>
       <c r="N34">
-        <v>0.801262193965417</v>
+        <v>0.1037055996099656</v>
       </c>
       <c r="O34">
-        <v>208.1619239759202</v>
+        <v>61.8619289091988</v>
       </c>
       <c r="P34">
-        <v>220.6213571807403</v>
+        <v>77.18815552225165</v>
       </c>
       <c r="Q34">
-        <v>29363.9911653819</v>
+        <v>-1031.296874392238</v>
       </c>
       <c r="R34">
-        <v>0.3435568071175736</v>
+        <v>0.04068479218116637</v>
       </c>
     </row>
     <row r="35" spans="1:18">
@@ -2340,55 +2340,55 @@
         <v>18</v>
       </c>
       <c r="B35">
-        <v>110.029998779297</v>
+        <v>84.41329513262913</v>
       </c>
       <c r="C35">
-        <v>64.23000335693401</v>
+        <v>39.01329513262912</v>
       </c>
       <c r="D35">
-        <v>1739.53877973504</v>
+        <v>390.8111103003052</v>
       </c>
       <c r="E35">
-        <v>-2678.890747159341</v>
+        <v>-771.2516106428646</v>
       </c>
       <c r="F35">
-        <v>0.3174240527079064</v>
+        <v>119.8534205574802</v>
       </c>
       <c r="G35">
-        <v>393.2468995314375</v>
+        <v>124.6382430530238</v>
       </c>
       <c r="H35">
-        <v>214.8448347492987</v>
+        <v>63.62413089645087</v>
       </c>
       <c r="I35">
-        <v>227.3954713564512</v>
+        <v>78.96088674115096</v>
       </c>
       <c r="J35">
-        <v>23209.99751054224</v>
+        <v>177.8690812839006</v>
       </c>
       <c r="K35">
-        <v>32731.24040040583</v>
+        <v>-848.5395588067458</v>
       </c>
       <c r="L35">
-        <v>0.01044117832187113</v>
+        <v>0.04192848027295665</v>
       </c>
       <c r="M35">
-        <v>59.23000335693401</v>
+        <v>33.81329513262911</v>
       </c>
       <c r="N35">
-        <v>1.184805518644615</v>
+        <v>119.8879868556589</v>
       </c>
       <c r="O35">
-        <v>214.2720933564717</v>
+        <v>63.62471597831762</v>
       </c>
       <c r="P35">
-        <v>226.8841342895672</v>
+        <v>78.9614722159501</v>
       </c>
       <c r="Q35">
-        <v>32643.9842360314</v>
+        <v>-848.5473619012962</v>
       </c>
       <c r="R35">
-        <v>0.4555216997788279</v>
+        <v>0.04216843052787186</v>
       </c>
     </row>
     <row r="36" spans="1:18">
@@ -2396,55 +2396,55 @@
         <v>18</v>
       </c>
       <c r="B36">
-        <v>411.130004882813</v>
+        <v>28.13</v>
       </c>
       <c r="C36">
-        <v>228.229995727539</v>
+        <v>20.22</v>
       </c>
       <c r="D36">
-        <v>67284.32778881623</v>
+        <v>5783.942936381173</v>
       </c>
       <c r="E36">
-        <v>59201.08701869292</v>
+        <v>-1537.776256557092</v>
       </c>
       <c r="F36">
-        <v>7.623475713315658</v>
+        <v>0.01128026490990577</v>
       </c>
       <c r="G36">
-        <v>404.5319570883723</v>
+        <v>127.9724322468525</v>
       </c>
       <c r="H36">
-        <v>220.9952367278531</v>
+        <v>65.38607066082437</v>
       </c>
       <c r="I36">
-        <v>233.7030570073583</v>
+        <v>80.73521540619458</v>
       </c>
       <c r="J36">
-        <v>26775.86818431553</v>
+        <v>100.0513582221934</v>
       </c>
       <c r="K36">
-        <v>36162.18751109277</v>
+        <v>-654.0285906727105</v>
       </c>
       <c r="L36">
-        <v>0.02272127288545152</v>
+        <v>0.0430819685742665</v>
       </c>
       <c r="M36">
-        <v>223.229995727539</v>
+        <v>15.02</v>
       </c>
       <c r="N36">
-        <v>4.629571405043485</v>
+        <v>0.01065853320317047</v>
       </c>
       <c r="O36">
-        <v>220.37959025232</v>
+        <v>65.3865734092325</v>
       </c>
       <c r="P36">
-        <v>233.1495838830973</v>
+        <v>80.73571854785253</v>
       </c>
       <c r="Q36">
-        <v>36061.44722538159</v>
+        <v>-654.0336194476392</v>
       </c>
       <c r="R36">
-        <v>0.5873417489527488</v>
+        <v>0.04329092422341666</v>
       </c>
     </row>
     <row r="37" spans="1:18">
@@ -2452,55 +2452,55 @@
         <v>18</v>
       </c>
       <c r="B37">
-        <v>319.399993896484</v>
+        <v>32.84</v>
       </c>
       <c r="C37">
-        <v>177.600006103516</v>
+        <v>23.24</v>
       </c>
       <c r="D37">
-        <v>28110.61891182146</v>
+        <v>5089.71495246585</v>
       </c>
       <c r="E37">
-        <v>29776.81071087166</v>
+        <v>-1657.993615943958</v>
       </c>
       <c r="F37">
-        <v>7.612066806844364</v>
+        <v>0.3949824084448612</v>
       </c>
       <c r="G37">
-        <v>415.8170146453072</v>
+        <v>131.3066214406812</v>
       </c>
       <c r="H37">
-        <v>227.1430766734426</v>
+        <v>67.14708303597342</v>
       </c>
       <c r="I37">
-        <v>240.0132046912304</v>
+        <v>82.51047146046264</v>
       </c>
       <c r="J37">
-        <v>30596.44390621548</v>
+        <v>44.4672703209742</v>
       </c>
       <c r="K37">
-        <v>39731.50175574544</v>
+        <v>-447.7621573113114</v>
       </c>
       <c r="L37">
-        <v>0.04074402494955186</v>
+        <v>0.04386179885673219</v>
       </c>
       <c r="M37">
-        <v>172.600006103516</v>
+        <v>18.04</v>
       </c>
       <c r="N37">
-        <v>6.226039743703078</v>
+        <v>0.3914055736412322</v>
       </c>
       <c r="O37">
-        <v>226.4845125803883</v>
+        <v>67.14750345089918</v>
       </c>
       <c r="P37">
-        <v>239.4176080444074</v>
+        <v>82.51089226900312</v>
       </c>
       <c r="Q37">
-        <v>39616.30678347218</v>
+        <v>-447.7649607971161</v>
       </c>
       <c r="R37">
-        <v>0.7403149795454832</v>
+        <v>0.04403807235563764</v>
       </c>
     </row>
     <row r="38" spans="1:18">
@@ -2508,55 +2508,55 @@
         <v>18</v>
       </c>
       <c r="B38">
-        <v>314.140014648438</v>
+        <v>83.56925201416</v>
       </c>
       <c r="C38">
-        <v>180.139999389648</v>
+        <v>52.269248962402</v>
       </c>
       <c r="D38">
-        <v>26374.48673236844</v>
+        <v>424.8951998097662</v>
       </c>
       <c r="E38">
-        <v>29255.13895711832</v>
+        <v>-1077.425307201972</v>
       </c>
       <c r="F38">
-        <v>7.20566813147533</v>
+        <v>7.59440420641679</v>
       </c>
       <c r="G38">
-        <v>427.102072202242</v>
+        <v>134.6408106345099</v>
       </c>
       <c r="H38">
-        <v>233.2884502728751</v>
+        <v>68.90717059859719</v>
       </c>
       <c r="I38">
-        <v>246.3258187212595</v>
+        <v>84.28665232725598</v>
       </c>
       <c r="J38">
-        <v>34671.7246762421</v>
+        <v>11.11681758024317</v>
       </c>
       <c r="K38">
-        <v>43439.11421350915</v>
+        <v>-229.7495435871441</v>
       </c>
       <c r="L38">
-        <v>0.06524630308105343</v>
+        <v>0.04425864927915509</v>
       </c>
       <c r="M38">
-        <v>175.139999389648</v>
+        <v>47.069248962402</v>
       </c>
       <c r="N38">
-        <v>8.575015559952444</v>
+        <v>7.585591409501577</v>
       </c>
       <c r="O38">
-        <v>232.5869564956349</v>
+        <v>68.90750868001686</v>
       </c>
       <c r="P38">
-        <v>245.6881106185391</v>
+        <v>84.28699080270272</v>
       </c>
       <c r="Q38">
-        <v>43308.49365225135</v>
+        <v>-229.7506708145602</v>
       </c>
       <c r="R38">
-        <v>0.9157099269099066</v>
+        <v>0.04440101295646785</v>
       </c>
     </row>
     <row r="39" spans="1:18">
@@ -2564,55 +2564,55 @@
         <v>18</v>
       </c>
       <c r="B39">
-        <v>20.840000152588</v>
+        <v>93.11</v>
       </c>
       <c r="C39">
-        <v>13.340000152588</v>
+        <v>58.51</v>
       </c>
       <c r="D39">
-        <v>17134.2280326416</v>
+        <v>122.5944589252024</v>
       </c>
       <c r="E39">
-        <v>-1746.176365617121</v>
+        <v>-647.8366575249986</v>
       </c>
       <c r="F39">
-        <v>4.943316412462525</v>
+        <v>15.50034601165779</v>
       </c>
       <c r="G39">
-        <v>438.3871297591768</v>
+        <v>137.9749998283386</v>
       </c>
       <c r="H39">
-        <v>239.4314512029183</v>
+        <v>70.66633624852318</v>
       </c>
       <c r="I39">
-        <v>252.6408054206779</v>
+        <v>86.0637551067471</v>
       </c>
       <c r="J39">
-        <v>39001.71049439537</v>
+        <v>1.292469707114106E-26</v>
       </c>
       <c r="K39">
-        <v>47284.95988589388</v>
+        <v>8.033832301467007E-12</v>
       </c>
       <c r="L39">
-        <v>0.0969626703527305</v>
+        <v>0.04426849467375751</v>
       </c>
       <c r="M39">
-        <v>8.340000152588001</v>
+        <v>53.31</v>
       </c>
       <c r="N39">
-        <v>9.514119248808209</v>
+        <v>15.48960897734345</v>
       </c>
       <c r="O39">
-        <v>238.6870161331436</v>
+        <v>70.66659199641317</v>
       </c>
       <c r="P39">
-        <v>251.9609974704088</v>
+        <v>86.06401124912368</v>
       </c>
       <c r="Q39">
-        <v>47137.94251522225</v>
+        <v>8.033861376635875E-12</v>
       </c>
       <c r="R39">
-        <v>1.114762977908295</v>
+        <v>0.04437617919965625</v>
       </c>
     </row>
     <row r="40" spans="1:18">
@@ -2620,55 +2620,55 @@
         <v>18</v>
       </c>
       <c r="B40">
-        <v>70.23000335693401</v>
+        <v>132</v>
       </c>
       <c r="C40">
-        <v>42.729999542236</v>
+        <v>61</v>
       </c>
       <c r="D40">
-        <v>6643.517194789833</v>
+        <v>773.8278711403043</v>
       </c>
       <c r="E40">
-        <v>-3482.827138462243</v>
+        <v>1696.883469338149</v>
       </c>
       <c r="F40">
-        <v>0.009038830785578463</v>
+        <v>201.5400087346858</v>
       </c>
       <c r="G40">
-        <v>449.6721873161116</v>
+        <v>141.3091890221672</v>
       </c>
       <c r="H40">
-        <v>245.572170917081</v>
+        <v>72.424583203548</v>
       </c>
       <c r="I40">
-        <v>258.9580733359768</v>
+        <v>87.84177658113938</v>
       </c>
       <c r="J40">
-        <v>43586.40136067531</v>
+        <v>11.11681758024469</v>
       </c>
       <c r="K40">
-        <v>51268.97753884286</v>
+        <v>241.4772626848239</v>
       </c>
       <c r="L40">
-        <v>0.1366220840693752</v>
+        <v>0.04389255389652052</v>
       </c>
       <c r="M40">
-        <v>37.729999542236</v>
+        <v>55.8</v>
       </c>
       <c r="N40">
-        <v>0.5930809599498119</v>
+        <v>201.5514651629877</v>
       </c>
       <c r="O40">
-        <v>244.784783393862</v>
+        <v>72.42475661788475</v>
       </c>
       <c r="P40">
-        <v>258.2361766990688</v>
+        <v>87.84195039046938</v>
       </c>
       <c r="Q40">
-        <v>51104.59183873881</v>
+        <v>241.4778408810316</v>
       </c>
       <c r="R40">
-        <v>1.338676236735239</v>
+        <v>0.04396524648318709</v>
       </c>
     </row>
     <row r="41" spans="1:18">
@@ -2676,55 +2676,2015 @@
         <v>18</v>
       </c>
       <c r="B41">
-        <v>224.669998168945</v>
+        <v>143</v>
       </c>
       <c r="C41">
-        <v>128.470001220703</v>
+        <v>89</v>
       </c>
       <c r="D41">
-        <v>5319.108857308576</v>
+        <v>1506.818630573735</v>
       </c>
       <c r="E41">
-        <v>9369.602518534417</v>
+        <v>3454.780799526151</v>
       </c>
       <c r="F41">
-        <v>0.1591615335336428</v>
+        <v>63.52370716315298</v>
       </c>
       <c r="G41">
-        <v>460.9572448730464</v>
+        <v>144.6433782159959</v>
       </c>
       <c r="H41">
-        <v>251.7106984726677</v>
+        <v>74.18191499375456</v>
       </c>
       <c r="I41">
-        <v>265.2775334098516</v>
+        <v>89.62071322034993</v>
       </c>
       <c r="J41">
-        <v>48425.79727508192</v>
+        <v>44.46727032097723</v>
       </c>
       <c r="K41">
-        <v>55391.10953922627</v>
+        <v>494.6730786993965</v>
       </c>
       <c r="L41">
-        <v>0.1849450303632487</v>
+        <v>0.04313722832422371</v>
       </c>
       <c r="M41">
-        <v>123.470001220703</v>
+        <v>83.8</v>
       </c>
       <c r="N41">
-        <v>0.09352270025280078</v>
+        <v>63.52160529303897</v>
       </c>
       <c r="O41">
-        <v>250.8803477708099</v>
+        <v>74.18200607451465</v>
       </c>
       <c r="P41">
-        <v>264.5135588114993</v>
+        <v>89.62080469665676</v>
       </c>
       <c r="Q41">
-        <v>55208.38370769961</v>
+        <v>494.6736860603686</v>
       </c>
       <c r="R41">
-        <v>1.588615872542383</v>
+        <v>0.04317507066356988</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18">
+      <c r="A42" t="s">
+        <v>18</v>
+      </c>
+      <c r="B42">
+        <v>183</v>
+      </c>
+      <c r="C42">
+        <v>82.7</v>
+      </c>
+      <c r="D42">
+        <v>6212.239573968029</v>
+      </c>
+      <c r="E42">
+        <v>6518.228900233851</v>
+      </c>
+      <c r="F42">
+        <v>381.8892978977622</v>
+      </c>
+      <c r="G42">
+        <v>147.9775674098246</v>
+      </c>
+      <c r="H42">
+        <v>75.93833545532917</v>
+      </c>
+      <c r="I42">
+        <v>91.40056118819243</v>
+      </c>
+      <c r="J42">
+        <v>100.0513582221976</v>
+      </c>
+      <c r="K42">
+        <v>759.5783324174956</v>
+      </c>
+      <c r="L42">
+        <v>0.0420140317981583</v>
+      </c>
+      <c r="M42">
+        <v>77.5</v>
+      </c>
+      <c r="N42">
+        <v>381.8558471847944</v>
+      </c>
+      <c r="O42">
+        <v>75.9383442024892</v>
+      </c>
+      <c r="P42">
+        <v>91.40057033149945</v>
+      </c>
+      <c r="Q42">
+        <v>759.578419911555</v>
+      </c>
+      <c r="R42">
+        <v>0.04201761774225318</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18">
+      <c r="A43" t="s">
+        <v>18</v>
+      </c>
+      <c r="B43">
+        <v>74.78</v>
+      </c>
+      <c r="C43">
+        <v>47.28</v>
+      </c>
+      <c r="D43">
+        <v>864.4916116147673</v>
+      </c>
+      <c r="E43">
+        <v>-1390.137822453973</v>
+      </c>
+      <c r="F43">
+        <v>5.892863623665074</v>
+      </c>
+      <c r="G43">
+        <v>151.3117566036533</v>
+      </c>
+      <c r="H43">
+        <v>77.69384872390302</v>
+      </c>
+      <c r="I43">
+        <v>93.18131634903568</v>
+      </c>
+      <c r="J43">
+        <v>177.8690812839059</v>
+      </c>
+      <c r="K43">
+        <v>1036.183963368799</v>
+      </c>
+      <c r="L43">
+        <v>0.04053951234497009</v>
+      </c>
+      <c r="M43">
+        <v>42.08</v>
+      </c>
+      <c r="N43">
+        <v>5.884047927991449</v>
+      </c>
+      <c r="O43">
+        <v>77.69377513743979</v>
+      </c>
+      <c r="P43">
+        <v>93.18124315936615</v>
+      </c>
+      <c r="Q43">
+        <v>1036.182981964037</v>
+      </c>
+      <c r="R43">
+        <v>0.0405098853354886</v>
+      </c>
+    </row>
+    <row r="44" spans="1:18">
+      <c r="A44" t="s">
+        <v>18</v>
+      </c>
+      <c r="B44">
+        <v>260.6</v>
+      </c>
+      <c r="C44">
+        <v>146.5</v>
+      </c>
+      <c r="D44">
+        <v>24466.51620415296</v>
+      </c>
+      <c r="E44">
+        <v>22915.2021025908</v>
+      </c>
+      <c r="F44">
+        <v>9.649804307920595</v>
+      </c>
+      <c r="G44">
+        <v>154.6459457974819</v>
+      </c>
+      <c r="H44">
+        <v>79.44845922744466</v>
+      </c>
+      <c r="I44">
+        <v>94.96297427491115</v>
+      </c>
+      <c r="J44">
+        <v>277.920439506102</v>
+      </c>
+      <c r="K44">
+        <v>1324.480971112431</v>
+      </c>
+      <c r="L44">
+        <v>0.03873516603374358</v>
+      </c>
+      <c r="M44">
+        <v>141.3</v>
+      </c>
+      <c r="N44">
+        <v>9.667034654677778</v>
+      </c>
+      <c r="O44">
+        <v>79.44830330733504</v>
+      </c>
+      <c r="P44">
+        <v>94.96281875228817</v>
+      </c>
+      <c r="Q44">
+        <v>1324.478371776707</v>
+      </c>
+      <c r="R44">
+        <v>0.0386738162870187</v>
+      </c>
+    </row>
+    <row r="45" spans="1:18">
+      <c r="A45" t="s">
+        <v>18</v>
+      </c>
+      <c r="B45">
+        <v>220.2</v>
+      </c>
+      <c r="C45">
+        <v>131.2</v>
+      </c>
+      <c r="D45">
+        <v>13460.12105132472</v>
+      </c>
+      <c r="E45">
+        <v>15221.53034716664</v>
+      </c>
+      <c r="F45">
+        <v>85.20580841857844</v>
+      </c>
+      <c r="G45">
+        <v>157.9801349913106</v>
+      </c>
+      <c r="H45">
+        <v>81.20217167873083</v>
+      </c>
+      <c r="I45">
+        <v>96.74553025304208</v>
+      </c>
+      <c r="J45">
+        <v>400.205432888786</v>
+      </c>
+      <c r="K45">
+        <v>1624.460419959882</v>
+      </c>
+      <c r="L45">
+        <v>0.03662734335379539</v>
+      </c>
+      <c r="M45">
+        <v>126</v>
+      </c>
+      <c r="N45">
+        <v>85.23857113835878</v>
+      </c>
+      <c r="O45">
+        <v>81.2019334249518</v>
+      </c>
+      <c r="P45">
+        <v>96.74529239748868</v>
+      </c>
+      <c r="Q45">
+        <v>1624.455653660829</v>
+      </c>
+      <c r="R45">
+        <v>0.03653620480878611</v>
+      </c>
+    </row>
+    <row r="46" spans="1:18">
+      <c r="A46" t="s">
+        <v>18</v>
+      </c>
+      <c r="B46">
+        <v>224</v>
+      </c>
+      <c r="C46">
+        <v>127</v>
+      </c>
+      <c r="D46">
+        <v>14356.29604094718</v>
+      </c>
+      <c r="E46">
+        <v>15216.85574763844</v>
+      </c>
+      <c r="F46">
+        <v>9.093503448633168</v>
+      </c>
+      <c r="G46">
+        <v>161.3143241851393</v>
+      </c>
+      <c r="H46">
+        <v>82.9549910674249</v>
+      </c>
+      <c r="I46">
+        <v>98.52897929376512</v>
+      </c>
+      <c r="J46">
+        <v>544.7240614319578</v>
+      </c>
+      <c r="K46">
+        <v>1936.113443538148</v>
+      </c>
+      <c r="L46">
+        <v>0.03424714852087294</v>
+      </c>
+      <c r="M46">
+        <v>121.8</v>
+      </c>
+      <c r="N46">
+        <v>9.104774976961515</v>
+      </c>
+      <c r="O46">
+        <v>82.95467047995359</v>
+      </c>
+      <c r="P46">
+        <v>98.52865910530417</v>
+      </c>
+      <c r="Q46">
+        <v>1936.10596124317</v>
+      </c>
+      <c r="R46">
+        <v>0.03412859555773538</v>
+      </c>
+    </row>
+    <row r="47" spans="1:18">
+      <c r="A47" t="s">
+        <v>18</v>
+      </c>
+      <c r="B47">
+        <v>200.9</v>
+      </c>
+      <c r="C47">
+        <v>98.86</v>
+      </c>
+      <c r="D47">
+        <v>9354.325446136976</v>
+      </c>
+      <c r="E47">
+        <v>9561.517930799499</v>
+      </c>
+      <c r="F47">
+        <v>165.7509876098936</v>
+      </c>
+      <c r="G47">
+        <v>164.648513378968</v>
+      </c>
+      <c r="H47">
+        <v>84.70692265179242</v>
+      </c>
+      <c r="I47">
+        <v>100.3133161388147</v>
+      </c>
+      <c r="J47">
+        <v>711.4763251356175</v>
+      </c>
+      <c r="K47">
+        <v>2259.431249184713</v>
+      </c>
+      <c r="L47">
+        <v>0.03163033213923484</v>
+      </c>
+      <c r="M47">
+        <v>93.66</v>
+      </c>
+      <c r="N47">
+        <v>165.7175697735359</v>
+      </c>
+      <c r="O47">
+        <v>84.70651973060608</v>
+      </c>
+      <c r="P47">
+        <v>100.312913617469</v>
+      </c>
+      <c r="Q47">
+        <v>2259.420501860989</v>
+      </c>
+      <c r="R47">
+        <v>0.03148717607654977</v>
+      </c>
+    </row>
+    <row r="48" spans="1:18">
+      <c r="A48" t="s">
+        <v>18</v>
+      </c>
+      <c r="B48">
+        <v>174.9</v>
+      </c>
+      <c r="C48">
+        <v>110.1</v>
+      </c>
+      <c r="D48">
+        <v>5001.001832930685</v>
+      </c>
+      <c r="E48">
+        <v>7786.025573346396</v>
+      </c>
+      <c r="F48">
+        <v>147.7069587614819</v>
+      </c>
+      <c r="G48">
+        <v>167.9827025727967</v>
+      </c>
+      <c r="H48">
+        <v>86.45797195008487</v>
+      </c>
+      <c r="I48">
+        <v>102.0985352699394</v>
+      </c>
+      <c r="J48">
+        <v>900.462223999765</v>
+      </c>
+      <c r="K48">
+        <v>2594.405122166853</v>
+      </c>
+      <c r="L48">
+        <v>0.02881717766435687</v>
+      </c>
+      <c r="M48">
+        <v>104.9</v>
+      </c>
+      <c r="N48">
+        <v>147.7229013397661</v>
+      </c>
+      <c r="O48">
+        <v>86.4574866951609</v>
+      </c>
+      <c r="P48">
+        <v>102.0980504157314</v>
+      </c>
+      <c r="Q48">
+        <v>2594.390560781339</v>
+      </c>
+      <c r="R48">
+        <v>0.02865266304361706</v>
+      </c>
+    </row>
+    <row r="49" spans="1:18">
+      <c r="A49" t="s">
+        <v>18</v>
+      </c>
+      <c r="B49">
+        <v>173.5</v>
+      </c>
+      <c r="C49">
+        <v>94.16</v>
+      </c>
+      <c r="D49">
+        <v>4804.952099911884</v>
+      </c>
+      <c r="E49">
+        <v>6526.960450375083</v>
+      </c>
+      <c r="F49">
+        <v>9.266539217832506</v>
+      </c>
+      <c r="G49">
+        <v>171.3168917666253</v>
+      </c>
+      <c r="H49">
+        <v>88.20814473162253</v>
+      </c>
+      <c r="I49">
+        <v>103.8846309178188</v>
+      </c>
+      <c r="J49">
+        <v>1111.681758024401</v>
+      </c>
+      <c r="K49">
+        <v>2941.026429718529</v>
+      </c>
+      <c r="L49">
+        <v>0.02585238212503747</v>
+      </c>
+      <c r="M49">
+        <v>88.95999999999999</v>
+      </c>
+      <c r="N49">
+        <v>9.262757025953176</v>
+      </c>
+      <c r="O49">
+        <v>88.20757714293848</v>
+      </c>
+      <c r="P49">
+        <v>103.8840637307711</v>
+      </c>
+      <c r="Q49">
+        <v>2941.007505237959</v>
+      </c>
+      <c r="R49">
+        <v>0.02567018279114374</v>
+      </c>
+    </row>
+    <row r="50" spans="1:18">
+      <c r="A50" t="s">
+        <v>18</v>
+      </c>
+      <c r="B50">
+        <v>237.1</v>
+      </c>
+      <c r="C50">
+        <v>148.6</v>
+      </c>
+      <c r="D50">
+        <v>17667.13139990881</v>
+      </c>
+      <c r="E50">
+        <v>19751.5794023549</v>
+      </c>
+      <c r="F50">
+        <v>312.1780079338797</v>
+      </c>
+      <c r="G50">
+        <v>174.651080960454</v>
+      </c>
+      <c r="H50">
+        <v>89.95744700760845</v>
+      </c>
+      <c r="I50">
+        <v>105.67159707125</v>
+      </c>
+      <c r="J50">
+        <v>1345.134927209524</v>
+      </c>
+      <c r="K50">
+        <v>3299.286624889035</v>
+      </c>
+      <c r="L50">
+        <v>0.02278493157480612</v>
+      </c>
+      <c r="M50">
+        <v>143.4</v>
+      </c>
+      <c r="N50">
+        <v>312.2554650926612</v>
+      </c>
+      <c r="O50">
+        <v>89.95679708514199</v>
+      </c>
+      <c r="P50">
+        <v>105.6709475513849</v>
+      </c>
+      <c r="Q50">
+        <v>3299.262788279925</v>
+      </c>
+      <c r="R50">
+        <v>0.02258914656180225</v>
+      </c>
+    </row>
+    <row r="51" spans="1:18">
+      <c r="A51" t="s">
+        <v>18</v>
+      </c>
+      <c r="B51">
+        <v>134.8</v>
+      </c>
+      <c r="C51">
+        <v>79.67</v>
+      </c>
+      <c r="D51">
+        <v>937.4473371779055</v>
+      </c>
+      <c r="E51">
+        <v>2439.317082002793</v>
+      </c>
+      <c r="F51">
+        <v>8.932146953222375</v>
+      </c>
+      <c r="G51">
+        <v>177.9852701542827</v>
+      </c>
+      <c r="H51">
+        <v>91.70588502170524</v>
+      </c>
+      <c r="I51">
+        <v>107.4594274865703</v>
+      </c>
+      <c r="J51">
+        <v>1600.821731555135</v>
+      </c>
+      <c r="K51">
+        <v>3669.177250198388</v>
+      </c>
+      <c r="L51">
+        <v>0.01966797175074813</v>
+      </c>
+      <c r="M51">
+        <v>74.47</v>
+      </c>
+      <c r="N51">
+        <v>8.930148556681919</v>
+      </c>
+      <c r="O51">
+        <v>91.70515276543424</v>
+      </c>
+      <c r="P51">
+        <v>107.4586956339099</v>
+      </c>
+      <c r="Q51">
+        <v>3669.147952427038</v>
+      </c>
+      <c r="R51">
+        <v>0.01946312098223324</v>
+      </c>
+    </row>
+    <row r="52" spans="1:18">
+      <c r="A52" t="s">
+        <v>18</v>
+      </c>
+      <c r="B52">
+        <v>123.91</v>
+      </c>
+      <c r="C52">
+        <v>87.45</v>
+      </c>
+      <c r="D52">
+        <v>389.1845853388083</v>
+      </c>
+      <c r="E52">
+        <v>1725.192768747887</v>
+      </c>
+      <c r="F52">
+        <v>273.693396292972</v>
+      </c>
+      <c r="G52">
+        <v>181.3194593481114</v>
+      </c>
+      <c r="H52">
+        <v>93.45346524040684</v>
+      </c>
+      <c r="I52">
+        <v>109.2481156972858</v>
+      </c>
+      <c r="J52">
+        <v>1878.742171061234</v>
+      </c>
+      <c r="K52">
+        <v>4050.689941095321</v>
+      </c>
+      <c r="L52">
+        <v>0.01655867442308107</v>
+      </c>
+      <c r="M52">
+        <v>82.25</v>
+      </c>
+      <c r="N52">
+        <v>273.6734363309362</v>
+      </c>
+      <c r="O52">
+        <v>93.45265065030932</v>
+      </c>
+      <c r="P52">
+        <v>109.2473015118521</v>
+      </c>
+      <c r="Q52">
+        <v>4050.654633127813</v>
+      </c>
+      <c r="R52">
+        <v>0.01634969423685914</v>
+      </c>
+    </row>
+    <row r="53" spans="1:18">
+      <c r="A53" t="s">
+        <v>18</v>
+      </c>
+      <c r="B53">
+        <v>126.69</v>
+      </c>
+      <c r="C53">
+        <v>75.53</v>
+      </c>
+      <c r="D53">
+        <v>506.5993409047117</v>
+      </c>
+      <c r="E53">
+        <v>1700.011248182137</v>
+      </c>
+      <c r="F53">
+        <v>9.918947437799011</v>
+      </c>
+      <c r="G53">
+        <v>184.65364854194</v>
+      </c>
+      <c r="H53">
+        <v>95.20019434323697</v>
+      </c>
+      <c r="I53">
+        <v>111.0376550238728</v>
+      </c>
+      <c r="J53">
+        <v>2178.896245727821</v>
+      </c>
+      <c r="K53">
+        <v>4443.816429214561</v>
+      </c>
+      <c r="L53">
+        <v>0.01351809992125015</v>
+      </c>
+      <c r="M53">
+        <v>70.33</v>
+      </c>
+      <c r="N53">
+        <v>9.915580264915405</v>
+      </c>
+      <c r="O53">
+        <v>95.19929741929114</v>
+      </c>
+      <c r="P53">
+        <v>111.0367585056875</v>
+      </c>
+      <c r="Q53">
+        <v>4443.774562016771</v>
+      </c>
+      <c r="R53">
+        <v>0.0133103384281134</v>
+      </c>
+    </row>
+    <row r="54" spans="1:18">
+      <c r="A54" t="s">
+        <v>18</v>
+      </c>
+      <c r="B54">
+        <v>96.26000000000001</v>
+      </c>
+      <c r="C54">
+        <v>59.43</v>
+      </c>
+      <c r="D54">
+        <v>62.76185821750293</v>
+      </c>
+      <c r="E54">
+        <v>-470.8186166759639</v>
+      </c>
+      <c r="F54">
+        <v>10.15435551626536</v>
+      </c>
+      <c r="G54">
+        <v>187.9878377357687</v>
+      </c>
+      <c r="H54">
+        <v>96.94607921280581</v>
+      </c>
+      <c r="I54">
+        <v>112.828038583721</v>
+      </c>
+      <c r="J54">
+        <v>2501.283955554895</v>
+      </c>
+      <c r="K54">
+        <v>4848.548545430954</v>
+      </c>
+      <c r="L54">
+        <v>0.0106110563219232</v>
+      </c>
+      <c r="M54">
+        <v>54.23</v>
+      </c>
+      <c r="N54">
+        <v>10.14616100126158</v>
+      </c>
+      <c r="O54">
+        <v>96.94509995499003</v>
+      </c>
+      <c r="P54">
+        <v>112.8270597328059</v>
+      </c>
+      <c r="Q54">
+        <v>4848.499569968543</v>
+      </c>
+      <c r="R54">
+        <v>0.01041026860850085</v>
+      </c>
+    </row>
+    <row r="55" spans="1:18">
+      <c r="A55" t="s">
+        <v>18</v>
+      </c>
+      <c r="B55">
+        <v>37.22</v>
+      </c>
+      <c r="C55">
+        <v>26.37</v>
+      </c>
+      <c r="D55">
+        <v>4483.941345767525</v>
+      </c>
+      <c r="E55">
+        <v>-1765.794221533656</v>
+      </c>
+      <c r="F55">
+        <v>2.061361641826796</v>
+      </c>
+      <c r="G55">
+        <v>191.3220269295974</v>
+      </c>
+      <c r="H55">
+        <v>98.69112692475605</v>
+      </c>
+      <c r="I55">
+        <v>114.6192593011879</v>
+      </c>
+      <c r="J55">
+        <v>2845.905300542458</v>
+      </c>
+      <c r="K55">
+        <v>5264.878222708749</v>
+      </c>
+      <c r="L55">
+        <v>0.007905955781368344</v>
+      </c>
+      <c r="M55">
+        <v>21.17</v>
+      </c>
+      <c r="N55">
+        <v>2.053489939148221</v>
+      </c>
+      <c r="O55">
+        <v>98.69006533304886</v>
+      </c>
+      <c r="P55">
+        <v>114.6181981175644</v>
+      </c>
+      <c r="Q55">
+        <v>5264.821589947175</v>
+      </c>
+      <c r="R55">
+        <v>0.007718298967118941</v>
+      </c>
+    </row>
+    <row r="56" spans="1:18">
+      <c r="A56" t="s">
+        <v>18</v>
+      </c>
+      <c r="B56">
+        <v>129.92</v>
+      </c>
+      <c r="C56">
+        <v>70.22</v>
+      </c>
+      <c r="D56">
+        <v>662.4323820838003</v>
+      </c>
+      <c r="E56">
+        <v>1807.30563306434</v>
+      </c>
+      <c r="F56">
+        <v>15.00358551712642</v>
+      </c>
+      <c r="G56">
+        <v>194.6562161234261</v>
+      </c>
+      <c r="H56">
+        <v>100.4353447376286</v>
+      </c>
+      <c r="I56">
+        <v>116.4113099177325</v>
+      </c>
+      <c r="J56">
+        <v>3212.760280690508</v>
+      </c>
+      <c r="K56">
+        <v>5692.797498745218</v>
+      </c>
+      <c r="L56">
+        <v>0.005474668489154271</v>
+      </c>
+      <c r="M56">
+        <v>65.02</v>
+      </c>
+      <c r="N56">
+        <v>15.00710941722218</v>
+      </c>
+      <c r="O56">
+        <v>100.4342008120088</v>
+      </c>
+      <c r="P56">
+        <v>116.4101664014217</v>
+      </c>
+      <c r="Q56">
+        <v>5692.732659649734</v>
+      </c>
+      <c r="R56">
+        <v>0.005306696647592212</v>
+      </c>
+    </row>
+    <row r="57" spans="1:18">
+      <c r="A57" t="s">
+        <v>18</v>
+      </c>
+      <c r="B57">
+        <v>75.87</v>
+      </c>
+      <c r="C57">
+        <v>41.98</v>
+      </c>
+      <c r="D57">
+        <v>801.5828323222617</v>
+      </c>
+      <c r="E57">
+        <v>-1188.547759953844</v>
+      </c>
+      <c r="F57">
+        <v>11.90601482908975</v>
+      </c>
+      <c r="G57">
+        <v>197.9904053172548</v>
+      </c>
+      <c r="H57">
+        <v>102.1787400826779</v>
+      </c>
+      <c r="I57">
+        <v>118.2041830021002</v>
+      </c>
+      <c r="J57">
+        <v>3601.848895999046</v>
+      </c>
+      <c r="K57">
+        <v>6132.298518408502</v>
+      </c>
+      <c r="L57">
+        <v>0.003392374712372525</v>
+      </c>
+      <c r="M57">
+        <v>36.77999999999999</v>
+      </c>
+      <c r="N57">
+        <v>11.91836770986767</v>
+      </c>
+      <c r="O57">
+        <v>102.1775138231243</v>
+      </c>
+      <c r="P57">
+        <v>118.2029571531234</v>
+      </c>
+      <c r="Q57">
+        <v>6132.224923944159</v>
+      </c>
+      <c r="R57">
+        <v>0.003251033666683003</v>
+      </c>
+    </row>
+    <row r="58" spans="1:18">
+      <c r="A58" t="s">
+        <v>18</v>
+      </c>
+      <c r="B58">
+        <v>49.65</v>
+      </c>
+      <c r="C58">
+        <v>25.38</v>
+      </c>
+      <c r="D58">
+        <v>2973.765003927303</v>
+      </c>
+      <c r="E58">
+        <v>-1384.02820570816</v>
+      </c>
+      <c r="F58">
+        <v>37.77252609073163</v>
+      </c>
+      <c r="G58">
+        <v>201.3245945110834</v>
+      </c>
+      <c r="H58">
+        <v>103.9213205536654</v>
+      </c>
+      <c r="I58">
+        <v>119.9978709605299</v>
+      </c>
+      <c r="J58">
+        <v>4013.171146468072</v>
+      </c>
+      <c r="K58">
+        <v>6583.37353597032</v>
+      </c>
+      <c r="L58">
+        <v>0.00173741538948384</v>
+      </c>
+      <c r="M58">
+        <v>20.18</v>
+      </c>
+      <c r="N58">
+        <v>37.80248746481175</v>
+      </c>
+      <c r="O58">
+        <v>103.9200119601572</v>
+      </c>
+      <c r="P58">
+        <v>119.9965627789078</v>
+      </c>
+      <c r="Q58">
+        <v>6583.290637101972</v>
+      </c>
+      <c r="R58">
+        <v>0.001630037392643564</v>
+      </c>
+    </row>
+    <row r="59" spans="1:18">
+      <c r="A59" t="s">
+        <v>18</v>
+      </c>
+      <c r="B59">
+        <v>118.68</v>
+      </c>
+      <c r="C59">
+        <v>63.92</v>
+      </c>
+      <c r="D59">
+        <v>210.1850969900048</v>
+      </c>
+      <c r="E59">
+        <v>926.696933772041</v>
+      </c>
+      <c r="F59">
+        <v>17.74792036506814</v>
+      </c>
+      <c r="G59">
+        <v>204.6587837049121</v>
+      </c>
+      <c r="H59">
+        <v>105.663093896659</v>
+      </c>
+      <c r="I59">
+        <v>121.7923660469534</v>
+      </c>
+      <c r="J59">
+        <v>4446.727032097587</v>
+      </c>
+      <c r="K59">
+        <v>7046.014917134918</v>
+      </c>
+      <c r="L59">
+        <v>0.0005911417210037487</v>
+      </c>
+      <c r="M59">
+        <v>58.72</v>
+      </c>
+      <c r="N59">
+        <v>17.75409192872138</v>
+      </c>
+      <c r="O59">
+        <v>105.6617029691755</v>
+      </c>
+      <c r="P59">
+        <v>121.7909755327068</v>
+      </c>
+      <c r="Q59">
+        <v>7045.922164827221</v>
+      </c>
+      <c r="R59">
+        <v>0.0005254400304684351</v>
+      </c>
+    </row>
+    <row r="60" spans="1:18">
+      <c r="A60" t="s">
+        <v>18</v>
+      </c>
+      <c r="B60">
+        <v>118.24</v>
+      </c>
+      <c r="C60">
+        <v>70.08</v>
+      </c>
+      <c r="D60">
+        <v>197.6206666126672</v>
+      </c>
+      <c r="E60">
+        <v>985.1679464134007</v>
+      </c>
+      <c r="F60">
+        <v>4.75460525551044</v>
+      </c>
+      <c r="G60">
+        <v>207.9929728987408</v>
+      </c>
+      <c r="H60">
+        <v>107.4040679998654</v>
+      </c>
+      <c r="I60">
+        <v>123.5876603731641</v>
+      </c>
+      <c r="J60">
+        <v>4902.516552887589</v>
+      </c>
+      <c r="K60">
+        <v>7520.215140866238</v>
+      </c>
+      <c r="L60">
+        <v>3.776419026277239E-05</v>
+      </c>
+      <c r="M60">
+        <v>64.88</v>
+      </c>
+      <c r="N60">
+        <v>4.751364380197337</v>
+      </c>
+      <c r="O60">
+        <v>107.4025947383861</v>
+      </c>
+      <c r="P60">
+        <v>123.5861875263134</v>
+      </c>
+      <c r="Q60">
+        <v>7520.111986083658</v>
+      </c>
+      <c r="R60">
+        <v>2.182754721424105E-05</v>
+      </c>
+    </row>
+    <row r="61" spans="1:18">
+      <c r="A61" t="s">
+        <v>18</v>
+      </c>
+      <c r="B61">
+        <v>246.48</v>
+      </c>
+      <c r="C61">
+        <v>128.96</v>
+      </c>
+      <c r="D61">
+        <v>20248.65301113477</v>
+      </c>
+      <c r="E61">
+        <v>18350.7193607516</v>
+      </c>
+      <c r="F61">
+        <v>48.24264609371202</v>
+      </c>
+      <c r="G61">
+        <v>211.3271620925695</v>
+      </c>
+      <c r="H61">
+        <v>109.1442508835209</v>
+      </c>
+      <c r="I61">
+        <v>125.3837459189257</v>
+      </c>
+      <c r="J61">
+        <v>5380.539708838078</v>
+      </c>
+      <c r="K61">
+        <v>8005.966801015964</v>
+      </c>
+      <c r="L61">
+        <v>0.0001642014321404532</v>
+      </c>
+      <c r="M61">
+        <v>123.76</v>
+      </c>
+      <c r="N61">
+        <v>48.20898703739802</v>
+      </c>
+      <c r="O61">
+        <v>109.1426952880256</v>
+      </c>
+      <c r="P61">
+        <v>125.3821907394913</v>
+      </c>
+      <c r="Q61">
+        <v>8005.852694722777</v>
+      </c>
+      <c r="R61">
+        <v>0.0002064884551393457</v>
+      </c>
+    </row>
+    <row r="62" spans="1:18">
+      <c r="A62" t="s">
+        <v>18</v>
+      </c>
+      <c r="B62">
+        <v>83.66</v>
+      </c>
+      <c r="C62">
+        <v>54.86</v>
+      </c>
+      <c r="D62">
+        <v>421.1622610483007</v>
+      </c>
+      <c r="E62">
+        <v>-1125.849988067363</v>
+      </c>
+      <c r="F62">
+        <v>28.0732721711713</v>
+      </c>
+      <c r="G62">
+        <v>214.6613512863981</v>
+      </c>
+      <c r="H62">
+        <v>110.8836506898642</v>
+      </c>
+      <c r="I62">
+        <v>127.1806145419995</v>
+      </c>
+      <c r="J62">
+        <v>5880.796499949056</v>
+      </c>
+      <c r="K62">
+        <v>8503.262607755652</v>
+      </c>
+      <c r="L62">
+        <v>0.001059929350627053</v>
+      </c>
+      <c r="M62">
+        <v>49.66</v>
+      </c>
+      <c r="N62">
+        <v>28.05634964838022</v>
+      </c>
+      <c r="O62">
+        <v>110.8820127603328</v>
+      </c>
+      <c r="P62">
+        <v>127.1789770300013</v>
+      </c>
+      <c r="Q62">
+        <v>8503.137000915945</v>
+      </c>
+      <c r="R62">
+        <v>0.001169262853407978</v>
+      </c>
+    </row>
+    <row r="63" spans="1:18">
+      <c r="A63" t="s">
+        <v>18</v>
+      </c>
+      <c r="B63">
+        <v>84.03</v>
+      </c>
+      <c r="C63">
+        <v>46.12</v>
+      </c>
+      <c r="D63">
+        <v>406.1127047746977</v>
+      </c>
+      <c r="E63">
+        <v>-929.4212261331896</v>
+      </c>
+      <c r="F63">
+        <v>13.23352227373786</v>
+      </c>
+      <c r="G63">
+        <v>217.9955404802268</v>
+      </c>
+      <c r="H63">
+        <v>112.6222756732154</v>
+      </c>
+      <c r="I63">
+        <v>128.9782579880654</v>
+      </c>
+      <c r="J63">
+        <v>6403.286926220521</v>
+      </c>
+      <c r="K63">
+        <v>9012.095388816711</v>
+      </c>
+      <c r="L63">
+        <v>0.002816830867964299</v>
+      </c>
+      <c r="M63">
+        <v>40.91999999999999</v>
+      </c>
+      <c r="N63">
+        <v>13.24507873993302</v>
+      </c>
+      <c r="O63">
+        <v>112.6205554096281</v>
+      </c>
+      <c r="P63">
+        <v>128.9765381435234</v>
+      </c>
+      <c r="Q63">
+        <v>9011.95773239439</v>
+      </c>
+      <c r="R63">
+        <v>0.003002392110905727</v>
+      </c>
+    </row>
+    <row r="64" spans="1:18">
+      <c r="A64" t="s">
+        <v>18</v>
+      </c>
+      <c r="B64">
+        <v>247.59</v>
+      </c>
+      <c r="C64">
+        <v>106.61</v>
+      </c>
+      <c r="D64">
+        <v>20565.78614231397</v>
+      </c>
+      <c r="E64">
+        <v>15288.70148469082</v>
+      </c>
+      <c r="F64">
+        <v>893.0731905944443</v>
+      </c>
+      <c r="G64">
+        <v>221.3297296740555</v>
+      </c>
+      <c r="H64">
+        <v>114.3601341901811</v>
+      </c>
+      <c r="I64">
+        <v>130.7766679005168</v>
+      </c>
+      <c r="J64">
+        <v>6948.010987652475</v>
+      </c>
+      <c r="K64">
+        <v>9532.458090542497</v>
+      </c>
+      <c r="L64">
+        <v>0.005529046668831072</v>
+      </c>
+      <c r="M64">
+        <v>101.41</v>
+      </c>
+      <c r="N64">
+        <v>892.9267126228445</v>
+      </c>
+      <c r="O64">
+        <v>114.3583315925182</v>
+      </c>
+      <c r="P64">
+        <v>130.7748657234505</v>
+      </c>
+      <c r="Q64">
+        <v>9532.307835501284</v>
+      </c>
+      <c r="R64">
+        <v>0.005800369553455358</v>
+      </c>
+    </row>
+    <row r="65" spans="1:18">
+      <c r="A65" t="s">
+        <v>18</v>
+      </c>
+      <c r="B65">
+        <v>261.34</v>
+      </c>
+      <c r="C65">
+        <v>139.19</v>
+      </c>
+      <c r="D65">
+        <v>24698.56209160574</v>
+      </c>
+      <c r="E65">
+        <v>21874.78886388814</v>
+      </c>
+      <c r="F65">
+        <v>21.1233228281963</v>
+      </c>
+      <c r="G65">
+        <v>224.6639188678842</v>
+      </c>
+      <c r="H65">
+        <v>116.0972346900074</v>
+      </c>
+      <c r="I65">
+        <v>132.5758358301075</v>
+      </c>
+      <c r="J65">
+        <v>7514.968684244915</v>
+      </c>
+      <c r="K65">
+        <v>10064.3437787572</v>
+      </c>
+      <c r="L65">
+        <v>0.009292827282961479</v>
+      </c>
+      <c r="M65">
+        <v>133.99</v>
+      </c>
+      <c r="N65">
+        <v>21.0976813126274</v>
+      </c>
+      <c r="O65">
+        <v>116.0953497582495</v>
+      </c>
+      <c r="P65">
+        <v>132.5739513205364</v>
+      </c>
+      <c r="Q65">
+        <v>10064.18037606064</v>
+      </c>
+      <c r="R65">
+        <v>0.009659792498562702</v>
+      </c>
+    </row>
+    <row r="66" spans="1:18">
+      <c r="A66" t="s">
+        <v>18</v>
+      </c>
+      <c r="B66">
+        <v>118.8</v>
+      </c>
+      <c r="C66">
+        <v>77.29000000000001</v>
+      </c>
+      <c r="D66">
+        <v>213.6789598201873</v>
+      </c>
+      <c r="E66">
+        <v>1129.806808936812</v>
+      </c>
+      <c r="F66">
+        <v>82.69238671413292</v>
+      </c>
+      <c r="G66">
+        <v>227.9981080617129</v>
+      </c>
+      <c r="H66">
+        <v>117.8335857050983</v>
+      </c>
+      <c r="I66">
+        <v>134.3757532444338</v>
+      </c>
+      <c r="J66">
+        <v>8104.160015997844</v>
+      </c>
+      <c r="K66">
+        <v>10607.74563945666</v>
+      </c>
+      <c r="L66">
+        <v>0.01420638682871566</v>
+      </c>
+      <c r="M66">
+        <v>72.09</v>
+      </c>
+      <c r="N66">
+        <v>82.67912076264224</v>
+      </c>
+      <c r="O66">
+        <v>117.8316184392261</v>
+      </c>
+      <c r="P66">
+        <v>134.3737864023771</v>
+      </c>
+      <c r="Q66">
+        <v>10607.56854006813</v>
+      </c>
+      <c r="R66">
+        <v>0.01467921596003864</v>
+      </c>
+    </row>
+    <row r="67" spans="1:18">
+      <c r="A67" t="s">
+        <v>18</v>
+      </c>
+      <c r="B67">
+        <v>17.52</v>
+      </c>
+      <c r="C67">
+        <v>12.62</v>
+      </c>
+      <c r="D67">
+        <v>7510.343531145837</v>
+      </c>
+      <c r="E67">
+        <v>-1093.67744617955</v>
+      </c>
+      <c r="F67">
+        <v>3.486678055954568</v>
+      </c>
+      <c r="G67">
+        <v>231.3322972555415</v>
+      </c>
+      <c r="H67">
+        <v>119.5691958417164</v>
+      </c>
+      <c r="I67">
+        <v>136.1764115372328</v>
+      </c>
+      <c r="J67">
+        <v>8715.584982911261</v>
+      </c>
+      <c r="K67">
+        <v>11162.65697932662</v>
+      </c>
+      <c r="L67">
+        <v>0.02036975871890225</v>
+      </c>
+      <c r="M67">
+        <v>7.419999999999999</v>
+      </c>
+      <c r="N67">
+        <v>3.498752586204419</v>
+      </c>
+      <c r="O67">
+        <v>119.5671462417111</v>
+      </c>
+      <c r="P67">
+        <v>136.1743623627094</v>
+      </c>
+      <c r="Q67">
+        <v>11162.46563420931</v>
+      </c>
+      <c r="R67">
+        <v>0.02095900832343478</v>
+      </c>
+    </row>
+    <row r="68" spans="1:18">
+      <c r="A68" t="s">
+        <v>18</v>
+      </c>
+      <c r="B68">
+        <v>124.2</v>
+      </c>
+      <c r="C68">
+        <v>61.58</v>
+      </c>
+      <c r="D68">
+        <v>400.7107871784171</v>
+      </c>
+      <c r="E68">
+        <v>1232.693771177758</v>
+      </c>
+      <c r="F68">
+        <v>89.87242359338828</v>
+      </c>
+      <c r="G68">
+        <v>234.6664864493702</v>
+      </c>
+      <c r="H68">
+        <v>121.3040737708837</v>
+      </c>
+      <c r="I68">
+        <v>137.9778020374826</v>
+      </c>
+      <c r="J68">
+        <v>9349.243584985166</v>
+      </c>
+      <c r="K68">
+        <v>11729.07122609405</v>
+      </c>
+      <c r="L68">
+        <v>0.02788465360835087</v>
+      </c>
+      <c r="M68">
+        <v>56.38</v>
+      </c>
+      <c r="N68">
+        <v>89.88372613487412</v>
+      </c>
+      <c r="O68">
+        <v>121.3019418367264</v>
+      </c>
+      <c r="P68">
+        <v>137.9756705305113</v>
+      </c>
+      <c r="Q68">
+        <v>11728.865086211</v>
+      </c>
+      <c r="R68">
+        <v>0.02860120927162753</v>
+      </c>
+    </row>
+    <row r="69" spans="1:18">
+      <c r="A69" t="s">
+        <v>18</v>
+      </c>
+      <c r="B69">
+        <v>30.49</v>
+      </c>
+      <c r="C69">
+        <v>20.29</v>
+      </c>
+      <c r="D69">
+        <v>5430.545972041436</v>
+      </c>
+      <c r="E69">
+        <v>-1495.215513231622</v>
+      </c>
+      <c r="F69">
+        <v>1.1562896500961</v>
+      </c>
+      <c r="G69">
+        <v>238.0006756431989</v>
+      </c>
+      <c r="H69">
+        <v>123.0382282194934</v>
+      </c>
+      <c r="I69">
+        <v>139.77991601829</v>
+      </c>
+      <c r="J69">
+        <v>10005.13582221956</v>
+      </c>
+      <c r="K69">
+        <v>12306.98192871786</v>
+      </c>
+      <c r="L69">
+        <v>0.03685431984108433</v>
+      </c>
+      <c r="M69">
+        <v>15.09</v>
+      </c>
+      <c r="N69">
+        <v>1.162556723483761</v>
+      </c>
+      <c r="O69">
+        <v>123.0360139511656</v>
+      </c>
+      <c r="P69">
+        <v>139.7777021788894</v>
+      </c>
+      <c r="Q69">
+        <v>12306.76044503194</v>
+      </c>
+      <c r="R69">
+        <v>0.03770939021798721</v>
+      </c>
+    </row>
+    <row r="70" spans="1:18">
+      <c r="A70" t="s">
+        <v>18</v>
+      </c>
+      <c r="B70">
+        <v>37.1</v>
+      </c>
+      <c r="C70">
+        <v>24.7</v>
+      </c>
+      <c r="D70">
+        <v>4500.026682937341</v>
+      </c>
+      <c r="E70">
+        <v>-1656.931283727012</v>
+      </c>
+      <c r="F70">
+        <v>0.02911092027061901</v>
+      </c>
+      <c r="G70">
+        <v>241.3348648370276</v>
+      </c>
+      <c r="H70">
+        <v>124.7716679616489</v>
+      </c>
+      <c r="I70">
+        <v>141.5827447055516</v>
+      </c>
+      <c r="J70">
+        <v>10683.26169461444</v>
+      </c>
+      <c r="K70">
+        <v>12896.38275742501</v>
+      </c>
+      <c r="L70">
+        <v>0.04738340663286492</v>
+      </c>
+      <c r="M70">
+        <v>19.5</v>
+      </c>
+      <c r="N70">
+        <v>0.03005581954232021</v>
+      </c>
+      <c r="O70">
+        <v>124.7693713591323</v>
+      </c>
+      <c r="P70">
+        <v>141.58044853374</v>
+      </c>
+      <c r="Q70">
+        <v>12896.14538089892</v>
+      </c>
+      <c r="R70">
+        <v>0.04838851748276429</v>
+      </c>
+    </row>
+    <row r="71" spans="1:18">
+      <c r="A71" t="s">
+        <v>18</v>
+      </c>
+      <c r="B71">
+        <v>87.19</v>
+      </c>
+      <c r="C71">
+        <v>60.69</v>
+      </c>
+      <c r="D71">
+        <v>288.736159302847</v>
+      </c>
+      <c r="E71">
+        <v>-1031.258936817504</v>
+      </c>
+      <c r="F71">
+        <v>85.68183289049603</v>
+      </c>
+      <c r="G71">
+        <v>244.6690540308562</v>
+      </c>
+      <c r="H71">
+        <v>126.5044018102386</v>
+      </c>
+      <c r="I71">
+        <v>143.386279286379</v>
+      </c>
+      <c r="J71">
+        <v>11383.62120216981</v>
+      </c>
+      <c r="K71">
+        <v>13497.26750359869</v>
+      </c>
+      <c r="L71">
+        <v>0.05957783020339363</v>
+      </c>
+      <c r="M71">
+        <v>55.48999999999999</v>
+      </c>
+      <c r="N71">
+        <v>85.65388047260778</v>
+      </c>
+      <c r="O71">
+        <v>126.5020228735151</v>
+      </c>
+      <c r="P71">
+        <v>143.3839007821744</v>
+      </c>
+      <c r="Q71">
+        <v>13497.01368519497</v>
+      </c>
+      <c r="R71">
+        <v>0.06074481842640037</v>
+      </c>
+    </row>
+    <row r="72" spans="1:18">
+      <c r="A72" t="s">
+        <v>18</v>
+      </c>
+      <c r="B72">
+        <v>100.7</v>
+      </c>
+      <c r="C72">
+        <v>49.9</v>
+      </c>
+      <c r="D72">
+        <v>12.12598293426957</v>
+      </c>
+      <c r="E72">
+        <v>-173.7636865578093</v>
+      </c>
+      <c r="F72">
+        <v>75.65451291007192</v>
+      </c>
+      <c r="G72">
+        <v>248.0032432246849</v>
+      </c>
+      <c r="H72">
+        <v>128.2364386087582</v>
+      </c>
+      <c r="I72">
+        <v>145.1905109172765</v>
+      </c>
+      <c r="J72">
+        <v>12106.21434488566</v>
+      </c>
+      <c r="K72">
+        <v>14109.63007952509</v>
+      </c>
+      <c r="L72">
+        <v>0.07354464305049391</v>
+      </c>
+      <c r="M72">
+        <v>44.7</v>
+      </c>
+      <c r="N72">
+        <v>75.6749788709399</v>
+      </c>
+      <c r="O72">
+        <v>128.23397733781</v>
+      </c>
+      <c r="P72">
+        <v>145.1880500806969</v>
+      </c>
+      <c r="Q72">
+        <v>14109.35927020614</v>
+      </c>
+      <c r="R72">
+        <v>0.0748856507321212</v>
+      </c>
+    </row>
+    <row r="73" spans="1:18">
+      <c r="A73" t="s">
+        <v>18</v>
+      </c>
+      <c r="B73">
+        <v>25.76</v>
+      </c>
+      <c r="C73">
+        <v>17.56</v>
+      </c>
+      <c r="D73">
+        <v>6150.04744548506</v>
+      </c>
+      <c r="E73">
+        <v>-1377.094502924952</v>
+      </c>
+      <c r="F73">
+        <v>1.682132946850579</v>
+      </c>
+      <c r="G73">
+        <v>251.3374324185136</v>
+      </c>
+      <c r="H73">
+        <v>129.9677872233882</v>
+      </c>
+      <c r="I73">
+        <v>146.9954307320636</v>
+      </c>
+      <c r="J73">
+        <v>12851.04112276201</v>
+      </c>
+      <c r="K73">
+        <v>14733.46451800557</v>
+      </c>
+      <c r="L73">
+        <v>0.08939190653819322</v>
+      </c>
+      <c r="M73">
+        <v>12.36</v>
+      </c>
+      <c r="N73">
+        <v>1.689993821953574</v>
+      </c>
+      <c r="O73">
+        <v>129.9652436181976</v>
+      </c>
+      <c r="P73">
+        <v>146.9928875631265</v>
+      </c>
+      <c r="Q73">
+        <v>14733.17616873362</v>
+      </c>
+      <c r="R73">
+        <v>0.0909193750091003</v>
+      </c>
+    </row>
+    <row r="74" spans="1:18">
+      <c r="A74" t="s">
+        <v>18</v>
+      </c>
+      <c r="B74">
+        <v>83.72</v>
+      </c>
+      <c r="C74">
+        <v>48.02</v>
+      </c>
+      <c r="D74">
+        <v>418.703192463392</v>
+      </c>
+      <c r="E74">
+        <v>-982.5966787275754</v>
+      </c>
+      <c r="F74">
+        <v>2.475576792739965</v>
+      </c>
+      <c r="G74">
+        <v>254.6716216123423</v>
+      </c>
+      <c r="H74">
+        <v>131.6984565353339</v>
+      </c>
+      <c r="I74">
+        <v>148.801029849535</v>
+      </c>
+      <c r="J74">
+        <v>13618.10153579884</v>
+      </c>
+      <c r="K74">
+        <v>15368.76497184093</v>
+      </c>
+      <c r="L74">
+        <v>0.1072285669492176</v>
+      </c>
+      <c r="M74">
+        <v>42.82</v>
+      </c>
+      <c r="N74">
+        <v>2.480600673979578</v>
+      </c>
+      <c r="O74">
+        <v>131.6958305958836</v>
+      </c>
+      <c r="P74">
+        <v>148.7984043482578</v>
+      </c>
+      <c r="Q74">
+        <v>15368.45853357806</v>
+      </c>
+      <c r="R74">
+        <v>0.1089552308663949</v>
+      </c>
+    </row>
+    <row r="75" spans="1:18">
+      <c r="A75" t="s">
+        <v>18</v>
+      </c>
+      <c r="B75">
+        <v>28.34</v>
+      </c>
+      <c r="C75">
+        <v>18.74</v>
+      </c>
+      <c r="D75">
+        <v>5752.045096333992</v>
+      </c>
+      <c r="E75">
+        <v>-1421.283544009887</v>
+      </c>
+      <c r="F75">
+        <v>2.205686177317498</v>
+      </c>
+      <c r="G75">
+        <v>258.005810806171</v>
+      </c>
+      <c r="H75">
+        <v>133.4284554334342</v>
+      </c>
+      <c r="I75">
+        <v>150.6072993808518</v>
+      </c>
+      <c r="J75">
+        <v>14407.39558399617</v>
+      </c>
+      <c r="K75">
+        <v>16015.52571319469</v>
+      </c>
+      <c r="L75">
+        <v>0.1271643351323992</v>
+      </c>
+      <c r="M75">
+        <v>13.54</v>
+      </c>
+      <c r="N75">
+        <v>2.214496681507276</v>
+      </c>
+      <c r="O75">
+        <v>133.4257471597069</v>
+      </c>
+      <c r="P75">
+        <v>150.6045915472518</v>
+      </c>
+      <c r="Q75">
+        <v>16015.20063690285</v>
+      </c>
+      <c r="R75">
+        <v>0.1291032165881942</v>
+      </c>
+    </row>
+    <row r="76" spans="1:18">
+      <c r="A76" t="s">
+        <v>18</v>
+      </c>
+      <c r="B76">
+        <v>117</v>
+      </c>
+      <c r="C76">
+        <v>62.81</v>
+      </c>
+      <c r="D76">
+        <v>164.2950173674442</v>
+      </c>
+      <c r="E76">
+        <v>805.0836181824448</v>
+      </c>
+      <c r="F76">
+        <v>19.64188985951823</v>
+      </c>
+      <c r="G76">
+        <v>261.3399999999997</v>
+      </c>
+      <c r="H76">
+        <v>135.1577928070432</v>
+      </c>
+      <c r="I76">
+        <v>152.4142304366599</v>
+      </c>
+      <c r="J76">
+        <v>15218.92326735398</v>
+      </c>
+      <c r="K76">
+        <v>16673.74113284224</v>
+      </c>
+      <c r="L76">
+        <v>0.1493095698569852</v>
+      </c>
+      <c r="M76">
+        <v>57.61</v>
+      </c>
+      <c r="N76">
+        <v>19.64875013047456</v>
+      </c>
+      <c r="O76">
+        <v>135.155002199022</v>
+      </c>
+      <c r="P76">
+        <v>152.411440270754</v>
+      </c>
+      <c r="Q76">
+        <v>16673.39686948323</v>
+      </c>
+      <c r="R76">
+        <v>0.1514739725213519</v>
       </c>
     </row>
   </sheetData>
